--- a/output/2025-07-01.xlsx
+++ b/output/2025-07-01.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>6.32</v>
+        <v>5.89</v>
       </c>
       <c r="F14" t="n">
-        <v>16.44</v>
+        <v>16.11</v>
       </c>
       <c r="G14" t="n">
-        <v>340.9</v>
+        <v>328.8</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>212.21</v>
+        <v>257.62</v>
       </c>
       <c r="K14" t="n">
-        <v>120.87</v>
+        <v>272.97</v>
       </c>
       <c r="L14" t="n">
-        <v>244.22</v>
+        <v>375.34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:35:07</t>
+          <t>04:35:04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>5.51</v>
+        <v>6.63</v>
       </c>
       <c r="F15" t="n">
-        <v>16</v>
+        <v>15.81</v>
       </c>
       <c r="G15" t="n">
-        <v>330.3</v>
+        <v>345.8</v>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>104.41</v>
+        <v>463.91</v>
       </c>
       <c r="K15" t="n">
-        <v>-144.37</v>
+        <v>162.9</v>
       </c>
       <c r="L15" t="n">
-        <v>178.17</v>
+        <v>491.67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:36:40</t>
+          <t>04:35:50</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5.87</v>
+        <v>6.1</v>
       </c>
       <c r="F16" t="n">
-        <v>15.6</v>
+        <v>16.06</v>
       </c>
       <c r="G16" t="n">
-        <v>326.7</v>
+        <v>323.4</v>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>201.44</v>
+        <v>-462.25</v>
       </c>
       <c r="K16" t="n">
-        <v>-117.89</v>
+        <v>406.45</v>
       </c>
       <c r="L16" t="n">
-        <v>233.4</v>
+        <v>615.53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:40:31</t>
+          <t>04:40:25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>5.81</v>
+        <v>5.64</v>
       </c>
       <c r="F17" t="n">
-        <v>15.75</v>
+        <v>16.33</v>
       </c>
       <c r="G17" t="n">
-        <v>336.8</v>
+        <v>337.2</v>
       </c>
       <c r="H17" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>-128.35</v>
+        <v>125.61</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.57</v>
+        <v>192.67</v>
       </c>
       <c r="L17" t="n">
-        <v>128.43</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:41:47</t>
+          <t>04:43:12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -796,31 +796,31 @@
         <v>5.8</v>
       </c>
       <c r="F18" t="n">
-        <v>16.04</v>
+        <v>16.01</v>
       </c>
       <c r="G18" t="n">
-        <v>340.5</v>
+        <v>326.4</v>
       </c>
       <c r="H18" t="n">
-        <v>99.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>218.71</v>
+        <v>248.57</v>
       </c>
       <c r="K18" t="n">
-        <v>-186.14</v>
+        <v>-216.68</v>
       </c>
       <c r="L18" t="n">
-        <v>287.2</v>
+        <v>329.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:42:42</t>
+          <t>04:45:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>6.36</v>
+        <v>6.82</v>
       </c>
       <c r="F19" t="n">
-        <v>16.35</v>
+        <v>16.42</v>
       </c>
       <c r="G19" t="n">
-        <v>337.8</v>
+        <v>325.8</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>449.04</v>
+        <v>3.01</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.88</v>
+        <v>203.76</v>
       </c>
       <c r="L19" t="n">
-        <v>449.05</v>
+        <v>203.78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:48:15</t>
+          <t>04:50:38</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>5.81</v>
+        <v>5.39</v>
       </c>
       <c r="F20" t="n">
-        <v>16.14</v>
+        <v>16.18</v>
       </c>
       <c r="G20" t="n">
-        <v>323.9</v>
+        <v>352.3</v>
       </c>
       <c r="H20" t="n">
-        <v>96.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>376.95</v>
+        <v>-295.18</v>
       </c>
       <c r="K20" t="n">
-        <v>4.62</v>
+        <v>524.0700000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>376.97</v>
+        <v>601.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:49:40</t>
+          <t>04:51:28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,13 +919,13 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>6.07</v>
+        <v>5.73</v>
       </c>
       <c r="F21" t="n">
-        <v>15.81</v>
+        <v>16.22</v>
       </c>
       <c r="G21" t="n">
-        <v>329.9</v>
+        <v>334.1</v>
       </c>
       <c r="H21" t="n">
         <v>100</v>
@@ -934,19 +934,19 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>205.81</v>
+        <v>308.17</v>
       </c>
       <c r="K21" t="n">
-        <v>297.89</v>
+        <v>-203.43</v>
       </c>
       <c r="L21" t="n">
-        <v>362.07</v>
+        <v>369.26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:51:31</t>
+          <t>04:52:53</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>5.57</v>
+        <v>5.81</v>
       </c>
       <c r="F22" t="n">
-        <v>15.81</v>
+        <v>16.41</v>
       </c>
       <c r="G22" t="n">
-        <v>309.3</v>
+        <v>326.8</v>
       </c>
       <c r="H22" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>50.76</v>
+        <v>-462.39</v>
       </c>
       <c r="K22" t="n">
-        <v>517.41</v>
+        <v>285.06</v>
       </c>
       <c r="L22" t="n">
-        <v>519.9</v>
+        <v>543.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:54:51</t>
+          <t>04:57:18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>5.67</v>
+        <v>6.03</v>
       </c>
       <c r="F23" t="n">
-        <v>15.88</v>
+        <v>15.64</v>
       </c>
       <c r="G23" t="n">
-        <v>320.7</v>
+        <v>314.8</v>
       </c>
       <c r="H23" t="n">
-        <v>97.8</v>
+        <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>28.18</v>
+        <v>1133.79</v>
       </c>
       <c r="K23" t="n">
-        <v>-60.14</v>
+        <v>241.24</v>
       </c>
       <c r="L23" t="n">
-        <v>66.42</v>
+        <v>1159.17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:57:02</t>
+          <t>04:59:43</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>6.77</v>
+        <v>5.62</v>
       </c>
       <c r="F24" t="n">
-        <v>15.97</v>
+        <v>16.02</v>
       </c>
       <c r="G24" t="n">
-        <v>318.8</v>
+        <v>339.4</v>
       </c>
       <c r="H24" t="n">
-        <v>95.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>370.94</v>
+        <v>-115.35</v>
       </c>
       <c r="K24" t="n">
-        <v>442.98</v>
+        <v>680.6</v>
       </c>
       <c r="L24" t="n">
-        <v>577.78</v>
+        <v>690.3099999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>04:58:24</t>
+          <t>05:01:20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>7.24</v>
+        <v>5.15</v>
       </c>
       <c r="F25" t="n">
-        <v>15.82</v>
+        <v>16.14</v>
       </c>
       <c r="G25" t="n">
-        <v>330.5</v>
+        <v>332.3</v>
       </c>
       <c r="H25" t="n">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>-275.23</v>
+        <v>261.86</v>
       </c>
       <c r="K25" t="n">
-        <v>154.89</v>
+        <v>275.69</v>
       </c>
       <c r="L25" t="n">
-        <v>315.83</v>
+        <v>380.23</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:01:35</t>
+          <t>05:06:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>6.27</v>
+        <v>6.46</v>
       </c>
       <c r="F26" t="n">
-        <v>15.79</v>
+        <v>16.22</v>
       </c>
       <c r="G26" t="n">
-        <v>328.2</v>
+        <v>318.3</v>
       </c>
       <c r="H26" t="n">
-        <v>95.7</v>
+        <v>97</v>
       </c>
       <c r="I26" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>61.23</v>
+        <v>876.78</v>
       </c>
       <c r="K26" t="n">
-        <v>-631.6799999999999</v>
+        <v>387.2</v>
       </c>
       <c r="L26" t="n">
-        <v>634.64</v>
+        <v>958.47</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:04:01</t>
+          <t>05:07:53</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>5.31</v>
+        <v>5.69</v>
       </c>
       <c r="F27" t="n">
-        <v>15.94</v>
+        <v>16.13</v>
       </c>
       <c r="G27" t="n">
-        <v>338.4</v>
+        <v>310.6</v>
       </c>
       <c r="H27" t="n">
         <v>98.40000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>773.0599999999999</v>
+        <v>-205.79</v>
       </c>
       <c r="K27" t="n">
-        <v>343.56</v>
+        <v>-491.24</v>
       </c>
       <c r="L27" t="n">
-        <v>845.97</v>
+        <v>532.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:05:35</t>
+          <t>05:08:46</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>5.81</v>
+        <v>5.68</v>
       </c>
       <c r="F28" t="n">
-        <v>16.01</v>
+        <v>15.68</v>
       </c>
       <c r="G28" t="n">
-        <v>313.2</v>
+        <v>333.4</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="I28" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>792.49</v>
+        <v>671.85</v>
       </c>
       <c r="K28" t="n">
-        <v>684.25</v>
+        <v>936.11</v>
       </c>
       <c r="L28" t="n">
-        <v>1047.01</v>
+        <v>1152.25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:14:25</t>
+          <t>05:19:43</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>6.77</v>
+        <v>5.81</v>
       </c>
       <c r="F29" t="n">
-        <v>16.23</v>
+        <v>16.18</v>
       </c>
       <c r="G29" t="n">
-        <v>330.4</v>
+        <v>324.3</v>
       </c>
       <c r="H29" t="n">
-        <v>93.3</v>
+        <v>96.8</v>
       </c>
       <c r="I29" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>55.8</v>
+        <v>-89.63</v>
       </c>
       <c r="K29" t="n">
-        <v>306.73</v>
+        <v>249.71</v>
       </c>
       <c r="L29" t="n">
-        <v>311.77</v>
+        <v>265.31</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:16:12</t>
+          <t>05:21:28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>6.44</v>
+        <v>6.28</v>
       </c>
       <c r="F30" t="n">
-        <v>15.8</v>
+        <v>16.59</v>
       </c>
       <c r="G30" t="n">
-        <v>324</v>
+        <v>328.2</v>
       </c>
       <c r="H30" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>-1.37</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>104.07</v>
+        <v>312.44</v>
       </c>
       <c r="L30" t="n">
-        <v>104.08</v>
+        <v>324.55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:18:02</t>
+          <t>05:22:47</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>5.39</v>
+        <v>6.03</v>
       </c>
       <c r="F31" t="n">
-        <v>16.53</v>
+        <v>16.29</v>
       </c>
       <c r="G31" t="n">
-        <v>323.9</v>
+        <v>339</v>
       </c>
       <c r="H31" t="n">
         <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>137.59</v>
+        <v>-103.03</v>
       </c>
       <c r="K31" t="n">
-        <v>68.88</v>
+        <v>187.36</v>
       </c>
       <c r="L31" t="n">
-        <v>153.87</v>
+        <v>213.82</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:21:58</t>
+          <t>05:28:10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>5.59</v>
+        <v>6.59</v>
       </c>
       <c r="F32" t="n">
-        <v>16.02</v>
+        <v>16.08</v>
       </c>
       <c r="G32" t="n">
-        <v>329.9</v>
+        <v>326.9</v>
       </c>
       <c r="H32" t="n">
         <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>-262.87</v>
+        <v>-301.07</v>
       </c>
       <c r="K32" t="n">
-        <v>-305.06</v>
+        <v>-65.31999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>402.69</v>
+        <v>308.07</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:23:13</t>
+          <t>05:29:06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>6.26</v>
+        <v>6</v>
       </c>
       <c r="F33" t="n">
-        <v>16.41</v>
+        <v>15.51</v>
       </c>
       <c r="G33" t="n">
-        <v>327</v>
+        <v>330.6</v>
       </c>
       <c r="H33" t="n">
         <v>100</v>
       </c>
       <c r="I33" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-413.29</v>
+        <v>-31.26</v>
       </c>
       <c r="K33" t="n">
-        <v>-470.03</v>
+        <v>-502.96</v>
       </c>
       <c r="L33" t="n">
-        <v>625.89</v>
+        <v>503.93</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:24:35</t>
+          <t>05:30:43</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>5.99</v>
+        <v>7.08</v>
       </c>
       <c r="F34" t="n">
-        <v>16.1</v>
+        <v>15.94</v>
       </c>
       <c r="G34" t="n">
-        <v>328</v>
+        <v>339.2</v>
       </c>
       <c r="H34" t="n">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="I34" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-222.24</v>
+        <v>-212.5</v>
       </c>
       <c r="K34" t="n">
-        <v>-317.57</v>
+        <v>44.68</v>
       </c>
       <c r="L34" t="n">
-        <v>387.61</v>
+        <v>217.15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:27:54</t>
+          <t>05:35:02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>5.86</v>
+        <v>6.67</v>
       </c>
       <c r="F35" t="n">
-        <v>15.77</v>
+        <v>15.78</v>
       </c>
       <c r="G35" t="n">
-        <v>321.2</v>
+        <v>339.5</v>
       </c>
       <c r="H35" t="n">
-        <v>100</v>
+        <v>90.3</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-669.91</v>
+        <v>-67.19</v>
       </c>
       <c r="K35" t="n">
-        <v>207.19</v>
+        <v>-354.86</v>
       </c>
       <c r="L35" t="n">
-        <v>701.22</v>
+        <v>361.16</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:30:23</t>
+          <t>05:36:48</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>6.08</v>
+        <v>5.64</v>
       </c>
       <c r="F36" t="n">
-        <v>15.79</v>
+        <v>16.22</v>
       </c>
       <c r="G36" t="n">
-        <v>323.1</v>
+        <v>322.3</v>
       </c>
       <c r="H36" t="n">
         <v>100</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>391.47</v>
+        <v>-154.91</v>
       </c>
       <c r="K36" t="n">
-        <v>395.14</v>
+        <v>-395.93</v>
       </c>
       <c r="L36" t="n">
-        <v>556.23</v>
+        <v>425.15</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:31:31</t>
+          <t>05:39:19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>5.85</v>
+        <v>6.18</v>
       </c>
       <c r="F37" t="n">
-        <v>16.13</v>
+        <v>16.51</v>
       </c>
       <c r="G37" t="n">
-        <v>326</v>
+        <v>333.1</v>
       </c>
       <c r="H37" t="n">
-        <v>93.8</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>105.07</v>
+        <v>-128.46</v>
       </c>
       <c r="K37" t="n">
-        <v>173.47</v>
+        <v>1008.09</v>
       </c>
       <c r="L37" t="n">
-        <v>202.81</v>
+        <v>1016.24</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:37:00</t>
+          <t>05:44:41</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>6.09</v>
+        <v>6.37</v>
       </c>
       <c r="F38" t="n">
-        <v>15.79</v>
+        <v>16.15</v>
       </c>
       <c r="G38" t="n">
-        <v>328.7</v>
+        <v>323.3</v>
       </c>
       <c r="H38" t="n">
-        <v>94.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>139.87</v>
+        <v>-411.49</v>
       </c>
       <c r="K38" t="n">
-        <v>-591.36</v>
+        <v>1082.88</v>
       </c>
       <c r="L38" t="n">
-        <v>607.6799999999999</v>
+        <v>1158.43</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:39:37</t>
+          <t>05:46:51</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>6.1</v>
+        <v>6.28</v>
       </c>
       <c r="F39" t="n">
-        <v>16.22</v>
+        <v>15.92</v>
       </c>
       <c r="G39" t="n">
-        <v>329.6</v>
+        <v>319.4</v>
       </c>
       <c r="H39" t="n">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>-96.19</v>
+        <v>345.26</v>
       </c>
       <c r="K39" t="n">
-        <v>151.12</v>
+        <v>-222.71</v>
       </c>
       <c r="L39" t="n">
-        <v>179.14</v>
+        <v>410.85</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:40:54</t>
+          <t>05:48:20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.95</v>
+        <v>6.68</v>
       </c>
       <c r="F40" t="n">
-        <v>15.82</v>
+        <v>16.8</v>
       </c>
       <c r="G40" t="n">
-        <v>338.6</v>
+        <v>336.6</v>
       </c>
       <c r="H40" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>-54.94</v>
+        <v>403.96</v>
       </c>
       <c r="K40" t="n">
-        <v>44.16</v>
+        <v>337.24</v>
       </c>
       <c r="L40" t="n">
-        <v>70.48999999999999</v>
+        <v>526.23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:47:12</t>
+          <t>05:52:48</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.63</v>
+        <v>6.82</v>
       </c>
       <c r="F41" t="n">
-        <v>16.27</v>
+        <v>15.77</v>
       </c>
       <c r="G41" t="n">
-        <v>327.6</v>
+        <v>321.4</v>
       </c>
       <c r="H41" t="n">
-        <v>97.7</v>
+        <v>94.8</v>
       </c>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>477.25</v>
+        <v>-93.55</v>
       </c>
       <c r="K41" t="n">
-        <v>419.01</v>
+        <v>-464.83</v>
       </c>
       <c r="L41" t="n">
-        <v>635.09</v>
+        <v>474.15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:48:42</t>
+          <t>05:53:41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>6.44</v>
+        <v>5.77</v>
       </c>
       <c r="F42" t="n">
-        <v>16.07</v>
+        <v>15.98</v>
       </c>
       <c r="G42" t="n">
-        <v>333.1</v>
+        <v>327.1</v>
       </c>
       <c r="H42" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="I42" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>427.13</v>
+        <v>17.21</v>
       </c>
       <c r="K42" t="n">
-        <v>-581.03</v>
+        <v>1109.17</v>
       </c>
       <c r="L42" t="n">
-        <v>721.13</v>
+        <v>1109.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:50:05</t>
+          <t>05:55:10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>5.89</v>
+        <v>6.7</v>
       </c>
       <c r="F43" t="n">
-        <v>16.52</v>
+        <v>16.04</v>
       </c>
       <c r="G43" t="n">
-        <v>336.5</v>
+        <v>327.6</v>
       </c>
       <c r="H43" t="n">
-        <v>98.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I43" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>308.6</v>
+        <v>-134.53</v>
       </c>
       <c r="K43" t="n">
-        <v>-339.1</v>
+        <v>-739.05</v>
       </c>
       <c r="L43" t="n">
-        <v>458.5</v>
+        <v>751.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:01:17</t>
+          <t>06:03:22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>5.82</v>
+        <v>6.69</v>
       </c>
       <c r="F44" t="n">
-        <v>16.43</v>
+        <v>15.25</v>
       </c>
       <c r="G44" t="n">
-        <v>312.9</v>
+        <v>330.6</v>
       </c>
       <c r="H44" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I44" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-100.3</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>-126.88</v>
+        <v>-87.76000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>161.73</v>
+        <v>110.74</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:01:57</t>
+          <t>06:05:04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>6.22</v>
+        <v>6.95</v>
       </c>
       <c r="F45" t="n">
-        <v>16.88</v>
+        <v>16.1</v>
       </c>
       <c r="G45" t="n">
-        <v>323.5</v>
+        <v>341.3</v>
       </c>
       <c r="H45" t="n">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="I45" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>8.24</v>
+        <v>294.21</v>
       </c>
       <c r="K45" t="n">
-        <v>112.36</v>
+        <v>-632.1799999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>112.67</v>
+        <v>697.29</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:03:51</t>
+          <t>06:07:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>5.75</v>
+        <v>6.61</v>
       </c>
       <c r="F46" t="n">
-        <v>16.25</v>
+        <v>16.36</v>
       </c>
       <c r="G46" t="n">
-        <v>315.2</v>
+        <v>327.5</v>
       </c>
       <c r="H46" t="n">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>138.43</v>
+        <v>-453.64</v>
       </c>
       <c r="K46" t="n">
-        <v>-172.78</v>
+        <v>122.46</v>
       </c>
       <c r="L46" t="n">
-        <v>221.39</v>
+        <v>469.88</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:06:34</t>
+          <t>06:12:07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="F47" t="n">
-        <v>16.38</v>
+        <v>16.26</v>
       </c>
       <c r="G47" t="n">
-        <v>328.2</v>
+        <v>336</v>
       </c>
       <c r="H47" t="n">
-        <v>97.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I47" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-453.06</v>
+        <v>-256.31</v>
       </c>
       <c r="K47" t="n">
-        <v>-339.05</v>
+        <v>427.28</v>
       </c>
       <c r="L47" t="n">
-        <v>565.88</v>
+        <v>498.26</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:09:03</t>
+          <t>06:13:08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>5.97</v>
+        <v>5.99</v>
       </c>
       <c r="F48" t="n">
-        <v>15.98</v>
+        <v>16.6</v>
       </c>
       <c r="G48" t="n">
-        <v>329.1</v>
+        <v>324.8</v>
       </c>
       <c r="H48" t="n">
-        <v>99.7</v>
+        <v>94.2</v>
       </c>
       <c r="I48" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>47.34</v>
+        <v>381.58</v>
       </c>
       <c r="K48" t="n">
-        <v>-241.56</v>
+        <v>352.6</v>
       </c>
       <c r="L48" t="n">
-        <v>246.15</v>
+        <v>519.55</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:11:16</t>
+          <t>06:14:01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>7.28</v>
+        <v>6.5</v>
       </c>
       <c r="F49" t="n">
-        <v>16.16</v>
+        <v>15.77</v>
       </c>
       <c r="G49" t="n">
-        <v>331.2</v>
+        <v>343.2</v>
       </c>
       <c r="H49" t="n">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="I49" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>308.02</v>
+        <v>47.48</v>
       </c>
       <c r="K49" t="n">
-        <v>-285.79</v>
+        <v>-383.12</v>
       </c>
       <c r="L49" t="n">
-        <v>420.19</v>
+        <v>386.05</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:15:03</t>
+          <t>06:18:44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>7.15</v>
+        <v>6.4</v>
       </c>
       <c r="F50" t="n">
-        <v>15.62</v>
+        <v>16.77</v>
       </c>
       <c r="G50" t="n">
-        <v>338.5</v>
+        <v>322.1</v>
       </c>
       <c r="H50" t="n">
         <v>100</v>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>-394.82</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-112.14</v>
+        <v>267.41</v>
       </c>
       <c r="L50" t="n">
-        <v>410.43</v>
+        <v>276.69</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:16:38</t>
+          <t>06:20:50</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>5.95</v>
+        <v>6.5</v>
       </c>
       <c r="F51" t="n">
-        <v>16.14</v>
+        <v>15.73</v>
       </c>
       <c r="G51" t="n">
-        <v>321.4</v>
+        <v>328</v>
       </c>
       <c r="H51" t="n">
-        <v>97.7</v>
+        <v>100</v>
       </c>
       <c r="I51" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-404.81</v>
+        <v>-137.73</v>
       </c>
       <c r="K51" t="n">
-        <v>-120.01</v>
+        <v>-32.52</v>
       </c>
       <c r="L51" t="n">
-        <v>422.23</v>
+        <v>141.52</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:18:30</t>
+          <t>06:22:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>6.57</v>
+        <v>6.47</v>
       </c>
       <c r="F52" t="n">
-        <v>16.09</v>
+        <v>15.1</v>
       </c>
       <c r="G52" t="n">
-        <v>333.6</v>
+        <v>336.1</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>-326.51</v>
+        <v>-222</v>
       </c>
       <c r="K52" t="n">
-        <v>106.76</v>
+        <v>646.33</v>
       </c>
       <c r="L52" t="n">
-        <v>343.52</v>
+        <v>683.4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:22:23</t>
+          <t>06:26:41</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>5.91</v>
+        <v>7.9</v>
       </c>
       <c r="F53" t="n">
-        <v>16.18</v>
+        <v>16.46</v>
       </c>
       <c r="G53" t="n">
-        <v>319.8</v>
+        <v>337.2</v>
       </c>
       <c r="H53" t="n">
         <v>100</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>405.43</v>
+        <v>77.88</v>
       </c>
       <c r="K53" t="n">
-        <v>-299.73</v>
+        <v>-387.81</v>
       </c>
       <c r="L53" t="n">
-        <v>504.19</v>
+        <v>395.55</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:24:05</t>
+          <t>06:28:21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>5.53</v>
+        <v>5.89</v>
       </c>
       <c r="F54" t="n">
-        <v>16.16</v>
+        <v>15.8</v>
       </c>
       <c r="G54" t="n">
-        <v>344.4</v>
+        <v>328.1</v>
       </c>
       <c r="H54" t="n">
-        <v>98.5</v>
+        <v>98.3</v>
       </c>
       <c r="I54" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>-81.72</v>
+        <v>764.59</v>
       </c>
       <c r="K54" t="n">
-        <v>-47.61</v>
+        <v>164.56</v>
       </c>
       <c r="L54" t="n">
-        <v>94.58</v>
+        <v>782.1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:25:06</t>
+          <t>06:30:08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>6.24</v>
+        <v>5.73</v>
       </c>
       <c r="F55" t="n">
-        <v>16.25</v>
+        <v>15.8</v>
       </c>
       <c r="G55" t="n">
-        <v>337.9</v>
+        <v>325.3</v>
       </c>
       <c r="H55" t="n">
         <v>100</v>
       </c>
       <c r="I55" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-244.83</v>
+        <v>-431.68</v>
       </c>
       <c r="K55" t="n">
-        <v>-259.49</v>
+        <v>-243.66</v>
       </c>
       <c r="L55" t="n">
-        <v>356.76</v>
+        <v>495.7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:30:46</t>
+          <t>06:34:50</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>6.35</v>
+        <v>5.75</v>
       </c>
       <c r="F56" t="n">
-        <v>15.62</v>
+        <v>16.09</v>
       </c>
       <c r="G56" t="n">
-        <v>318.4</v>
+        <v>326.1</v>
       </c>
       <c r="H56" t="n">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="I56" t="n">
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>534.42</v>
+        <v>945.3200000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>-115.32</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>546.72</v>
+        <v>948.52</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:33:00</t>
+          <t>06:35:41</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>7.65</v>
+        <v>6.95</v>
       </c>
       <c r="F57" t="n">
-        <v>15.82</v>
+        <v>16.43</v>
       </c>
       <c r="G57" t="n">
-        <v>341.3</v>
+        <v>330.1</v>
       </c>
       <c r="H57" t="n">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="I57" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J57" t="n">
-        <v>-9.960000000000001</v>
+        <v>-381.25</v>
       </c>
       <c r="K57" t="n">
-        <v>366.84</v>
+        <v>-109.84</v>
       </c>
       <c r="L57" t="n">
-        <v>366.98</v>
+        <v>396.75</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:34:49</t>
+          <t>06:36:57</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>6.33</v>
+        <v>6.64</v>
       </c>
       <c r="F58" t="n">
-        <v>15.61</v>
+        <v>15.65</v>
       </c>
       <c r="G58" t="n">
-        <v>329.7</v>
+        <v>344.6</v>
       </c>
       <c r="H58" t="n">
         <v>100</v>
       </c>
       <c r="I58" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>-375.83</v>
+        <v>126.16</v>
       </c>
       <c r="K58" t="n">
-        <v>523.85</v>
+        <v>1180.69</v>
       </c>
       <c r="L58" t="n">
-        <v>644.72</v>
+        <v>1187.41</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:45:29</t>
+          <t>06:45:11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.84</v>
+        <v>5.8</v>
       </c>
       <c r="F59" t="n">
-        <v>15.87</v>
+        <v>16.02</v>
       </c>
       <c r="G59" t="n">
-        <v>324.4</v>
+        <v>334.4</v>
       </c>
       <c r="H59" t="n">
         <v>100</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-83.89</v>
+        <v>-176.71</v>
       </c>
       <c r="K59" t="n">
-        <v>-208.12</v>
+        <v>219.03</v>
       </c>
       <c r="L59" t="n">
-        <v>224.39</v>
+        <v>281.42</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:46:09</t>
+          <t>06:47:16</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>6.69</v>
+        <v>7.27</v>
       </c>
       <c r="F60" t="n">
-        <v>16.71</v>
+        <v>16.32</v>
       </c>
       <c r="G60" t="n">
-        <v>322</v>
+        <v>328.2</v>
       </c>
       <c r="H60" t="n">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>105.7</v>
+        <v>-453.51</v>
       </c>
       <c r="K60" t="n">
-        <v>-160.07</v>
+        <v>368.49</v>
       </c>
       <c r="L60" t="n">
-        <v>191.82</v>
+        <v>584.34</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:47:36</t>
+          <t>06:49:52</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>6.49</v>
+        <v>6.07</v>
       </c>
       <c r="F61" t="n">
-        <v>16.26</v>
+        <v>15.21</v>
       </c>
       <c r="G61" t="n">
-        <v>343.1</v>
+        <v>328.9</v>
       </c>
       <c r="H61" t="n">
-        <v>92.8</v>
+        <v>100</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-143.54</v>
+        <v>-278.45</v>
       </c>
       <c r="K61" t="n">
-        <v>-171.49</v>
+        <v>30.49</v>
       </c>
       <c r="L61" t="n">
-        <v>223.64</v>
+        <v>280.11</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:52:53</t>
+          <t>06:55:30</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>7.03</v>
+        <v>6.39</v>
       </c>
       <c r="F62" t="n">
-        <v>16.12</v>
+        <v>16.39</v>
       </c>
       <c r="G62" t="n">
-        <v>338.1</v>
+        <v>321.7</v>
       </c>
       <c r="H62" t="n">
-        <v>96</v>
+        <v>95.8</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>-14.26</v>
+        <v>656.9299999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>89.06</v>
+        <v>-137.82</v>
       </c>
       <c r="L62" t="n">
-        <v>90.2</v>
+        <v>671.23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:54:05</t>
+          <t>06:56:55</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>6.92</v>
+        <v>6.33</v>
       </c>
       <c r="F63" t="n">
-        <v>16.48</v>
+        <v>16.28</v>
       </c>
       <c r="G63" t="n">
-        <v>331.3</v>
+        <v>329.8</v>
       </c>
       <c r="H63" t="n">
-        <v>98.90000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="I63" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>394.3</v>
+        <v>-180.01</v>
       </c>
       <c r="K63" t="n">
-        <v>180.55</v>
+        <v>-393.2</v>
       </c>
       <c r="L63" t="n">
-        <v>433.67</v>
+        <v>432.45</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06:54:59</t>
+          <t>06:57:53</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>6.68</v>
+        <v>6.54</v>
       </c>
       <c r="F64" t="n">
-        <v>16.75</v>
+        <v>16.04</v>
       </c>
       <c r="G64" t="n">
-        <v>332</v>
+        <v>325.9</v>
       </c>
       <c r="H64" t="n">
-        <v>97.8</v>
+        <v>100</v>
       </c>
       <c r="I64" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-80.23999999999999</v>
+        <v>-276.83</v>
       </c>
       <c r="K64" t="n">
-        <v>234.41</v>
+        <v>83.7</v>
       </c>
       <c r="L64" t="n">
-        <v>247.77</v>
+        <v>289.21</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:01:04</t>
+          <t>07:03:19</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.7</v>
+        <v>5.95</v>
       </c>
       <c r="F65" t="n">
-        <v>15.46</v>
+        <v>15.71</v>
       </c>
       <c r="G65" t="n">
-        <v>312.6</v>
+        <v>317.5</v>
       </c>
       <c r="H65" t="n">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>4.09</v>
+        <v>-454.34</v>
       </c>
       <c r="K65" t="n">
-        <v>212.8</v>
+        <v>-448.43</v>
       </c>
       <c r="L65" t="n">
-        <v>212.84</v>
+        <v>638.36</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:03:04</t>
+          <t>07:04:41</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>6.87</v>
+        <v>6.53</v>
       </c>
       <c r="F66" t="n">
-        <v>16.25</v>
+        <v>15.87</v>
       </c>
       <c r="G66" t="n">
-        <v>324.2</v>
+        <v>333</v>
       </c>
       <c r="H66" t="n">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="I66" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J66" t="n">
-        <v>-79.16</v>
+        <v>-377.22</v>
       </c>
       <c r="K66" t="n">
-        <v>188.96</v>
+        <v>186.19</v>
       </c>
       <c r="L66" t="n">
-        <v>204.87</v>
+        <v>420.67</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:04:02</t>
+          <t>07:07:08</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>7.44</v>
+        <v>6.72</v>
       </c>
       <c r="F67" t="n">
-        <v>16.32</v>
+        <v>15.79</v>
       </c>
       <c r="G67" t="n">
-        <v>327.7</v>
+        <v>317.6</v>
       </c>
       <c r="H67" t="n">
         <v>100</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>461.47</v>
+        <v>-429.46</v>
       </c>
       <c r="K67" t="n">
-        <v>-381.76</v>
+        <v>63.31</v>
       </c>
       <c r="L67" t="n">
-        <v>598.91</v>
+        <v>434.1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:07:54</t>
+          <t>07:09:54</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>6.71</v>
+        <v>6.8</v>
       </c>
       <c r="F68" t="n">
-        <v>15.78</v>
+        <v>15.51</v>
       </c>
       <c r="G68" t="n">
-        <v>327.6</v>
+        <v>333.3</v>
       </c>
       <c r="H68" t="n">
         <v>100</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-346.17</v>
+        <v>269.51</v>
       </c>
       <c r="K68" t="n">
-        <v>-411.48</v>
+        <v>848.16</v>
       </c>
       <c r="L68" t="n">
-        <v>537.72</v>
+        <v>889.95</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:08:51</t>
+          <t>07:12:03</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>7.32</v>
+        <v>6.61</v>
       </c>
       <c r="F69" t="n">
-        <v>15.87</v>
+        <v>15.27</v>
       </c>
       <c r="G69" t="n">
-        <v>313.8</v>
+        <v>316.6</v>
       </c>
       <c r="H69" t="n">
         <v>100</v>
       </c>
       <c r="I69" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>394.13</v>
+        <v>-1004.97</v>
       </c>
       <c r="K69" t="n">
-        <v>619.1</v>
+        <v>5.4</v>
       </c>
       <c r="L69" t="n">
-        <v>733.91</v>
+        <v>1004.98</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:10:37</t>
+          <t>07:14:09</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>5.8</v>
+        <v>7.15</v>
       </c>
       <c r="F70" t="n">
-        <v>15.13</v>
+        <v>16.72</v>
       </c>
       <c r="G70" t="n">
-        <v>336.4</v>
+        <v>319.4</v>
       </c>
       <c r="H70" t="n">
-        <v>100</v>
+        <v>95.7</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>706.52</v>
+        <v>-604.87</v>
       </c>
       <c r="K70" t="n">
-        <v>-77.34</v>
+        <v>518.85</v>
       </c>
       <c r="L70" t="n">
-        <v>710.75</v>
+        <v>796.91</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:14:43</t>
+          <t>07:17:32</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>6.93</v>
+        <v>6.87</v>
       </c>
       <c r="F71" t="n">
-        <v>16.36</v>
+        <v>16.08</v>
       </c>
       <c r="G71" t="n">
-        <v>333.8</v>
+        <v>314.9</v>
       </c>
       <c r="H71" t="n">
         <v>100</v>
       </c>
       <c r="I71" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-671.63</v>
+        <v>607.51</v>
       </c>
       <c r="K71" t="n">
-        <v>-383.42</v>
+        <v>747.46</v>
       </c>
       <c r="L71" t="n">
-        <v>773.37</v>
+        <v>963.21</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:16:05</t>
+          <t>07:19:40</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>7.16</v>
+        <v>6.22</v>
       </c>
       <c r="F72" t="n">
-        <v>16.18</v>
+        <v>16.08</v>
       </c>
       <c r="G72" t="n">
-        <v>337.1</v>
+        <v>317</v>
       </c>
       <c r="H72" t="n">
-        <v>100</v>
+        <v>98.7</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-563.63</v>
+        <v>-526.25</v>
       </c>
       <c r="K72" t="n">
-        <v>278.49</v>
+        <v>-53.27</v>
       </c>
       <c r="L72" t="n">
-        <v>628.6799999999999</v>
+        <v>528.9400000000001</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:17:39</t>
+          <t>07:21:51</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>7.43</v>
+        <v>7.71</v>
       </c>
       <c r="F73" t="n">
-        <v>16.03</v>
+        <v>16.1</v>
       </c>
       <c r="G73" t="n">
-        <v>343.5</v>
+        <v>333.8</v>
       </c>
       <c r="H73" t="n">
-        <v>95.7</v>
+        <v>91</v>
       </c>
       <c r="I73" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>869.77</v>
+        <v>-1074.53</v>
       </c>
       <c r="K73" t="n">
-        <v>-158.77</v>
+        <v>5.47</v>
       </c>
       <c r="L73" t="n">
-        <v>884.15</v>
+        <v>1074.55</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:29:37</t>
+          <t>07:31:35</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>6.64</v>
+        <v>6.09</v>
       </c>
       <c r="F74" t="n">
-        <v>16.18</v>
+        <v>15.72</v>
       </c>
       <c r="G74" t="n">
-        <v>335.6</v>
+        <v>334</v>
       </c>
       <c r="H74" t="n">
-        <v>98.8</v>
+        <v>98.2</v>
       </c>
       <c r="I74" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>-163.83</v>
+        <v>228.51</v>
       </c>
       <c r="K74" t="n">
-        <v>-156.49</v>
+        <v>-392.1</v>
       </c>
       <c r="L74" t="n">
-        <v>226.56</v>
+        <v>453.83</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:30:34</t>
+          <t>07:32:59</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>6.92</v>
+        <v>6.9</v>
       </c>
       <c r="F75" t="n">
-        <v>16.27</v>
+        <v>16.61</v>
       </c>
       <c r="G75" t="n">
-        <v>332.5</v>
+        <v>320.9</v>
       </c>
       <c r="H75" t="n">
-        <v>95.40000000000001</v>
+        <v>98</v>
       </c>
       <c r="I75" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>24.05</v>
+        <v>-303.63</v>
       </c>
       <c r="K75" t="n">
-        <v>203.11</v>
+        <v>15.79</v>
       </c>
       <c r="L75" t="n">
-        <v>204.53</v>
+        <v>304.04</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:32:12</t>
+          <t>07:34:22</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>6.7</v>
+        <v>6.41</v>
       </c>
       <c r="F76" t="n">
-        <v>15.68</v>
+        <v>16.18</v>
       </c>
       <c r="G76" t="n">
-        <v>326.9</v>
+        <v>338.8</v>
       </c>
       <c r="H76" t="n">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>-164.96</v>
+        <v>267.59</v>
       </c>
       <c r="K76" t="n">
-        <v>273.29</v>
+        <v>-148.01</v>
       </c>
       <c r="L76" t="n">
-        <v>319.22</v>
+        <v>305.79</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:38:16</t>
+          <t>07:40:07</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>7</v>
+        <v>6.66</v>
       </c>
       <c r="F77" t="n">
-        <v>15.52</v>
+        <v>15.99</v>
       </c>
       <c r="G77" t="n">
-        <v>320.5</v>
+        <v>317.1</v>
       </c>
       <c r="H77" t="n">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="I77" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>277.09</v>
+        <v>-11.24</v>
       </c>
       <c r="K77" t="n">
-        <v>54.19</v>
+        <v>-155.09</v>
       </c>
       <c r="L77" t="n">
-        <v>282.34</v>
+        <v>155.49</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:40:26</t>
+          <t>07:42:15</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>6.37</v>
+        <v>6.46</v>
       </c>
       <c r="F78" t="n">
-        <v>15.7</v>
+        <v>16.17</v>
       </c>
       <c r="G78" t="n">
-        <v>332.1</v>
+        <v>335</v>
       </c>
       <c r="H78" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-71.02</v>
+        <v>39.24</v>
       </c>
       <c r="K78" t="n">
-        <v>3.33</v>
+        <v>-218.64</v>
       </c>
       <c r="L78" t="n">
-        <v>71.09999999999999</v>
+        <v>222.14</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:42:19</t>
+          <t>07:43:07</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>6.21</v>
+        <v>6.75</v>
       </c>
       <c r="F79" t="n">
-        <v>16.04</v>
+        <v>16.51</v>
       </c>
       <c r="G79" t="n">
-        <v>312.1</v>
+        <v>321.3</v>
       </c>
       <c r="H79" t="n">
-        <v>99.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-79.09</v>
+        <v>-303.68</v>
       </c>
       <c r="K79" t="n">
-        <v>130.4</v>
+        <v>-43.1</v>
       </c>
       <c r="L79" t="n">
-        <v>152.51</v>
+        <v>306.73</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:48:45</t>
+          <t>07:47:23</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>6.97</v>
+        <v>7.47</v>
       </c>
       <c r="F80" t="n">
-        <v>15.82</v>
+        <v>15.51</v>
       </c>
       <c r="G80" t="n">
-        <v>330.4</v>
+        <v>319.8</v>
       </c>
       <c r="H80" t="n">
-        <v>95.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>131.63</v>
+        <v>-17.81</v>
       </c>
       <c r="K80" t="n">
-        <v>204.54</v>
+        <v>-425.69</v>
       </c>
       <c r="L80" t="n">
-        <v>243.23</v>
+        <v>426.06</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:50:58</t>
+          <t>07:48:02</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>6.85</v>
+        <v>6.64</v>
       </c>
       <c r="F81" t="n">
-        <v>15.83</v>
+        <v>16.67</v>
       </c>
       <c r="G81" t="n">
-        <v>322.7</v>
+        <v>315</v>
       </c>
       <c r="H81" t="n">
         <v>100</v>
       </c>
       <c r="I81" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>279.99</v>
+        <v>-16.18</v>
       </c>
       <c r="K81" t="n">
-        <v>-391.67</v>
+        <v>492.58</v>
       </c>
       <c r="L81" t="n">
-        <v>481.45</v>
+        <v>492.85</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:51:45</t>
+          <t>07:49:54</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>6.63</v>
+        <v>7.22</v>
       </c>
       <c r="F82" t="n">
-        <v>15.95</v>
+        <v>15.47</v>
       </c>
       <c r="G82" t="n">
-        <v>332.3</v>
+        <v>326.5</v>
       </c>
       <c r="H82" t="n">
-        <v>99.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-198.48</v>
+        <v>540.91</v>
       </c>
       <c r="K82" t="n">
-        <v>-31.92</v>
+        <v>55.53</v>
       </c>
       <c r="L82" t="n">
-        <v>201.03</v>
+        <v>543.76</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07:57:03</t>
+          <t>07:54:14</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>6.87</v>
+        <v>7.76</v>
       </c>
       <c r="F83" t="n">
-        <v>15.8</v>
+        <v>16</v>
       </c>
       <c r="G83" t="n">
-        <v>339.2</v>
+        <v>333.3</v>
       </c>
       <c r="H83" t="n">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-243.46</v>
+        <v>-384.71</v>
       </c>
       <c r="K83" t="n">
-        <v>449.63</v>
+        <v>1284.53</v>
       </c>
       <c r="L83" t="n">
-        <v>511.31</v>
+        <v>1340.9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07:58:22</t>
+          <t>07:56:07</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>7.26</v>
+        <v>6.91</v>
       </c>
       <c r="F84" t="n">
-        <v>15.46</v>
+        <v>16.02</v>
       </c>
       <c r="G84" t="n">
-        <v>327.4</v>
+        <v>325.8</v>
       </c>
       <c r="H84" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I84" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>399.18</v>
+        <v>-148.09</v>
       </c>
       <c r="K84" t="n">
-        <v>302.15</v>
+        <v>-461.78</v>
       </c>
       <c r="L84" t="n">
-        <v>500.64</v>
+        <v>484.94</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:00:59</t>
+          <t>07:57:28</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>8.050000000000001</v>
+        <v>7.55</v>
       </c>
       <c r="F85" t="n">
-        <v>15.78</v>
+        <v>15.9</v>
       </c>
       <c r="G85" t="n">
-        <v>341.8</v>
+        <v>337.7</v>
       </c>
       <c r="H85" t="n">
-        <v>96.3</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-48.92</v>
+        <v>232.02</v>
       </c>
       <c r="K85" t="n">
-        <v>4.95</v>
+        <v>1212.64</v>
       </c>
       <c r="L85" t="n">
-        <v>49.17</v>
+        <v>1234.63</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:04:42</t>
+          <t>08:01:42</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>7.1</v>
+        <v>6.92</v>
       </c>
       <c r="F86" t="n">
-        <v>16.42</v>
+        <v>16.32</v>
       </c>
       <c r="G86" t="n">
-        <v>336.5</v>
+        <v>321.1</v>
       </c>
       <c r="H86" t="n">
-        <v>99.59999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-137.75</v>
+        <v>526.73</v>
       </c>
       <c r="K86" t="n">
-        <v>266.51</v>
+        <v>-23.73</v>
       </c>
       <c r="L86" t="n">
-        <v>300</v>
+        <v>527.26</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:06:16</t>
+          <t>08:02:47</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>7.47</v>
+        <v>6.02</v>
       </c>
       <c r="F87" t="n">
-        <v>16.27</v>
+        <v>15.08</v>
       </c>
       <c r="G87" t="n">
-        <v>321.7</v>
+        <v>331.3</v>
       </c>
       <c r="H87" t="n">
-        <v>86.2</v>
+        <v>99.7</v>
       </c>
       <c r="I87" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-36.86</v>
+        <v>-608.65</v>
       </c>
       <c r="K87" t="n">
-        <v>-690.63</v>
+        <v>-22.53</v>
       </c>
       <c r="L87" t="n">
-        <v>691.62</v>
+        <v>609.0599999999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:07:20</t>
+          <t>08:04:03</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>6.56</v>
+        <v>7.61</v>
       </c>
       <c r="F88" t="n">
-        <v>16.03</v>
+        <v>16.71</v>
       </c>
       <c r="G88" t="n">
-        <v>312.7</v>
+        <v>328</v>
       </c>
       <c r="H88" t="n">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>944.8099999999999</v>
+        <v>-859.4</v>
       </c>
       <c r="K88" t="n">
-        <v>-217.06</v>
+        <v>-233.66</v>
       </c>
       <c r="L88" t="n">
-        <v>969.42</v>
+        <v>890.6</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-01.xlsx
+++ b/output/2025-07-01.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>257.62</v>
+        <v>299.11</v>
       </c>
       <c r="K14" t="n">
-        <v>272.97</v>
+        <v>316.94</v>
       </c>
       <c r="L14" t="n">
-        <v>375.34</v>
+        <v>435.8</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>463.91</v>
+        <v>530.3099999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>162.9</v>
+        <v>186.22</v>
       </c>
       <c r="L15" t="n">
-        <v>491.67</v>
+        <v>562.05</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-462.25</v>
+        <v>-544.08</v>
       </c>
       <c r="K16" t="n">
-        <v>406.45</v>
+        <v>478.4</v>
       </c>
       <c r="L16" t="n">
-        <v>615.53</v>
+        <v>724.5</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>125.61</v>
+        <v>185.66</v>
       </c>
       <c r="K17" t="n">
-        <v>192.67</v>
+        <v>284.79</v>
       </c>
       <c r="L17" t="n">
-        <v>230</v>
+        <v>339.96</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>248.57</v>
+        <v>368.8</v>
       </c>
       <c r="K18" t="n">
-        <v>-216.68</v>
+        <v>-321.48</v>
       </c>
       <c r="L18" t="n">
-        <v>329.75</v>
+        <v>489.25</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>3.01</v>
+        <v>6.11</v>
       </c>
       <c r="K19" t="n">
-        <v>203.76</v>
+        <v>413.03</v>
       </c>
       <c r="L19" t="n">
-        <v>203.78</v>
+        <v>413.08</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-295.18</v>
+        <v>-391.76</v>
       </c>
       <c r="K20" t="n">
-        <v>524.0700000000001</v>
+        <v>695.53</v>
       </c>
       <c r="L20" t="n">
-        <v>601.49</v>
+        <v>798.27</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>308.17</v>
+        <v>458.05</v>
       </c>
       <c r="K21" t="n">
-        <v>-203.43</v>
+        <v>-302.37</v>
       </c>
       <c r="L21" t="n">
-        <v>369.26</v>
+        <v>548.85</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-462.39</v>
+        <v>-623.64</v>
       </c>
       <c r="K22" t="n">
-        <v>285.06</v>
+        <v>384.47</v>
       </c>
       <c r="L22" t="n">
-        <v>543.2</v>
+        <v>732.63</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>1133.79</v>
+        <v>1449.56</v>
       </c>
       <c r="K23" t="n">
-        <v>241.24</v>
+        <v>308.43</v>
       </c>
       <c r="L23" t="n">
-        <v>1159.17</v>
+        <v>1482.01</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-115.35</v>
+        <v>-185.17</v>
       </c>
       <c r="K24" t="n">
-        <v>680.6</v>
+        <v>1092.57</v>
       </c>
       <c r="L24" t="n">
-        <v>690.3099999999999</v>
+        <v>1108.15</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>261.86</v>
+        <v>481.1</v>
       </c>
       <c r="K25" t="n">
-        <v>275.69</v>
+        <v>506.5</v>
       </c>
       <c r="L25" t="n">
-        <v>380.23</v>
+        <v>698.5700000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>876.78</v>
+        <v>1525.66</v>
       </c>
       <c r="K26" t="n">
-        <v>387.2</v>
+        <v>673.76</v>
       </c>
       <c r="L26" t="n">
-        <v>958.47</v>
+        <v>1667.81</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-205.79</v>
+        <v>-385.96</v>
       </c>
       <c r="K27" t="n">
-        <v>-491.24</v>
+        <v>-921.36</v>
       </c>
       <c r="L27" t="n">
-        <v>532.6</v>
+        <v>998.9299999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>671.85</v>
+        <v>1011.1</v>
       </c>
       <c r="K28" t="n">
-        <v>936.11</v>
+        <v>1408.79</v>
       </c>
       <c r="L28" t="n">
-        <v>1152.25</v>
+        <v>1734.08</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>-89.63</v>
+        <v>-131.19</v>
       </c>
       <c r="K29" t="n">
-        <v>249.71</v>
+        <v>365.48</v>
       </c>
       <c r="L29" t="n">
-        <v>265.31</v>
+        <v>388.32</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>87.81999999999999</v>
+        <v>124.98</v>
       </c>
       <c r="K30" t="n">
-        <v>312.44</v>
+        <v>444.69</v>
       </c>
       <c r="L30" t="n">
-        <v>324.55</v>
+        <v>461.92</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-103.03</v>
+        <v>-155.42</v>
       </c>
       <c r="K31" t="n">
-        <v>187.36</v>
+        <v>282.65</v>
       </c>
       <c r="L31" t="n">
-        <v>213.82</v>
+        <v>322.56</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>-301.07</v>
+        <v>-478.45</v>
       </c>
       <c r="K32" t="n">
-        <v>-65.31999999999999</v>
+        <v>-103.81</v>
       </c>
       <c r="L32" t="n">
-        <v>308.07</v>
+        <v>489.58</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-31.26</v>
+        <v>-40.17</v>
       </c>
       <c r="K33" t="n">
-        <v>-502.96</v>
+        <v>-646.29</v>
       </c>
       <c r="L33" t="n">
-        <v>503.93</v>
+        <v>647.54</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-212.5</v>
+        <v>-401.63</v>
       </c>
       <c r="K34" t="n">
-        <v>44.68</v>
+        <v>84.44</v>
       </c>
       <c r="L34" t="n">
-        <v>217.15</v>
+        <v>410.41</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-67.19</v>
+        <v>-124.15</v>
       </c>
       <c r="K35" t="n">
-        <v>-354.86</v>
+        <v>-655.73</v>
       </c>
       <c r="L35" t="n">
-        <v>361.16</v>
+        <v>667.38</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-154.91</v>
+        <v>-227.99</v>
       </c>
       <c r="K36" t="n">
-        <v>-395.93</v>
+        <v>-582.71</v>
       </c>
       <c r="L36" t="n">
-        <v>425.15</v>
+        <v>625.72</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-128.46</v>
+        <v>-162.67</v>
       </c>
       <c r="K37" t="n">
-        <v>1008.09</v>
+        <v>1276.58</v>
       </c>
       <c r="L37" t="n">
-        <v>1016.24</v>
+        <v>1286.91</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-411.49</v>
+        <v>-602.47</v>
       </c>
       <c r="K38" t="n">
-        <v>1082.88</v>
+        <v>1585.46</v>
       </c>
       <c r="L38" t="n">
-        <v>1158.43</v>
+        <v>1696.07</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>345.26</v>
+        <v>651.95</v>
       </c>
       <c r="K39" t="n">
-        <v>-222.71</v>
+        <v>-420.55</v>
       </c>
       <c r="L39" t="n">
-        <v>410.85</v>
+        <v>775.8200000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>403.96</v>
+        <v>691.35</v>
       </c>
       <c r="K40" t="n">
-        <v>337.24</v>
+        <v>577.15</v>
       </c>
       <c r="L40" t="n">
-        <v>526.23</v>
+        <v>900.6</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-93.55</v>
+        <v>-225.85</v>
       </c>
       <c r="K41" t="n">
-        <v>-464.83</v>
+        <v>-1122.19</v>
       </c>
       <c r="L41" t="n">
-        <v>474.15</v>
+        <v>1144.69</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>17.21</v>
+        <v>24.45</v>
       </c>
       <c r="K42" t="n">
-        <v>1109.17</v>
+        <v>1576.37</v>
       </c>
       <c r="L42" t="n">
-        <v>1109.3</v>
+        <v>1576.56</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-134.53</v>
+        <v>-227.21</v>
       </c>
       <c r="K43" t="n">
-        <v>-739.05</v>
+        <v>-1248.24</v>
       </c>
       <c r="L43" t="n">
-        <v>751.2</v>
+        <v>1268.75</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>67.54000000000001</v>
+        <v>153.24</v>
       </c>
       <c r="K44" t="n">
-        <v>-87.76000000000001</v>
+        <v>-199.11</v>
       </c>
       <c r="L44" t="n">
-        <v>110.74</v>
+        <v>251.25</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>294.21</v>
+        <v>363.05</v>
       </c>
       <c r="K45" t="n">
-        <v>-632.1799999999999</v>
+        <v>-780.1</v>
       </c>
       <c r="L45" t="n">
-        <v>697.29</v>
+        <v>860.4400000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-453.64</v>
+        <v>-590.83</v>
       </c>
       <c r="K46" t="n">
-        <v>122.46</v>
+        <v>159.49</v>
       </c>
       <c r="L46" t="n">
-        <v>469.88</v>
+        <v>611.98</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-256.31</v>
+        <v>-341</v>
       </c>
       <c r="K47" t="n">
-        <v>427.28</v>
+        <v>568.46</v>
       </c>
       <c r="L47" t="n">
-        <v>498.26</v>
+        <v>662.9</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>381.58</v>
+        <v>475.27</v>
       </c>
       <c r="K48" t="n">
-        <v>352.6</v>
+        <v>439.17</v>
       </c>
       <c r="L48" t="n">
-        <v>519.55</v>
+        <v>647.11</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>47.48</v>
+        <v>67.23</v>
       </c>
       <c r="K49" t="n">
-        <v>-383.12</v>
+        <v>-542.5</v>
       </c>
       <c r="L49" t="n">
-        <v>386.05</v>
+        <v>546.65</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>71.06999999999999</v>
+        <v>141.21</v>
       </c>
       <c r="K50" t="n">
-        <v>267.41</v>
+        <v>531.35</v>
       </c>
       <c r="L50" t="n">
-        <v>276.69</v>
+        <v>549.8</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-137.73</v>
+        <v>-368.96</v>
       </c>
       <c r="K51" t="n">
-        <v>-32.52</v>
+        <v>-87.13</v>
       </c>
       <c r="L51" t="n">
-        <v>141.52</v>
+        <v>379.11</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>-222</v>
+        <v>-300.9</v>
       </c>
       <c r="K52" t="n">
-        <v>646.33</v>
+        <v>876.03</v>
       </c>
       <c r="L52" t="n">
-        <v>683.4</v>
+        <v>926.27</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>77.88</v>
+        <v>172.76</v>
       </c>
       <c r="K53" t="n">
-        <v>-387.81</v>
+        <v>-860.3200000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>395.55</v>
+        <v>877.5</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>764.59</v>
+        <v>1150.55</v>
       </c>
       <c r="K54" t="n">
-        <v>164.56</v>
+        <v>247.63</v>
       </c>
       <c r="L54" t="n">
-        <v>782.1</v>
+        <v>1176.89</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-431.68</v>
+        <v>-750.75</v>
       </c>
       <c r="K55" t="n">
-        <v>-243.66</v>
+        <v>-423.76</v>
       </c>
       <c r="L55" t="n">
-        <v>495.7</v>
+        <v>862.08</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>945.3200000000001</v>
+        <v>1400.34</v>
       </c>
       <c r="K56" t="n">
-        <v>77.79000000000001</v>
+        <v>115.23</v>
       </c>
       <c r="L56" t="n">
-        <v>948.52</v>
+        <v>1405.07</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>17</v>
       </c>
       <c r="J57" t="n">
-        <v>-381.25</v>
+        <v>-1025.98</v>
       </c>
       <c r="K57" t="n">
-        <v>-109.84</v>
+        <v>-295.59</v>
       </c>
       <c r="L57" t="n">
-        <v>396.75</v>
+        <v>1067.71</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>126.16</v>
+        <v>207.32</v>
       </c>
       <c r="K58" t="n">
-        <v>1180.69</v>
+        <v>1940.32</v>
       </c>
       <c r="L58" t="n">
-        <v>1187.41</v>
+        <v>1951.37</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-176.71</v>
+        <v>-257.19</v>
       </c>
       <c r="K59" t="n">
-        <v>219.03</v>
+        <v>318.78</v>
       </c>
       <c r="L59" t="n">
-        <v>281.42</v>
+        <v>409.59</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-453.51</v>
+        <v>-572.9</v>
       </c>
       <c r="K60" t="n">
-        <v>368.49</v>
+        <v>465.5</v>
       </c>
       <c r="L60" t="n">
-        <v>584.34</v>
+        <v>738.1799999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-278.45</v>
+        <v>-375.5</v>
       </c>
       <c r="K61" t="n">
-        <v>30.49</v>
+        <v>41.12</v>
       </c>
       <c r="L61" t="n">
-        <v>280.11</v>
+        <v>377.75</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>656.9299999999999</v>
+        <v>811.12</v>
       </c>
       <c r="K62" t="n">
-        <v>-137.82</v>
+        <v>-170.16</v>
       </c>
       <c r="L62" t="n">
-        <v>671.23</v>
+        <v>828.77</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-180.01</v>
+        <v>-233.54</v>
       </c>
       <c r="K63" t="n">
-        <v>-393.2</v>
+        <v>-510.12</v>
       </c>
       <c r="L63" t="n">
-        <v>432.45</v>
+        <v>561.04</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-276.83</v>
+        <v>-399.54</v>
       </c>
       <c r="K64" t="n">
-        <v>83.7</v>
+        <v>120.8</v>
       </c>
       <c r="L64" t="n">
-        <v>289.21</v>
+        <v>417.4</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-454.34</v>
+        <v>-563.88</v>
       </c>
       <c r="K65" t="n">
-        <v>-448.43</v>
+        <v>-556.54</v>
       </c>
       <c r="L65" t="n">
-        <v>638.36</v>
+        <v>792.28</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>18</v>
       </c>
       <c r="J66" t="n">
-        <v>-377.22</v>
+        <v>-628.54</v>
       </c>
       <c r="K66" t="n">
-        <v>186.19</v>
+        <v>310.24</v>
       </c>
       <c r="L66" t="n">
-        <v>420.67</v>
+        <v>700.9400000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-429.46</v>
+        <v>-735.64</v>
       </c>
       <c r="K67" t="n">
-        <v>63.31</v>
+        <v>108.45</v>
       </c>
       <c r="L67" t="n">
-        <v>434.1</v>
+        <v>743.59</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>269.51</v>
+        <v>392.37</v>
       </c>
       <c r="K68" t="n">
-        <v>848.16</v>
+        <v>1234.79</v>
       </c>
       <c r="L68" t="n">
-        <v>889.95</v>
+        <v>1295.63</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-1004.97</v>
+        <v>-1355.01</v>
       </c>
       <c r="K69" t="n">
-        <v>5.4</v>
+        <v>7.29</v>
       </c>
       <c r="L69" t="n">
-        <v>1004.98</v>
+        <v>1355.03</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-604.87</v>
+        <v>-1037.9</v>
       </c>
       <c r="K70" t="n">
-        <v>518.85</v>
+        <v>890.29</v>
       </c>
       <c r="L70" t="n">
-        <v>796.91</v>
+        <v>1367.43</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>607.51</v>
+        <v>967.04</v>
       </c>
       <c r="K71" t="n">
-        <v>747.46</v>
+        <v>1189.82</v>
       </c>
       <c r="L71" t="n">
-        <v>963.21</v>
+        <v>1533.25</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-526.25</v>
+        <v>-1192.2</v>
       </c>
       <c r="K72" t="n">
-        <v>-53.27</v>
+        <v>-120.68</v>
       </c>
       <c r="L72" t="n">
-        <v>528.9400000000001</v>
+        <v>1198.29</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>-1074.53</v>
+        <v>-1999.9</v>
       </c>
       <c r="K73" t="n">
-        <v>5.47</v>
+        <v>10.19</v>
       </c>
       <c r="L73" t="n">
-        <v>1074.55</v>
+        <v>1999.93</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>228.51</v>
+        <v>263.99</v>
       </c>
       <c r="K74" t="n">
-        <v>-392.1</v>
+        <v>-452.99</v>
       </c>
       <c r="L74" t="n">
-        <v>453.83</v>
+        <v>524.3</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-303.63</v>
+        <v>-412.43</v>
       </c>
       <c r="K75" t="n">
-        <v>15.79</v>
+        <v>21.44</v>
       </c>
       <c r="L75" t="n">
-        <v>304.04</v>
+        <v>412.99</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>267.59</v>
+        <v>348.29</v>
       </c>
       <c r="K76" t="n">
-        <v>-148.01</v>
+        <v>-192.64</v>
       </c>
       <c r="L76" t="n">
-        <v>305.79</v>
+        <v>398.02</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-11.24</v>
+        <v>-26.42</v>
       </c>
       <c r="K77" t="n">
-        <v>-155.09</v>
+        <v>-364.64</v>
       </c>
       <c r="L77" t="n">
-        <v>155.49</v>
+        <v>365.6</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>39.24</v>
+        <v>74.38</v>
       </c>
       <c r="K78" t="n">
-        <v>-218.64</v>
+        <v>-414.43</v>
       </c>
       <c r="L78" t="n">
-        <v>222.14</v>
+        <v>421.05</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-303.68</v>
+        <v>-446.3</v>
       </c>
       <c r="K79" t="n">
-        <v>-43.1</v>
+        <v>-63.35</v>
       </c>
       <c r="L79" t="n">
-        <v>306.73</v>
+        <v>450.78</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-17.81</v>
+        <v>-28.14</v>
       </c>
       <c r="K80" t="n">
-        <v>-425.69</v>
+        <v>-672.6900000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>426.06</v>
+        <v>673.28</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-16.18</v>
+        <v>-26.07</v>
       </c>
       <c r="K81" t="n">
-        <v>492.58</v>
+        <v>793.3</v>
       </c>
       <c r="L81" t="n">
-        <v>492.85</v>
+        <v>793.73</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>540.91</v>
+        <v>768.13</v>
       </c>
       <c r="K82" t="n">
-        <v>55.53</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>543.76</v>
+        <v>772.16</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-384.71</v>
+        <v>-543.33</v>
       </c>
       <c r="K83" t="n">
-        <v>1284.53</v>
+        <v>1814.13</v>
       </c>
       <c r="L83" t="n">
-        <v>1340.9</v>
+        <v>1893.74</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-148.09</v>
+        <v>-296.32</v>
       </c>
       <c r="K84" t="n">
-        <v>-461.78</v>
+        <v>-923.98</v>
       </c>
       <c r="L84" t="n">
-        <v>484.94</v>
+        <v>970.33</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>232.02</v>
+        <v>313.82</v>
       </c>
       <c r="K85" t="n">
-        <v>1212.64</v>
+        <v>1640.16</v>
       </c>
       <c r="L85" t="n">
-        <v>1234.63</v>
+        <v>1669.92</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>526.73</v>
+        <v>1106.88</v>
       </c>
       <c r="K86" t="n">
-        <v>-23.73</v>
+        <v>-49.86</v>
       </c>
       <c r="L86" t="n">
-        <v>527.26</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-608.65</v>
+        <v>-1251.9</v>
       </c>
       <c r="K87" t="n">
-        <v>-22.53</v>
+        <v>-46.33</v>
       </c>
       <c r="L87" t="n">
-        <v>609.0599999999999</v>
+        <v>1252.75</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>-859.4</v>
+        <v>-1569.95</v>
       </c>
       <c r="K88" t="n">
-        <v>-233.66</v>
+        <v>-426.85</v>
       </c>
       <c r="L88" t="n">
-        <v>890.6</v>
+        <v>1626.94</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-01.xlsx
+++ b/output/2025-07-01.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>299.11</v>
+        <v>201.24</v>
       </c>
       <c r="K14" t="n">
-        <v>316.94</v>
+        <v>213.24</v>
       </c>
       <c r="L14" t="n">
-        <v>435.8</v>
+        <v>293.2</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>530.3099999999999</v>
+        <v>352.11</v>
       </c>
       <c r="K15" t="n">
-        <v>186.22</v>
+        <v>123.64</v>
       </c>
       <c r="L15" t="n">
-        <v>562.05</v>
+        <v>373.18</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-544.08</v>
+        <v>-318.67</v>
       </c>
       <c r="K16" t="n">
-        <v>478.4</v>
+        <v>280.2</v>
       </c>
       <c r="L16" t="n">
-        <v>724.5</v>
+        <v>424.34</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>185.66</v>
+        <v>117.28</v>
       </c>
       <c r="K17" t="n">
-        <v>284.79</v>
+        <v>179.9</v>
       </c>
       <c r="L17" t="n">
-        <v>339.96</v>
+        <v>214.75</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>368.8</v>
+        <v>204.4</v>
       </c>
       <c r="K18" t="n">
-        <v>-321.48</v>
+        <v>-178.17</v>
       </c>
       <c r="L18" t="n">
-        <v>489.25</v>
+        <v>271.15</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>6.11</v>
+        <v>3.32</v>
       </c>
       <c r="K19" t="n">
-        <v>413.03</v>
+        <v>224.82</v>
       </c>
       <c r="L19" t="n">
-        <v>413.08</v>
+        <v>224.84</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-391.76</v>
+        <v>-199.87</v>
       </c>
       <c r="K20" t="n">
-        <v>695.53</v>
+        <v>354.86</v>
       </c>
       <c r="L20" t="n">
-        <v>798.27</v>
+        <v>407.27</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>458.05</v>
+        <v>251.36</v>
       </c>
       <c r="K21" t="n">
-        <v>-302.37</v>
+        <v>-165.93</v>
       </c>
       <c r="L21" t="n">
-        <v>548.85</v>
+        <v>301.19</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-623.64</v>
+        <v>-332.13</v>
       </c>
       <c r="K22" t="n">
-        <v>384.47</v>
+        <v>204.75</v>
       </c>
       <c r="L22" t="n">
-        <v>732.63</v>
+        <v>390.17</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>1449.56</v>
+        <v>702.1</v>
       </c>
       <c r="K23" t="n">
-        <v>308.43</v>
+        <v>149.39</v>
       </c>
       <c r="L23" t="n">
-        <v>1482.01</v>
+        <v>717.8099999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-185.17</v>
+        <v>-79.62</v>
       </c>
       <c r="K24" t="n">
-        <v>1092.57</v>
+        <v>469.77</v>
       </c>
       <c r="L24" t="n">
-        <v>1108.15</v>
+        <v>476.47</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>481.1</v>
+        <v>219.2</v>
       </c>
       <c r="K25" t="n">
-        <v>506.5</v>
+        <v>230.78</v>
       </c>
       <c r="L25" t="n">
-        <v>698.5700000000001</v>
+        <v>318.29</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>1525.66</v>
+        <v>599.64</v>
       </c>
       <c r="K26" t="n">
-        <v>673.76</v>
+        <v>264.81</v>
       </c>
       <c r="L26" t="n">
-        <v>1667.81</v>
+        <v>655.51</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-385.96</v>
+        <v>-166.12</v>
       </c>
       <c r="K27" t="n">
-        <v>-921.36</v>
+        <v>-396.55</v>
       </c>
       <c r="L27" t="n">
-        <v>998.9299999999999</v>
+        <v>429.93</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>1011.1</v>
+        <v>413.16</v>
       </c>
       <c r="K28" t="n">
-        <v>1408.79</v>
+        <v>575.66</v>
       </c>
       <c r="L28" t="n">
-        <v>1734.08</v>
+        <v>708.58</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>-131.19</v>
+        <v>-77.28</v>
       </c>
       <c r="K29" t="n">
-        <v>365.48</v>
+        <v>215.3</v>
       </c>
       <c r="L29" t="n">
-        <v>388.32</v>
+        <v>228.75</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>124.98</v>
+        <v>72.95999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>444.69</v>
+        <v>259.6</v>
       </c>
       <c r="L30" t="n">
-        <v>461.92</v>
+        <v>269.66</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-155.42</v>
+        <v>-98.37</v>
       </c>
       <c r="K31" t="n">
-        <v>282.65</v>
+        <v>178.89</v>
       </c>
       <c r="L31" t="n">
-        <v>322.56</v>
+        <v>204.16</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>-478.45</v>
+        <v>-267.41</v>
       </c>
       <c r="K32" t="n">
-        <v>-103.81</v>
+        <v>-58.02</v>
       </c>
       <c r="L32" t="n">
-        <v>489.58</v>
+        <v>273.63</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-40.17</v>
+        <v>-22.69</v>
       </c>
       <c r="K33" t="n">
-        <v>-646.29</v>
+        <v>-365</v>
       </c>
       <c r="L33" t="n">
-        <v>647.54</v>
+        <v>365.71</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-401.63</v>
+        <v>-228.26</v>
       </c>
       <c r="K34" t="n">
-        <v>84.44</v>
+        <v>47.99</v>
       </c>
       <c r="L34" t="n">
-        <v>410.41</v>
+        <v>233.25</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-124.15</v>
+        <v>-58.96</v>
       </c>
       <c r="K35" t="n">
-        <v>-655.73</v>
+        <v>-311.44</v>
       </c>
       <c r="L35" t="n">
-        <v>667.38</v>
+        <v>316.97</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-227.99</v>
+        <v>-118.64</v>
       </c>
       <c r="K36" t="n">
-        <v>-582.71</v>
+        <v>-303.21</v>
       </c>
       <c r="L36" t="n">
-        <v>625.72</v>
+        <v>325.6</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-162.67</v>
+        <v>-79.7</v>
       </c>
       <c r="K37" t="n">
-        <v>1276.58</v>
+        <v>625.5</v>
       </c>
       <c r="L37" t="n">
-        <v>1286.91</v>
+        <v>630.5599999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-602.47</v>
+        <v>-255.33</v>
       </c>
       <c r="K38" t="n">
-        <v>1585.46</v>
+        <v>671.9400000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>1696.07</v>
+        <v>718.8200000000001</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>651.95</v>
+        <v>305.56</v>
       </c>
       <c r="K39" t="n">
-        <v>-420.55</v>
+        <v>-197.11</v>
       </c>
       <c r="L39" t="n">
-        <v>775.8200000000001</v>
+        <v>363.62</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>691.35</v>
+        <v>331.13</v>
       </c>
       <c r="K40" t="n">
-        <v>577.15</v>
+        <v>276.43</v>
       </c>
       <c r="L40" t="n">
-        <v>900.6</v>
+        <v>431.35</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-225.85</v>
+        <v>-88.26000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>-1122.19</v>
+        <v>-438.55</v>
       </c>
       <c r="L41" t="n">
-        <v>1144.69</v>
+        <v>447.35</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>24.45</v>
+        <v>10.81</v>
       </c>
       <c r="K42" t="n">
-        <v>1576.37</v>
+        <v>696.76</v>
       </c>
       <c r="L42" t="n">
-        <v>1576.56</v>
+        <v>696.84</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-227.21</v>
+        <v>-101.76</v>
       </c>
       <c r="K43" t="n">
-        <v>-1248.24</v>
+        <v>-559.0700000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>1268.75</v>
+        <v>568.26</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>153.24</v>
+        <v>95.89</v>
       </c>
       <c r="K44" t="n">
-        <v>-199.11</v>
+        <v>-124.6</v>
       </c>
       <c r="L44" t="n">
-        <v>251.25</v>
+        <v>157.22</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>363.05</v>
+        <v>204.97</v>
       </c>
       <c r="K45" t="n">
-        <v>-780.1</v>
+        <v>-440.42</v>
       </c>
       <c r="L45" t="n">
-        <v>860.4400000000001</v>
+        <v>485.78</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-590.83</v>
+        <v>-343.03</v>
       </c>
       <c r="K46" t="n">
-        <v>159.49</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>611.98</v>
+        <v>355.3</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-341</v>
+        <v>-203.06</v>
       </c>
       <c r="K47" t="n">
-        <v>568.46</v>
+        <v>338.51</v>
       </c>
       <c r="L47" t="n">
-        <v>662.9</v>
+        <v>394.75</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>475.27</v>
+        <v>275.01</v>
       </c>
       <c r="K48" t="n">
-        <v>439.17</v>
+        <v>254.12</v>
       </c>
       <c r="L48" t="n">
-        <v>647.11</v>
+        <v>374.44</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>67.23</v>
+        <v>38.55</v>
       </c>
       <c r="K49" t="n">
-        <v>-542.5</v>
+        <v>-311.05</v>
       </c>
       <c r="L49" t="n">
-        <v>546.65</v>
+        <v>313.43</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>141.21</v>
+        <v>68.92</v>
       </c>
       <c r="K50" t="n">
-        <v>531.35</v>
+        <v>259.35</v>
       </c>
       <c r="L50" t="n">
-        <v>549.8</v>
+        <v>268.35</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-368.96</v>
+        <v>-194.02</v>
       </c>
       <c r="K51" t="n">
-        <v>-87.13</v>
+        <v>-45.82</v>
       </c>
       <c r="L51" t="n">
-        <v>379.11</v>
+        <v>199.36</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>-300.9</v>
+        <v>-154.13</v>
       </c>
       <c r="K52" t="n">
-        <v>876.03</v>
+        <v>448.72</v>
       </c>
       <c r="L52" t="n">
-        <v>926.27</v>
+        <v>474.45</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>172.76</v>
+        <v>79.67</v>
       </c>
       <c r="K53" t="n">
-        <v>-860.3200000000001</v>
+        <v>-396.74</v>
       </c>
       <c r="L53" t="n">
-        <v>877.5</v>
+        <v>404.66</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>1150.55</v>
+        <v>515.59</v>
       </c>
       <c r="K54" t="n">
-        <v>247.63</v>
+        <v>110.97</v>
       </c>
       <c r="L54" t="n">
-        <v>1176.89</v>
+        <v>527.4</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-750.75</v>
+        <v>-337.53</v>
       </c>
       <c r="K55" t="n">
-        <v>-423.76</v>
+        <v>-190.52</v>
       </c>
       <c r="L55" t="n">
-        <v>862.08</v>
+        <v>387.58</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>1400.34</v>
+        <v>619.21</v>
       </c>
       <c r="K56" t="n">
-        <v>115.23</v>
+        <v>50.95</v>
       </c>
       <c r="L56" t="n">
-        <v>1405.07</v>
+        <v>621.3099999999999</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>17</v>
       </c>
       <c r="J57" t="n">
-        <v>-1025.98</v>
+        <v>-400.18</v>
       </c>
       <c r="K57" t="n">
-        <v>-295.59</v>
+        <v>-115.3</v>
       </c>
       <c r="L57" t="n">
-        <v>1067.71</v>
+        <v>416.46</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>207.32</v>
+        <v>81.25</v>
       </c>
       <c r="K58" t="n">
-        <v>1940.32</v>
+        <v>760.39</v>
       </c>
       <c r="L58" t="n">
-        <v>1951.37</v>
+        <v>764.72</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-257.19</v>
+        <v>-151.54</v>
       </c>
       <c r="K59" t="n">
-        <v>318.78</v>
+        <v>187.83</v>
       </c>
       <c r="L59" t="n">
-        <v>409.59</v>
+        <v>241.34</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-572.9</v>
+        <v>-346.21</v>
       </c>
       <c r="K60" t="n">
-        <v>465.5</v>
+        <v>281.31</v>
       </c>
       <c r="L60" t="n">
-        <v>738.1799999999999</v>
+        <v>446.09</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-375.5</v>
+        <v>-244.3</v>
       </c>
       <c r="K61" t="n">
-        <v>41.12</v>
+        <v>26.75</v>
       </c>
       <c r="L61" t="n">
-        <v>377.75</v>
+        <v>245.76</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>811.12</v>
+        <v>454.84</v>
       </c>
       <c r="K62" t="n">
-        <v>-170.16</v>
+        <v>-95.42</v>
       </c>
       <c r="L62" t="n">
-        <v>828.77</v>
+        <v>464.74</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-233.54</v>
+        <v>-141.48</v>
       </c>
       <c r="K63" t="n">
-        <v>-510.12</v>
+        <v>-309.03</v>
       </c>
       <c r="L63" t="n">
-        <v>561.04</v>
+        <v>339.87</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-399.54</v>
+        <v>-255.66</v>
       </c>
       <c r="K64" t="n">
-        <v>120.8</v>
+        <v>77.3</v>
       </c>
       <c r="L64" t="n">
-        <v>417.4</v>
+        <v>267.09</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-563.88</v>
+        <v>-317.44</v>
       </c>
       <c r="K65" t="n">
-        <v>-556.54</v>
+        <v>-313.31</v>
       </c>
       <c r="L65" t="n">
-        <v>792.28</v>
+        <v>446.02</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>18</v>
       </c>
       <c r="J66" t="n">
-        <v>-628.54</v>
+        <v>-313.58</v>
       </c>
       <c r="K66" t="n">
-        <v>310.24</v>
+        <v>154.78</v>
       </c>
       <c r="L66" t="n">
-        <v>700.9400000000001</v>
+        <v>349.7</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-735.64</v>
+        <v>-357.2</v>
       </c>
       <c r="K67" t="n">
-        <v>108.45</v>
+        <v>52.66</v>
       </c>
       <c r="L67" t="n">
-        <v>743.59</v>
+        <v>361.06</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>392.37</v>
+        <v>187.58</v>
       </c>
       <c r="K68" t="n">
-        <v>1234.79</v>
+        <v>590.33</v>
       </c>
       <c r="L68" t="n">
-        <v>1295.63</v>
+        <v>619.41</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-1355.01</v>
+        <v>-669.5</v>
       </c>
       <c r="K69" t="n">
-        <v>7.29</v>
+        <v>3.6</v>
       </c>
       <c r="L69" t="n">
-        <v>1355.03</v>
+        <v>669.51</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-1037.9</v>
+        <v>-444.7</v>
       </c>
       <c r="K70" t="n">
-        <v>890.29</v>
+        <v>381.46</v>
       </c>
       <c r="L70" t="n">
-        <v>1367.43</v>
+        <v>585.89</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>967.04</v>
+        <v>432.01</v>
       </c>
       <c r="K71" t="n">
-        <v>1189.82</v>
+        <v>531.53</v>
       </c>
       <c r="L71" t="n">
-        <v>1533.25</v>
+        <v>684.95</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-1192.2</v>
+        <v>-459.89</v>
       </c>
       <c r="K72" t="n">
-        <v>-120.68</v>
+        <v>-46.55</v>
       </c>
       <c r="L72" t="n">
-        <v>1198.29</v>
+        <v>462.24</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>-1999.9</v>
+        <v>-772.35</v>
       </c>
       <c r="K73" t="n">
-        <v>10.19</v>
+        <v>3.93</v>
       </c>
       <c r="L73" t="n">
-        <v>1999.93</v>
+        <v>772.36</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>263.99</v>
+        <v>171.69</v>
       </c>
       <c r="K74" t="n">
-        <v>-452.99</v>
+        <v>-294.6</v>
       </c>
       <c r="L74" t="n">
-        <v>524.3</v>
+        <v>340.98</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-412.43</v>
+        <v>-272.73</v>
       </c>
       <c r="K75" t="n">
-        <v>21.44</v>
+        <v>14.18</v>
       </c>
       <c r="L75" t="n">
-        <v>412.99</v>
+        <v>273.1</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>348.29</v>
+        <v>232.08</v>
       </c>
       <c r="K76" t="n">
-        <v>-192.64</v>
+        <v>-128.37</v>
       </c>
       <c r="L76" t="n">
-        <v>398.02</v>
+        <v>265.22</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-26.42</v>
+        <v>-14.42</v>
       </c>
       <c r="K77" t="n">
-        <v>-364.64</v>
+        <v>-198.97</v>
       </c>
       <c r="L77" t="n">
-        <v>365.6</v>
+        <v>199.49</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>74.38</v>
+        <v>40.71</v>
       </c>
       <c r="K78" t="n">
-        <v>-414.43</v>
+        <v>-226.87</v>
       </c>
       <c r="L78" t="n">
-        <v>421.05</v>
+        <v>230.5</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-446.3</v>
+        <v>-276.23</v>
       </c>
       <c r="K79" t="n">
-        <v>-63.35</v>
+        <v>-39.21</v>
       </c>
       <c r="L79" t="n">
-        <v>450.78</v>
+        <v>279</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-28.14</v>
+        <v>-15.47</v>
       </c>
       <c r="K80" t="n">
-        <v>-672.6900000000001</v>
+        <v>-369.76</v>
       </c>
       <c r="L80" t="n">
-        <v>673.28</v>
+        <v>370.08</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-26.07</v>
+        <v>-12.67</v>
       </c>
       <c r="K81" t="n">
-        <v>793.3</v>
+        <v>385.68</v>
       </c>
       <c r="L81" t="n">
-        <v>793.73</v>
+        <v>385.89</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>768.13</v>
+        <v>423.6</v>
       </c>
       <c r="K82" t="n">
-        <v>78.84999999999999</v>
+        <v>43.48</v>
       </c>
       <c r="L82" t="n">
-        <v>772.16</v>
+        <v>425.83</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-543.33</v>
+        <v>-249.29</v>
       </c>
       <c r="K83" t="n">
-        <v>1814.13</v>
+        <v>832.34</v>
       </c>
       <c r="L83" t="n">
-        <v>1893.74</v>
+        <v>868.87</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-296.32</v>
+        <v>-130.5</v>
       </c>
       <c r="K84" t="n">
-        <v>-923.98</v>
+        <v>-406.92</v>
       </c>
       <c r="L84" t="n">
-        <v>970.33</v>
+        <v>427.34</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>313.82</v>
+        <v>153.02</v>
       </c>
       <c r="K85" t="n">
-        <v>1640.16</v>
+        <v>799.74</v>
       </c>
       <c r="L85" t="n">
-        <v>1669.92</v>
+        <v>814.24</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>1106.88</v>
+        <v>479.51</v>
       </c>
       <c r="K86" t="n">
-        <v>-49.86</v>
+        <v>-21.6</v>
       </c>
       <c r="L86" t="n">
-        <v>1108</v>
+        <v>480</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-1251.9</v>
+        <v>-484.72</v>
       </c>
       <c r="K87" t="n">
-        <v>-46.33</v>
+        <v>-17.94</v>
       </c>
       <c r="L87" t="n">
-        <v>1252.75</v>
+        <v>485.05</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>-1569.95</v>
+        <v>-655.1</v>
       </c>
       <c r="K88" t="n">
-        <v>-426.85</v>
+        <v>-178.11</v>
       </c>
       <c r="L88" t="n">
-        <v>1626.94</v>
+        <v>678.88</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-01.xlsx
+++ b/output/2025-07-01.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>201.24</v>
+        <v>223.23</v>
       </c>
       <c r="K14" t="n">
-        <v>213.24</v>
+        <v>236.53</v>
       </c>
       <c r="L14" t="n">
-        <v>293.2</v>
+        <v>325.24</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>352.11</v>
+        <v>392.54</v>
       </c>
       <c r="K15" t="n">
-        <v>123.64</v>
+        <v>137.84</v>
       </c>
       <c r="L15" t="n">
-        <v>373.18</v>
+        <v>416.04</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-318.67</v>
+        <v>-360.19</v>
       </c>
       <c r="K16" t="n">
-        <v>280.2</v>
+        <v>316.71</v>
       </c>
       <c r="L16" t="n">
-        <v>424.34</v>
+        <v>479.63</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>117.28</v>
+        <v>130.56</v>
       </c>
       <c r="K17" t="n">
-        <v>179.9</v>
+        <v>200.26</v>
       </c>
       <c r="L17" t="n">
-        <v>214.75</v>
+        <v>239.06</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>204.4</v>
+        <v>231.84</v>
       </c>
       <c r="K18" t="n">
-        <v>-178.17</v>
+        <v>-202.09</v>
       </c>
       <c r="L18" t="n">
-        <v>271.15</v>
+        <v>307.56</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>3.32</v>
+        <v>3.79</v>
       </c>
       <c r="K19" t="n">
-        <v>224.82</v>
+        <v>256.17</v>
       </c>
       <c r="L19" t="n">
-        <v>224.84</v>
+        <v>256.2</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-199.87</v>
+        <v>-232.93</v>
       </c>
       <c r="K20" t="n">
-        <v>354.86</v>
+        <v>413.55</v>
       </c>
       <c r="L20" t="n">
-        <v>407.27</v>
+        <v>474.64</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>251.36</v>
+        <v>289.18</v>
       </c>
       <c r="K21" t="n">
-        <v>-165.93</v>
+        <v>-190.9</v>
       </c>
       <c r="L21" t="n">
-        <v>301.19</v>
+        <v>346.51</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-332.13</v>
+        <v>-383.8</v>
       </c>
       <c r="K22" t="n">
-        <v>204.75</v>
+        <v>236.61</v>
       </c>
       <c r="L22" t="n">
-        <v>390.17</v>
+        <v>450.87</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>702.1</v>
+        <v>826.88</v>
       </c>
       <c r="K23" t="n">
-        <v>149.39</v>
+        <v>175.94</v>
       </c>
       <c r="L23" t="n">
-        <v>717.8099999999999</v>
+        <v>845.39</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-79.62</v>
+        <v>-95.48999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>469.77</v>
+        <v>563.4400000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>476.47</v>
+        <v>571.47</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>219.2</v>
+        <v>262.39</v>
       </c>
       <c r="K25" t="n">
-        <v>230.78</v>
+        <v>276.25</v>
       </c>
       <c r="L25" t="n">
-        <v>318.29</v>
+        <v>381</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>599.64</v>
+        <v>727.58</v>
       </c>
       <c r="K26" t="n">
-        <v>264.81</v>
+        <v>321.31</v>
       </c>
       <c r="L26" t="n">
-        <v>655.51</v>
+        <v>795.37</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-166.12</v>
+        <v>-200.83</v>
       </c>
       <c r="K27" t="n">
-        <v>-396.55</v>
+        <v>-479.41</v>
       </c>
       <c r="L27" t="n">
-        <v>429.93</v>
+        <v>519.78</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>413.16</v>
+        <v>501.1</v>
       </c>
       <c r="K28" t="n">
-        <v>575.66</v>
+        <v>698.1900000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>708.58</v>
+        <v>859.4</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>-77.28</v>
+        <v>-87.17</v>
       </c>
       <c r="K29" t="n">
-        <v>215.3</v>
+        <v>242.85</v>
       </c>
       <c r="L29" t="n">
-        <v>228.75</v>
+        <v>258.02</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>72.95999999999999</v>
+        <v>82.94</v>
       </c>
       <c r="K30" t="n">
-        <v>259.6</v>
+        <v>295.08</v>
       </c>
       <c r="L30" t="n">
-        <v>269.66</v>
+        <v>306.52</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-98.37</v>
+        <v>-110.23</v>
       </c>
       <c r="K31" t="n">
-        <v>178.89</v>
+        <v>200.47</v>
       </c>
       <c r="L31" t="n">
-        <v>204.16</v>
+        <v>228.78</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>-267.41</v>
+        <v>-304.64</v>
       </c>
       <c r="K32" t="n">
-        <v>-58.02</v>
+        <v>-66.09999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>273.63</v>
+        <v>311.72</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-22.69</v>
+        <v>-25.75</v>
       </c>
       <c r="K33" t="n">
-        <v>-365</v>
+        <v>-414.32</v>
       </c>
       <c r="L33" t="n">
-        <v>365.71</v>
+        <v>415.12</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-228.26</v>
+        <v>-259.05</v>
       </c>
       <c r="K34" t="n">
-        <v>47.99</v>
+        <v>54.47</v>
       </c>
       <c r="L34" t="n">
-        <v>233.25</v>
+        <v>264.71</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-58.96</v>
+        <v>-68.39</v>
       </c>
       <c r="K35" t="n">
-        <v>-311.44</v>
+        <v>-361.23</v>
       </c>
       <c r="L35" t="n">
-        <v>316.97</v>
+        <v>367.65</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-118.64</v>
+        <v>-137.68</v>
       </c>
       <c r="K36" t="n">
-        <v>-303.21</v>
+        <v>-351.9</v>
       </c>
       <c r="L36" t="n">
-        <v>325.6</v>
+        <v>377.87</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-79.7</v>
+        <v>-92.97</v>
       </c>
       <c r="K37" t="n">
-        <v>625.5</v>
+        <v>729.62</v>
       </c>
       <c r="L37" t="n">
-        <v>630.5599999999999</v>
+        <v>735.52</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-255.33</v>
+        <v>-305.81</v>
       </c>
       <c r="K38" t="n">
-        <v>671.9400000000001</v>
+        <v>804.78</v>
       </c>
       <c r="L38" t="n">
-        <v>718.8200000000001</v>
+        <v>860.9299999999999</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>305.56</v>
+        <v>359.37</v>
       </c>
       <c r="K39" t="n">
-        <v>-197.11</v>
+        <v>-231.81</v>
       </c>
       <c r="L39" t="n">
-        <v>363.62</v>
+        <v>427.65</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>331.13</v>
+        <v>388.88</v>
       </c>
       <c r="K40" t="n">
-        <v>276.43</v>
+        <v>324.64</v>
       </c>
       <c r="L40" t="n">
-        <v>431.35</v>
+        <v>506.57</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-88.26000000000001</v>
+        <v>-106.49</v>
       </c>
       <c r="K41" t="n">
-        <v>-438.55</v>
+        <v>-529.11</v>
       </c>
       <c r="L41" t="n">
-        <v>447.35</v>
+        <v>539.71</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>10.81</v>
+        <v>12.91</v>
       </c>
       <c r="K42" t="n">
-        <v>696.76</v>
+        <v>832.28</v>
       </c>
       <c r="L42" t="n">
-        <v>696.84</v>
+        <v>832.38</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-101.76</v>
+        <v>-121.09</v>
       </c>
       <c r="K43" t="n">
-        <v>-559.0700000000001</v>
+        <v>-665.24</v>
       </c>
       <c r="L43" t="n">
-        <v>568.26</v>
+        <v>676.17</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>95.89</v>
+        <v>107.96</v>
       </c>
       <c r="K44" t="n">
-        <v>-124.6</v>
+        <v>-140.27</v>
       </c>
       <c r="L44" t="n">
-        <v>157.22</v>
+        <v>177.01</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>204.97</v>
+        <v>234.27</v>
       </c>
       <c r="K45" t="n">
-        <v>-440.42</v>
+        <v>-503.38</v>
       </c>
       <c r="L45" t="n">
-        <v>485.78</v>
+        <v>555.23</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-343.03</v>
+        <v>-389.92</v>
       </c>
       <c r="K46" t="n">
-        <v>92.59999999999999</v>
+        <v>105.26</v>
       </c>
       <c r="L46" t="n">
-        <v>355.3</v>
+        <v>403.88</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-203.06</v>
+        <v>-229.48</v>
       </c>
       <c r="K47" t="n">
-        <v>338.51</v>
+        <v>382.56</v>
       </c>
       <c r="L47" t="n">
-        <v>394.75</v>
+        <v>446.11</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>275.01</v>
+        <v>308.55</v>
       </c>
       <c r="K48" t="n">
-        <v>254.12</v>
+        <v>285.11</v>
       </c>
       <c r="L48" t="n">
-        <v>374.44</v>
+        <v>420.11</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>38.55</v>
+        <v>43.57</v>
       </c>
       <c r="K49" t="n">
-        <v>-311.05</v>
+        <v>-351.6</v>
       </c>
       <c r="L49" t="n">
-        <v>313.43</v>
+        <v>354.29</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>68.92</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="K50" t="n">
-        <v>259.35</v>
+        <v>303.46</v>
       </c>
       <c r="L50" t="n">
-        <v>268.35</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-194.02</v>
+        <v>-224.21</v>
       </c>
       <c r="K51" t="n">
-        <v>-45.82</v>
+        <v>-52.95</v>
       </c>
       <c r="L51" t="n">
-        <v>199.36</v>
+        <v>230.37</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>-154.13</v>
+        <v>-177.92</v>
       </c>
       <c r="K52" t="n">
-        <v>448.72</v>
+        <v>517.99</v>
       </c>
       <c r="L52" t="n">
-        <v>474.45</v>
+        <v>547.7</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>79.67</v>
+        <v>93.58</v>
       </c>
       <c r="K53" t="n">
-        <v>-396.74</v>
+        <v>-466.04</v>
       </c>
       <c r="L53" t="n">
-        <v>404.66</v>
+        <v>475.34</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>515.59</v>
+        <v>614.17</v>
       </c>
       <c r="K54" t="n">
-        <v>110.97</v>
+        <v>132.18</v>
       </c>
       <c r="L54" t="n">
-        <v>527.4</v>
+        <v>628.23</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-337.53</v>
+        <v>-403.28</v>
       </c>
       <c r="K55" t="n">
-        <v>-190.52</v>
+        <v>-227.63</v>
       </c>
       <c r="L55" t="n">
-        <v>387.58</v>
+        <v>463.08</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>619.21</v>
+        <v>746.39</v>
       </c>
       <c r="K56" t="n">
-        <v>50.95</v>
+        <v>61.42</v>
       </c>
       <c r="L56" t="n">
-        <v>621.3099999999999</v>
+        <v>748.92</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>17</v>
       </c>
       <c r="J57" t="n">
-        <v>-400.18</v>
+        <v>-482.8</v>
       </c>
       <c r="K57" t="n">
-        <v>-115.3</v>
+        <v>-139.1</v>
       </c>
       <c r="L57" t="n">
-        <v>416.46</v>
+        <v>502.44</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>81.25</v>
+        <v>98.83</v>
       </c>
       <c r="K58" t="n">
-        <v>760.39</v>
+        <v>924.9</v>
       </c>
       <c r="L58" t="n">
-        <v>764.72</v>
+        <v>930.16</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-151.54</v>
+        <v>-171.62</v>
       </c>
       <c r="K59" t="n">
-        <v>187.83</v>
+        <v>212.72</v>
       </c>
       <c r="L59" t="n">
-        <v>241.34</v>
+        <v>273.32</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-346.21</v>
+        <v>-391.94</v>
       </c>
       <c r="K60" t="n">
-        <v>281.31</v>
+        <v>318.47</v>
       </c>
       <c r="L60" t="n">
-        <v>446.09</v>
+        <v>505.02</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-244.3</v>
+        <v>-272.64</v>
       </c>
       <c r="K61" t="n">
-        <v>26.75</v>
+        <v>29.85</v>
       </c>
       <c r="L61" t="n">
-        <v>245.76</v>
+        <v>274.27</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>454.84</v>
+        <v>514.74</v>
       </c>
       <c r="K62" t="n">
-        <v>-95.42</v>
+        <v>-107.99</v>
       </c>
       <c r="L62" t="n">
-        <v>464.74</v>
+        <v>525.95</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-141.48</v>
+        <v>-158.46</v>
       </c>
       <c r="K63" t="n">
-        <v>-309.03</v>
+        <v>-346.12</v>
       </c>
       <c r="L63" t="n">
-        <v>339.87</v>
+        <v>380.67</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-255.66</v>
+        <v>-284.97</v>
       </c>
       <c r="K64" t="n">
-        <v>77.3</v>
+        <v>86.16</v>
       </c>
       <c r="L64" t="n">
-        <v>267.09</v>
+        <v>297.71</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-317.44</v>
+        <v>-361.83</v>
       </c>
       <c r="K65" t="n">
-        <v>-313.31</v>
+        <v>-357.12</v>
       </c>
       <c r="L65" t="n">
-        <v>446.02</v>
+        <v>508.39</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>18</v>
       </c>
       <c r="J66" t="n">
-        <v>-313.58</v>
+        <v>-364.11</v>
       </c>
       <c r="K66" t="n">
-        <v>154.78</v>
+        <v>179.72</v>
       </c>
       <c r="L66" t="n">
-        <v>349.7</v>
+        <v>406.05</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-357.2</v>
+        <v>-417.96</v>
       </c>
       <c r="K67" t="n">
-        <v>52.66</v>
+        <v>61.62</v>
       </c>
       <c r="L67" t="n">
-        <v>361.06</v>
+        <v>422.48</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>187.58</v>
+        <v>220.19</v>
       </c>
       <c r="K68" t="n">
-        <v>590.33</v>
+        <v>692.95</v>
       </c>
       <c r="L68" t="n">
-        <v>619.41</v>
+        <v>727.09</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-669.5</v>
+        <v>-782.87</v>
       </c>
       <c r="K69" t="n">
-        <v>3.6</v>
+        <v>4.21</v>
       </c>
       <c r="L69" t="n">
-        <v>669.51</v>
+        <v>782.88</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-444.7</v>
+        <v>-527.27</v>
       </c>
       <c r="K70" t="n">
-        <v>381.46</v>
+        <v>452.29</v>
       </c>
       <c r="L70" t="n">
-        <v>585.89</v>
+        <v>694.6799999999999</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>432.01</v>
+        <v>513.39</v>
       </c>
       <c r="K71" t="n">
-        <v>531.53</v>
+        <v>631.67</v>
       </c>
       <c r="L71" t="n">
-        <v>684.95</v>
+        <v>813.99</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-459.89</v>
+        <v>-562.58</v>
       </c>
       <c r="K72" t="n">
-        <v>-46.55</v>
+        <v>-56.95</v>
       </c>
       <c r="L72" t="n">
-        <v>462.24</v>
+        <v>565.45</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>-772.35</v>
+        <v>-921.73</v>
       </c>
       <c r="K73" t="n">
-        <v>3.93</v>
+        <v>4.69</v>
       </c>
       <c r="L73" t="n">
-        <v>772.36</v>
+        <v>921.75</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>171.69</v>
+        <v>191.18</v>
       </c>
       <c r="K74" t="n">
-        <v>-294.6</v>
+        <v>-328.05</v>
       </c>
       <c r="L74" t="n">
-        <v>340.98</v>
+        <v>379.7</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-272.73</v>
+        <v>-303.89</v>
       </c>
       <c r="K75" t="n">
-        <v>14.18</v>
+        <v>15.8</v>
       </c>
       <c r="L75" t="n">
-        <v>273.1</v>
+        <v>304.3</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>232.08</v>
+        <v>258.08</v>
       </c>
       <c r="K76" t="n">
-        <v>-128.37</v>
+        <v>-142.75</v>
       </c>
       <c r="L76" t="n">
-        <v>265.22</v>
+        <v>294.93</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-14.42</v>
+        <v>-16.44</v>
       </c>
       <c r="K77" t="n">
-        <v>-198.97</v>
+        <v>-226.85</v>
       </c>
       <c r="L77" t="n">
-        <v>199.49</v>
+        <v>227.44</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>40.71</v>
+        <v>46.51</v>
       </c>
       <c r="K78" t="n">
-        <v>-226.87</v>
+        <v>-259.17</v>
       </c>
       <c r="L78" t="n">
-        <v>230.5</v>
+        <v>263.32</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-276.23</v>
+        <v>-309.67</v>
       </c>
       <c r="K79" t="n">
-        <v>-39.21</v>
+        <v>-43.95</v>
       </c>
       <c r="L79" t="n">
-        <v>279</v>
+        <v>312.77</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-15.47</v>
+        <v>-17.6</v>
       </c>
       <c r="K80" t="n">
-        <v>-369.76</v>
+        <v>-420.8</v>
       </c>
       <c r="L80" t="n">
-        <v>370.08</v>
+        <v>421.17</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.67</v>
+        <v>-14.83</v>
       </c>
       <c r="K81" t="n">
-        <v>385.68</v>
+        <v>451.29</v>
       </c>
       <c r="L81" t="n">
-        <v>385.89</v>
+        <v>451.53</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>423.6</v>
+        <v>483.59</v>
       </c>
       <c r="K82" t="n">
-        <v>43.48</v>
+        <v>49.64</v>
       </c>
       <c r="L82" t="n">
-        <v>425.83</v>
+        <v>486.13</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-249.29</v>
+        <v>-290.25</v>
       </c>
       <c r="K83" t="n">
-        <v>832.34</v>
+        <v>969.12</v>
       </c>
       <c r="L83" t="n">
-        <v>868.87</v>
+        <v>1011.65</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-130.5</v>
+        <v>-154.08</v>
       </c>
       <c r="K84" t="n">
-        <v>-406.92</v>
+        <v>-480.45</v>
       </c>
       <c r="L84" t="n">
-        <v>427.34</v>
+        <v>504.56</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>153.02</v>
+        <v>176.96</v>
       </c>
       <c r="K85" t="n">
-        <v>799.74</v>
+        <v>924.85</v>
       </c>
       <c r="L85" t="n">
-        <v>814.24</v>
+        <v>941.62</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>479.51</v>
+        <v>570.7</v>
       </c>
       <c r="K86" t="n">
-        <v>-21.6</v>
+        <v>-25.71</v>
       </c>
       <c r="L86" t="n">
-        <v>480</v>
+        <v>571.28</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-484.72</v>
+        <v>-594.79</v>
       </c>
       <c r="K87" t="n">
-        <v>-17.94</v>
+        <v>-22.01</v>
       </c>
       <c r="L87" t="n">
-        <v>485.05</v>
+        <v>595.2</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>-655.1</v>
+        <v>-780.28</v>
       </c>
       <c r="K88" t="n">
-        <v>-178.11</v>
+        <v>-212.15</v>
       </c>
       <c r="L88" t="n">
-        <v>678.88</v>
+        <v>808.61</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-01.xlsx
+++ b/output/2025-07-01.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>223.23</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>236.53</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>325.24</v>
+        <v>132.2</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>392.54</v>
+        <v>161.22</v>
       </c>
       <c r="K15" t="n">
-        <v>137.84</v>
+        <v>56.61</v>
       </c>
       <c r="L15" t="n">
-        <v>416.04</v>
+        <v>170.87</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-360.19</v>
+        <v>-146.88</v>
       </c>
       <c r="K16" t="n">
-        <v>316.71</v>
+        <v>129.15</v>
       </c>
       <c r="L16" t="n">
-        <v>479.63</v>
+        <v>195.59</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>130.56</v>
+        <v>56.04</v>
       </c>
       <c r="K17" t="n">
-        <v>200.26</v>
+        <v>85.97</v>
       </c>
       <c r="L17" t="n">
-        <v>239.06</v>
+        <v>102.62</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>231.84</v>
+        <v>100.03</v>
       </c>
       <c r="K18" t="n">
-        <v>-202.09</v>
+        <v>-87.19</v>
       </c>
       <c r="L18" t="n">
-        <v>307.56</v>
+        <v>132.7</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>3.79</v>
+        <v>1.68</v>
       </c>
       <c r="K19" t="n">
-        <v>256.17</v>
+        <v>113.46</v>
       </c>
       <c r="L19" t="n">
-        <v>256.2</v>
+        <v>113.47</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-232.93</v>
+        <v>-111.37</v>
       </c>
       <c r="K20" t="n">
-        <v>413.55</v>
+        <v>197.72</v>
       </c>
       <c r="L20" t="n">
-        <v>474.64</v>
+        <v>226.93</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>289.18</v>
+        <v>138.37</v>
       </c>
       <c r="K21" t="n">
-        <v>-190.9</v>
+        <v>-91.34</v>
       </c>
       <c r="L21" t="n">
-        <v>346.51</v>
+        <v>165.8</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-383.8</v>
+        <v>-183.68</v>
       </c>
       <c r="K22" t="n">
-        <v>236.61</v>
+        <v>113.24</v>
       </c>
       <c r="L22" t="n">
-        <v>450.87</v>
+        <v>215.78</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>826.88</v>
+        <v>384.86</v>
       </c>
       <c r="K23" t="n">
-        <v>175.94</v>
+        <v>81.89</v>
       </c>
       <c r="L23" t="n">
-        <v>845.39</v>
+        <v>393.48</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-95.48999999999999</v>
+        <v>-43.64</v>
       </c>
       <c r="K24" t="n">
-        <v>563.4400000000001</v>
+        <v>257.47</v>
       </c>
       <c r="L24" t="n">
-        <v>571.47</v>
+        <v>261.14</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>262.39</v>
+        <v>116.99</v>
       </c>
       <c r="K25" t="n">
-        <v>276.25</v>
+        <v>123.17</v>
       </c>
       <c r="L25" t="n">
-        <v>381</v>
+        <v>169.87</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>727.58</v>
+        <v>402.5</v>
       </c>
       <c r="K26" t="n">
-        <v>321.31</v>
+        <v>177.75</v>
       </c>
       <c r="L26" t="n">
-        <v>795.37</v>
+        <v>440</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-200.83</v>
+        <v>-109.13</v>
       </c>
       <c r="K27" t="n">
-        <v>-479.41</v>
+        <v>-260.5</v>
       </c>
       <c r="L27" t="n">
-        <v>519.78</v>
+        <v>282.44</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>501.1</v>
+        <v>272.22</v>
       </c>
       <c r="K28" t="n">
-        <v>698.1900000000001</v>
+        <v>379.28</v>
       </c>
       <c r="L28" t="n">
-        <v>859.4</v>
+        <v>466.86</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>-87.17</v>
+        <v>-35.39</v>
       </c>
       <c r="K29" t="n">
-        <v>242.85</v>
+        <v>98.58</v>
       </c>
       <c r="L29" t="n">
-        <v>258.02</v>
+        <v>104.74</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>82.94</v>
+        <v>33.91</v>
       </c>
       <c r="K30" t="n">
-        <v>295.08</v>
+        <v>120.64</v>
       </c>
       <c r="L30" t="n">
-        <v>306.52</v>
+        <v>125.32</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-110.23</v>
+        <v>-44.9</v>
       </c>
       <c r="K31" t="n">
-        <v>200.47</v>
+        <v>81.66</v>
       </c>
       <c r="L31" t="n">
-        <v>228.78</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>-304.64</v>
+        <v>-134.23</v>
       </c>
       <c r="K32" t="n">
-        <v>-66.09999999999999</v>
+        <v>-29.13</v>
       </c>
       <c r="L32" t="n">
-        <v>311.72</v>
+        <v>137.35</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-25.75</v>
+        <v>-11.18</v>
       </c>
       <c r="K33" t="n">
-        <v>-414.32</v>
+        <v>-179.82</v>
       </c>
       <c r="L33" t="n">
-        <v>415.12</v>
+        <v>180.16</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-259.05</v>
+        <v>-115.35</v>
       </c>
       <c r="K34" t="n">
-        <v>54.47</v>
+        <v>24.25</v>
       </c>
       <c r="L34" t="n">
-        <v>264.71</v>
+        <v>117.87</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-68.39</v>
+        <v>-32.78</v>
       </c>
       <c r="K35" t="n">
-        <v>-361.23</v>
+        <v>-173.16</v>
       </c>
       <c r="L35" t="n">
-        <v>367.65</v>
+        <v>176.24</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-137.68</v>
+        <v>-65.87</v>
       </c>
       <c r="K36" t="n">
-        <v>-351.9</v>
+        <v>-168.35</v>
       </c>
       <c r="L36" t="n">
-        <v>377.87</v>
+        <v>180.78</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-92.97</v>
+        <v>-44.53</v>
       </c>
       <c r="K37" t="n">
-        <v>729.62</v>
+        <v>349.45</v>
       </c>
       <c r="L37" t="n">
-        <v>735.52</v>
+        <v>352.27</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-305.81</v>
+        <v>-144.27</v>
       </c>
       <c r="K38" t="n">
-        <v>804.78</v>
+        <v>379.67</v>
       </c>
       <c r="L38" t="n">
-        <v>860.9299999999999</v>
+        <v>406.16</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>359.37</v>
+        <v>168.96</v>
       </c>
       <c r="K39" t="n">
-        <v>-231.81</v>
+        <v>-108.99</v>
       </c>
       <c r="L39" t="n">
-        <v>427.65</v>
+        <v>201.06</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>388.88</v>
+        <v>185.52</v>
       </c>
       <c r="K40" t="n">
-        <v>324.64</v>
+        <v>154.87</v>
       </c>
       <c r="L40" t="n">
-        <v>506.57</v>
+        <v>241.66</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-106.49</v>
+        <v>-59.33</v>
       </c>
       <c r="K41" t="n">
-        <v>-529.11</v>
+        <v>-294.78</v>
       </c>
       <c r="L41" t="n">
-        <v>539.71</v>
+        <v>300.69</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>12.91</v>
+        <v>7.03</v>
       </c>
       <c r="K42" t="n">
-        <v>832.28</v>
+        <v>453.18</v>
       </c>
       <c r="L42" t="n">
-        <v>832.38</v>
+        <v>453.24</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-121.09</v>
+        <v>-67.31</v>
       </c>
       <c r="K43" t="n">
-        <v>-665.24</v>
+        <v>-369.78</v>
       </c>
       <c r="L43" t="n">
-        <v>676.17</v>
+        <v>375.85</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>107.96</v>
+        <v>44.37</v>
       </c>
       <c r="K44" t="n">
-        <v>-140.27</v>
+        <v>-57.65</v>
       </c>
       <c r="L44" t="n">
-        <v>177.01</v>
+        <v>72.75</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>234.27</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>-503.38</v>
+        <v>-207.51</v>
       </c>
       <c r="L45" t="n">
-        <v>555.23</v>
+        <v>228.88</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-389.92</v>
+        <v>-160.1</v>
       </c>
       <c r="K46" t="n">
-        <v>105.26</v>
+        <v>43.22</v>
       </c>
       <c r="L46" t="n">
-        <v>403.88</v>
+        <v>165.83</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-229.48</v>
+        <v>-102.99</v>
       </c>
       <c r="K47" t="n">
-        <v>382.56</v>
+        <v>171.69</v>
       </c>
       <c r="L47" t="n">
-        <v>446.11</v>
+        <v>200.21</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>308.55</v>
+        <v>133.87</v>
       </c>
       <c r="K48" t="n">
-        <v>285.11</v>
+        <v>123.71</v>
       </c>
       <c r="L48" t="n">
-        <v>420.11</v>
+        <v>182.28</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>43.57</v>
+        <v>19.16</v>
       </c>
       <c r="K49" t="n">
-        <v>-351.6</v>
+        <v>-154.6</v>
       </c>
       <c r="L49" t="n">
-        <v>354.29</v>
+        <v>155.78</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>80.65000000000001</v>
+        <v>38.64</v>
       </c>
       <c r="K50" t="n">
-        <v>303.46</v>
+        <v>145.4</v>
       </c>
       <c r="L50" t="n">
-        <v>314</v>
+        <v>150.45</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-224.21</v>
+        <v>-107.45</v>
       </c>
       <c r="K51" t="n">
-        <v>-52.95</v>
+        <v>-25.37</v>
       </c>
       <c r="L51" t="n">
-        <v>230.37</v>
+        <v>110.4</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>-177.92</v>
+        <v>-85.26000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>517.99</v>
+        <v>248.22</v>
       </c>
       <c r="L52" t="n">
-        <v>547.7</v>
+        <v>262.46</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>93.58</v>
+        <v>46.26</v>
       </c>
       <c r="K53" t="n">
-        <v>-466.04</v>
+        <v>-230.37</v>
       </c>
       <c r="L53" t="n">
-        <v>475.34</v>
+        <v>234.97</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>614.17</v>
+        <v>284.15</v>
       </c>
       <c r="K54" t="n">
-        <v>132.18</v>
+        <v>61.16</v>
       </c>
       <c r="L54" t="n">
-        <v>628.23</v>
+        <v>290.65</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-403.28</v>
+        <v>-185.24</v>
       </c>
       <c r="K55" t="n">
-        <v>-227.63</v>
+        <v>-104.56</v>
       </c>
       <c r="L55" t="n">
-        <v>463.08</v>
+        <v>212.71</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>746.39</v>
+        <v>406.21</v>
       </c>
       <c r="K56" t="n">
-        <v>61.42</v>
+        <v>33.43</v>
       </c>
       <c r="L56" t="n">
-        <v>748.92</v>
+        <v>407.58</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>17</v>
       </c>
       <c r="J57" t="n">
-        <v>-482.8</v>
+        <v>-269.62</v>
       </c>
       <c r="K57" t="n">
-        <v>-139.1</v>
+        <v>-77.68000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>502.44</v>
+        <v>280.59</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>98.83</v>
+        <v>54.87</v>
       </c>
       <c r="K58" t="n">
-        <v>924.9</v>
+        <v>513.51</v>
       </c>
       <c r="L58" t="n">
-        <v>930.16</v>
+        <v>516.4299999999999</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-171.62</v>
+        <v>-69.66</v>
       </c>
       <c r="K59" t="n">
-        <v>212.72</v>
+        <v>86.34</v>
       </c>
       <c r="L59" t="n">
-        <v>273.32</v>
+        <v>110.94</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-391.94</v>
+        <v>-162.11</v>
       </c>
       <c r="K60" t="n">
-        <v>318.47</v>
+        <v>131.72</v>
       </c>
       <c r="L60" t="n">
-        <v>505.02</v>
+        <v>208.88</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-272.64</v>
+        <v>-111.13</v>
       </c>
       <c r="K61" t="n">
-        <v>29.85</v>
+        <v>12.17</v>
       </c>
       <c r="L61" t="n">
-        <v>274.27</v>
+        <v>111.79</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>514.74</v>
+        <v>225.73</v>
       </c>
       <c r="K62" t="n">
-        <v>-107.99</v>
+        <v>-47.35</v>
       </c>
       <c r="L62" t="n">
-        <v>525.95</v>
+        <v>230.64</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-158.46</v>
+        <v>-69.38</v>
       </c>
       <c r="K63" t="n">
-        <v>-346.12</v>
+        <v>-151.55</v>
       </c>
       <c r="L63" t="n">
-        <v>380.67</v>
+        <v>166.68</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-284.97</v>
+        <v>-125.42</v>
       </c>
       <c r="K64" t="n">
-        <v>86.16</v>
+        <v>37.92</v>
       </c>
       <c r="L64" t="n">
-        <v>297.71</v>
+        <v>131.03</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-361.83</v>
+        <v>-173.22</v>
       </c>
       <c r="K65" t="n">
-        <v>-357.12</v>
+        <v>-170.96</v>
       </c>
       <c r="L65" t="n">
-        <v>508.39</v>
+        <v>243.38</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>18</v>
       </c>
       <c r="J66" t="n">
-        <v>-364.11</v>
+        <v>-174.5</v>
       </c>
       <c r="K66" t="n">
-        <v>179.72</v>
+        <v>86.13</v>
       </c>
       <c r="L66" t="n">
-        <v>406.05</v>
+        <v>194.6</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-417.96</v>
+        <v>-200.37</v>
       </c>
       <c r="K67" t="n">
-        <v>61.62</v>
+        <v>29.54</v>
       </c>
       <c r="L67" t="n">
-        <v>422.48</v>
+        <v>202.54</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>220.19</v>
+        <v>105.47</v>
       </c>
       <c r="K68" t="n">
-        <v>692.95</v>
+        <v>331.91</v>
       </c>
       <c r="L68" t="n">
-        <v>727.09</v>
+        <v>348.27</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-782.87</v>
+        <v>-372.57</v>
       </c>
       <c r="K69" t="n">
-        <v>4.21</v>
+        <v>2</v>
       </c>
       <c r="L69" t="n">
-        <v>782.88</v>
+        <v>372.57</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-527.27</v>
+        <v>-255.36</v>
       </c>
       <c r="K70" t="n">
-        <v>452.29</v>
+        <v>219.05</v>
       </c>
       <c r="L70" t="n">
-        <v>694.6799999999999</v>
+        <v>336.44</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>513.39</v>
+        <v>286.29</v>
       </c>
       <c r="K71" t="n">
-        <v>631.67</v>
+        <v>352.24</v>
       </c>
       <c r="L71" t="n">
-        <v>813.99</v>
+        <v>453.91</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-562.58</v>
+        <v>-309.62</v>
       </c>
       <c r="K72" t="n">
-        <v>-56.95</v>
+        <v>-31.34</v>
       </c>
       <c r="L72" t="n">
-        <v>565.45</v>
+        <v>311.21</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>-921.73</v>
+        <v>-521.16</v>
       </c>
       <c r="K73" t="n">
-        <v>4.69</v>
+        <v>2.65</v>
       </c>
       <c r="L73" t="n">
-        <v>921.75</v>
+        <v>521.17</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>191.18</v>
+        <v>77.95</v>
       </c>
       <c r="K74" t="n">
-        <v>-328.05</v>
+        <v>-133.76</v>
       </c>
       <c r="L74" t="n">
-        <v>379.7</v>
+        <v>154.81</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-303.89</v>
+        <v>-125.2</v>
       </c>
       <c r="K75" t="n">
-        <v>15.8</v>
+        <v>6.51</v>
       </c>
       <c r="L75" t="n">
-        <v>304.3</v>
+        <v>125.37</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>258.08</v>
+        <v>105.7</v>
       </c>
       <c r="K76" t="n">
-        <v>-142.75</v>
+        <v>-58.46</v>
       </c>
       <c r="L76" t="n">
-        <v>294.93</v>
+        <v>120.79</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-16.44</v>
+        <v>-7.25</v>
       </c>
       <c r="K77" t="n">
-        <v>-226.85</v>
+        <v>-100.11</v>
       </c>
       <c r="L77" t="n">
-        <v>227.44</v>
+        <v>100.38</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>46.51</v>
+        <v>20.43</v>
       </c>
       <c r="K78" t="n">
-        <v>-259.17</v>
+        <v>-113.85</v>
       </c>
       <c r="L78" t="n">
-        <v>263.32</v>
+        <v>115.67</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-309.67</v>
+        <v>-136.94</v>
       </c>
       <c r="K79" t="n">
-        <v>-43.95</v>
+        <v>-19.44</v>
       </c>
       <c r="L79" t="n">
-        <v>312.77</v>
+        <v>138.32</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-17.6</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>-420.8</v>
+        <v>-201.96</v>
       </c>
       <c r="L80" t="n">
-        <v>421.17</v>
+        <v>202.14</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-14.83</v>
+        <v>-7.11</v>
       </c>
       <c r="K81" t="n">
-        <v>451.29</v>
+        <v>216.32</v>
       </c>
       <c r="L81" t="n">
-        <v>451.53</v>
+        <v>216.44</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>483.59</v>
+        <v>232.02</v>
       </c>
       <c r="K82" t="n">
-        <v>49.64</v>
+        <v>23.82</v>
       </c>
       <c r="L82" t="n">
-        <v>486.13</v>
+        <v>233.23</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-290.25</v>
+        <v>-142.97</v>
       </c>
       <c r="K83" t="n">
-        <v>969.12</v>
+        <v>477.37</v>
       </c>
       <c r="L83" t="n">
-        <v>1011.65</v>
+        <v>498.32</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-154.08</v>
+        <v>-74.06999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>-480.45</v>
+        <v>-230.96</v>
       </c>
       <c r="L84" t="n">
-        <v>504.56</v>
+        <v>242.55</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>176.96</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>924.85</v>
+        <v>453.05</v>
       </c>
       <c r="L85" t="n">
-        <v>941.62</v>
+        <v>461.27</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>570.7</v>
+        <v>318.54</v>
       </c>
       <c r="K86" t="n">
-        <v>-25.71</v>
+        <v>-14.35</v>
       </c>
       <c r="L86" t="n">
-        <v>571.28</v>
+        <v>318.86</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-594.79</v>
+        <v>-325.86</v>
       </c>
       <c r="K87" t="n">
-        <v>-22.01</v>
+        <v>-12.06</v>
       </c>
       <c r="L87" t="n">
-        <v>595.2</v>
+        <v>326.08</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>-780.28</v>
+        <v>-440.52</v>
       </c>
       <c r="K88" t="n">
-        <v>-212.15</v>
+        <v>-119.77</v>
       </c>
       <c r="L88" t="n">
-        <v>808.61</v>
+        <v>456.51</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-01.xlsx
+++ b/output/2025-07-01.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>90.73999999999999</v>
+        <v>69.53</v>
       </c>
       <c r="K14" t="n">
-        <v>96.15000000000001</v>
+        <v>73.67</v>
       </c>
       <c r="L14" t="n">
-        <v>132.2</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>161.22</v>
+        <v>118.39</v>
       </c>
       <c r="K15" t="n">
-        <v>56.61</v>
+        <v>41.57</v>
       </c>
       <c r="L15" t="n">
-        <v>170.87</v>
+        <v>125.47</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-146.88</v>
+        <v>-108.86</v>
       </c>
       <c r="K16" t="n">
-        <v>129.15</v>
+        <v>95.72</v>
       </c>
       <c r="L16" t="n">
-        <v>195.59</v>
+        <v>144.96</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>56.04</v>
+        <v>48.55</v>
       </c>
       <c r="K17" t="n">
-        <v>85.97</v>
+        <v>74.47</v>
       </c>
       <c r="L17" t="n">
-        <v>102.62</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>100.03</v>
+        <v>84.56</v>
       </c>
       <c r="K18" t="n">
-        <v>-87.19</v>
+        <v>-73.70999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>132.7</v>
+        <v>112.17</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="K19" t="n">
-        <v>113.46</v>
+        <v>97.92</v>
       </c>
       <c r="L19" t="n">
-        <v>113.47</v>
+        <v>97.93000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-111.37</v>
+        <v>-105.76</v>
       </c>
       <c r="K20" t="n">
-        <v>197.72</v>
+        <v>187.76</v>
       </c>
       <c r="L20" t="n">
-        <v>226.93</v>
+        <v>215.5</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>138.37</v>
+        <v>135.89</v>
       </c>
       <c r="K21" t="n">
-        <v>-91.34</v>
+        <v>-89.7</v>
       </c>
       <c r="L21" t="n">
-        <v>165.8</v>
+        <v>162.83</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-183.68</v>
+        <v>-175.37</v>
       </c>
       <c r="K22" t="n">
-        <v>113.24</v>
+        <v>108.12</v>
       </c>
       <c r="L22" t="n">
-        <v>215.78</v>
+        <v>206.02</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>384.86</v>
+        <v>398.31</v>
       </c>
       <c r="K23" t="n">
-        <v>81.89</v>
+        <v>84.75</v>
       </c>
       <c r="L23" t="n">
-        <v>393.48</v>
+        <v>407.23</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-43.64</v>
+        <v>-46.74</v>
       </c>
       <c r="K24" t="n">
-        <v>257.47</v>
+        <v>275.78</v>
       </c>
       <c r="L24" t="n">
-        <v>261.14</v>
+        <v>279.71</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>116.99</v>
+        <v>129.22</v>
       </c>
       <c r="K25" t="n">
-        <v>123.17</v>
+        <v>136.05</v>
       </c>
       <c r="L25" t="n">
-        <v>169.87</v>
+        <v>187.64</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>402.5</v>
+        <v>481.13</v>
       </c>
       <c r="K26" t="n">
-        <v>177.75</v>
+        <v>212.48</v>
       </c>
       <c r="L26" t="n">
-        <v>440</v>
+        <v>525.96</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-109.13</v>
+        <v>-131.74</v>
       </c>
       <c r="K27" t="n">
-        <v>-260.5</v>
+        <v>-314.49</v>
       </c>
       <c r="L27" t="n">
-        <v>282.44</v>
+        <v>340.96</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>272.22</v>
+        <v>310.23</v>
       </c>
       <c r="K28" t="n">
-        <v>379.28</v>
+        <v>432.25</v>
       </c>
       <c r="L28" t="n">
-        <v>466.86</v>
+        <v>532.0599999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>-35.39</v>
+        <v>-28.11</v>
       </c>
       <c r="K29" t="n">
-        <v>98.58</v>
+        <v>78.31999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>104.74</v>
+        <v>83.22</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>33.91</v>
+        <v>26.1</v>
       </c>
       <c r="K30" t="n">
-        <v>120.64</v>
+        <v>92.86</v>
       </c>
       <c r="L30" t="n">
-        <v>125.32</v>
+        <v>96.45</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-44.9</v>
+        <v>-35.84</v>
       </c>
       <c r="K31" t="n">
-        <v>81.66</v>
+        <v>65.19</v>
       </c>
       <c r="L31" t="n">
-        <v>93.2</v>
+        <v>74.39</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>-134.23</v>
+        <v>-111.88</v>
       </c>
       <c r="K32" t="n">
-        <v>-29.13</v>
+        <v>-24.28</v>
       </c>
       <c r="L32" t="n">
-        <v>137.35</v>
+        <v>114.48</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-11.18</v>
+        <v>-9.07</v>
       </c>
       <c r="K33" t="n">
-        <v>-179.82</v>
+        <v>-145.92</v>
       </c>
       <c r="L33" t="n">
-        <v>180.16</v>
+        <v>146.2</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-115.35</v>
+        <v>-98.09999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>24.25</v>
+        <v>20.63</v>
       </c>
       <c r="L34" t="n">
-        <v>117.87</v>
+        <v>100.25</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-32.78</v>
+        <v>-32.61</v>
       </c>
       <c r="K35" t="n">
-        <v>-173.16</v>
+        <v>-172.23</v>
       </c>
       <c r="L35" t="n">
-        <v>176.24</v>
+        <v>175.29</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-65.87</v>
+        <v>-64.02</v>
       </c>
       <c r="K36" t="n">
-        <v>-168.35</v>
+        <v>-163.63</v>
       </c>
       <c r="L36" t="n">
-        <v>180.78</v>
+        <v>175.71</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-44.53</v>
+        <v>-40.9</v>
       </c>
       <c r="K37" t="n">
-        <v>349.45</v>
+        <v>320.95</v>
       </c>
       <c r="L37" t="n">
-        <v>352.27</v>
+        <v>323.55</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-144.27</v>
+        <v>-151.26</v>
       </c>
       <c r="K38" t="n">
-        <v>379.67</v>
+        <v>398.06</v>
       </c>
       <c r="L38" t="n">
-        <v>406.16</v>
+        <v>425.83</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>168.96</v>
+        <v>190.31</v>
       </c>
       <c r="K39" t="n">
-        <v>-108.99</v>
+        <v>-122.76</v>
       </c>
       <c r="L39" t="n">
-        <v>201.06</v>
+        <v>226.47</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>185.52</v>
+        <v>206.23</v>
       </c>
       <c r="K40" t="n">
-        <v>154.87</v>
+        <v>172.16</v>
       </c>
       <c r="L40" t="n">
-        <v>241.66</v>
+        <v>268.64</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-59.33</v>
+        <v>-75.95</v>
       </c>
       <c r="K41" t="n">
-        <v>-294.78</v>
+        <v>-377.39</v>
       </c>
       <c r="L41" t="n">
-        <v>300.69</v>
+        <v>384.95</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>7.03</v>
+        <v>8.01</v>
       </c>
       <c r="K42" t="n">
-        <v>453.18</v>
+        <v>516.47</v>
       </c>
       <c r="L42" t="n">
-        <v>453.24</v>
+        <v>516.53</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-67.31</v>
+        <v>-81.84</v>
       </c>
       <c r="K43" t="n">
-        <v>-369.78</v>
+        <v>-449.58</v>
       </c>
       <c r="L43" t="n">
-        <v>375.85</v>
+        <v>456.97</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>44.37</v>
+        <v>36.65</v>
       </c>
       <c r="K44" t="n">
-        <v>-57.65</v>
+        <v>-47.62</v>
       </c>
       <c r="L44" t="n">
-        <v>72.75</v>
+        <v>60.09</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>96.56999999999999</v>
+        <v>69.19</v>
       </c>
       <c r="K45" t="n">
-        <v>-207.51</v>
+        <v>-148.67</v>
       </c>
       <c r="L45" t="n">
-        <v>228.88</v>
+        <v>163.99</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-160.1</v>
+        <v>-118.67</v>
       </c>
       <c r="K46" t="n">
-        <v>43.22</v>
+        <v>32.03</v>
       </c>
       <c r="L46" t="n">
-        <v>165.83</v>
+        <v>122.92</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-102.99</v>
+        <v>-81.16</v>
       </c>
       <c r="K47" t="n">
-        <v>171.69</v>
+        <v>135.3</v>
       </c>
       <c r="L47" t="n">
-        <v>200.21</v>
+        <v>157.77</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>133.87</v>
+        <v>108.23</v>
       </c>
       <c r="K48" t="n">
-        <v>123.71</v>
+        <v>100.01</v>
       </c>
       <c r="L48" t="n">
-        <v>182.28</v>
+        <v>147.37</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>19.16</v>
+        <v>15.67</v>
       </c>
       <c r="K49" t="n">
-        <v>-154.6</v>
+        <v>-126.47</v>
       </c>
       <c r="L49" t="n">
-        <v>155.78</v>
+        <v>127.43</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>38.64</v>
+        <v>39.17</v>
       </c>
       <c r="K50" t="n">
-        <v>145.4</v>
+        <v>147.37</v>
       </c>
       <c r="L50" t="n">
-        <v>150.45</v>
+        <v>152.49</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-107.45</v>
+        <v>-111.32</v>
       </c>
       <c r="K51" t="n">
-        <v>-25.37</v>
+        <v>-26.29</v>
       </c>
       <c r="L51" t="n">
-        <v>110.4</v>
+        <v>114.38</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>-85.26000000000001</v>
+        <v>-80.16</v>
       </c>
       <c r="K52" t="n">
-        <v>248.22</v>
+        <v>233.38</v>
       </c>
       <c r="L52" t="n">
-        <v>262.46</v>
+        <v>246.76</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>46.26</v>
+        <v>54.03</v>
       </c>
       <c r="K53" t="n">
-        <v>-230.37</v>
+        <v>-269.05</v>
       </c>
       <c r="L53" t="n">
-        <v>234.97</v>
+        <v>274.42</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>284.15</v>
+        <v>301.92</v>
       </c>
       <c r="K54" t="n">
-        <v>61.16</v>
+        <v>64.98</v>
       </c>
       <c r="L54" t="n">
-        <v>290.65</v>
+        <v>308.83</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-185.24</v>
+        <v>-203.17</v>
       </c>
       <c r="K55" t="n">
-        <v>-104.56</v>
+        <v>-114.68</v>
       </c>
       <c r="L55" t="n">
-        <v>212.71</v>
+        <v>233.31</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>406.21</v>
+        <v>467.61</v>
       </c>
       <c r="K56" t="n">
-        <v>33.43</v>
+        <v>38.48</v>
       </c>
       <c r="L56" t="n">
-        <v>407.58</v>
+        <v>469.19</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>17</v>
       </c>
       <c r="J57" t="n">
-        <v>-269.62</v>
+        <v>-351.65</v>
       </c>
       <c r="K57" t="n">
-        <v>-77.68000000000001</v>
+        <v>-101.31</v>
       </c>
       <c r="L57" t="n">
-        <v>280.59</v>
+        <v>365.95</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>54.87</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>513.51</v>
+        <v>606.35</v>
       </c>
       <c r="L58" t="n">
-        <v>516.4299999999999</v>
+        <v>609.8</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-69.66</v>
+        <v>-55.53</v>
       </c>
       <c r="K59" t="n">
-        <v>86.34</v>
+        <v>68.83</v>
       </c>
       <c r="L59" t="n">
-        <v>110.94</v>
+        <v>88.44</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-162.11</v>
+        <v>-110.88</v>
       </c>
       <c r="K60" t="n">
-        <v>131.72</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>208.88</v>
+        <v>142.87</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-111.13</v>
+        <v>-87.17</v>
       </c>
       <c r="K61" t="n">
-        <v>12.17</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>111.79</v>
+        <v>87.7</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>225.73</v>
+        <v>179.28</v>
       </c>
       <c r="K62" t="n">
-        <v>-47.35</v>
+        <v>-37.61</v>
       </c>
       <c r="L62" t="n">
-        <v>230.64</v>
+        <v>183.19</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-69.38</v>
+        <v>-56.68</v>
       </c>
       <c r="K63" t="n">
-        <v>-151.55</v>
+        <v>-123.81</v>
       </c>
       <c r="L63" t="n">
-        <v>166.68</v>
+        <v>136.17</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-125.42</v>
+        <v>-105.03</v>
       </c>
       <c r="K64" t="n">
-        <v>37.92</v>
+        <v>31.76</v>
       </c>
       <c r="L64" t="n">
-        <v>131.03</v>
+        <v>109.73</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-173.22</v>
+        <v>-163.77</v>
       </c>
       <c r="K65" t="n">
-        <v>-170.96</v>
+        <v>-161.64</v>
       </c>
       <c r="L65" t="n">
-        <v>243.38</v>
+        <v>230.1</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>18</v>
       </c>
       <c r="J66" t="n">
-        <v>-174.5</v>
+        <v>-172.04</v>
       </c>
       <c r="K66" t="n">
-        <v>86.13</v>
+        <v>84.92</v>
       </c>
       <c r="L66" t="n">
-        <v>194.6</v>
+        <v>191.86</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-200.37</v>
+        <v>-197.56</v>
       </c>
       <c r="K67" t="n">
-        <v>29.54</v>
+        <v>29.13</v>
       </c>
       <c r="L67" t="n">
-        <v>202.54</v>
+        <v>199.69</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>105.47</v>
+        <v>113.61</v>
       </c>
       <c r="K68" t="n">
-        <v>331.91</v>
+        <v>357.53</v>
       </c>
       <c r="L68" t="n">
-        <v>348.27</v>
+        <v>375.15</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-372.57</v>
+        <v>-395.5</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="L69" t="n">
-        <v>372.57</v>
+        <v>395.5</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-255.36</v>
+        <v>-281.38</v>
       </c>
       <c r="K70" t="n">
-        <v>219.05</v>
+        <v>241.36</v>
       </c>
       <c r="L70" t="n">
-        <v>336.44</v>
+        <v>370.71</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>286.29</v>
+        <v>345.91</v>
       </c>
       <c r="K71" t="n">
-        <v>352.24</v>
+        <v>425.6</v>
       </c>
       <c r="L71" t="n">
-        <v>453.91</v>
+        <v>548.45</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-309.62</v>
+        <v>-387.84</v>
       </c>
       <c r="K72" t="n">
-        <v>-31.34</v>
+        <v>-39.26</v>
       </c>
       <c r="L72" t="n">
-        <v>311.21</v>
+        <v>389.82</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>-521.16</v>
+        <v>-609.1</v>
       </c>
       <c r="K73" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="L73" t="n">
-        <v>521.17</v>
+        <v>609.1</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>77.95</v>
+        <v>58.78</v>
       </c>
       <c r="K74" t="n">
-        <v>-133.76</v>
+        <v>-100.85</v>
       </c>
       <c r="L74" t="n">
-        <v>154.81</v>
+        <v>116.73</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-125.2</v>
+        <v>-94.94</v>
       </c>
       <c r="K75" t="n">
-        <v>6.51</v>
+        <v>4.94</v>
       </c>
       <c r="L75" t="n">
-        <v>125.37</v>
+        <v>95.06999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>105.7</v>
+        <v>81.14</v>
       </c>
       <c r="K76" t="n">
-        <v>-58.46</v>
+        <v>-44.88</v>
       </c>
       <c r="L76" t="n">
-        <v>120.79</v>
+        <v>92.72</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-7.25</v>
+        <v>-6.43</v>
       </c>
       <c r="K77" t="n">
-        <v>-100.11</v>
+        <v>-88.8</v>
       </c>
       <c r="L77" t="n">
-        <v>100.38</v>
+        <v>89.03</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>20.43</v>
+        <v>17.67</v>
       </c>
       <c r="K78" t="n">
-        <v>-113.85</v>
+        <v>-98.44</v>
       </c>
       <c r="L78" t="n">
-        <v>115.67</v>
+        <v>100.01</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-136.94</v>
+        <v>-113.69</v>
       </c>
       <c r="K79" t="n">
-        <v>-19.44</v>
+        <v>-16.14</v>
       </c>
       <c r="L79" t="n">
-        <v>138.32</v>
+        <v>114.83</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.449999999999999</v>
+        <v>-8.27</v>
       </c>
       <c r="K80" t="n">
-        <v>-201.96</v>
+        <v>-197.8</v>
       </c>
       <c r="L80" t="n">
-        <v>202.14</v>
+        <v>197.98</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-7.11</v>
+        <v>-6.92</v>
       </c>
       <c r="K81" t="n">
-        <v>216.32</v>
+        <v>210.5</v>
       </c>
       <c r="L81" t="n">
-        <v>216.44</v>
+        <v>210.61</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>232.02</v>
+        <v>222.56</v>
       </c>
       <c r="K82" t="n">
-        <v>23.82</v>
+        <v>22.85</v>
       </c>
       <c r="L82" t="n">
-        <v>233.23</v>
+        <v>223.73</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-142.97</v>
+        <v>-152.11</v>
       </c>
       <c r="K83" t="n">
-        <v>477.37</v>
+        <v>507.88</v>
       </c>
       <c r="L83" t="n">
-        <v>498.32</v>
+        <v>530.17</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-74.06999999999999</v>
+        <v>-84.25</v>
       </c>
       <c r="K84" t="n">
-        <v>-230.96</v>
+        <v>-262.72</v>
       </c>
       <c r="L84" t="n">
-        <v>242.55</v>
+        <v>275.9</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>86.68000000000001</v>
+        <v>92.13</v>
       </c>
       <c r="K85" t="n">
-        <v>453.05</v>
+        <v>481.52</v>
       </c>
       <c r="L85" t="n">
-        <v>461.27</v>
+        <v>490.25</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>318.54</v>
+        <v>404.9</v>
       </c>
       <c r="K86" t="n">
-        <v>-14.35</v>
+        <v>-18.24</v>
       </c>
       <c r="L86" t="n">
-        <v>318.86</v>
+        <v>405.31</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-325.86</v>
+        <v>-399.05</v>
       </c>
       <c r="K87" t="n">
-        <v>-12.06</v>
+        <v>-14.77</v>
       </c>
       <c r="L87" t="n">
-        <v>326.08</v>
+        <v>399.33</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>-440.52</v>
+        <v>-525.04</v>
       </c>
       <c r="K88" t="n">
-        <v>-119.77</v>
+        <v>-142.75</v>
       </c>
       <c r="L88" t="n">
-        <v>456.51</v>
+        <v>544.11</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-01.xlsx
+++ b/output/2025-07-01.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>69.53</v>
+        <v>65.97</v>
       </c>
       <c r="K14" t="n">
-        <v>73.67</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>101.3</v>
+        <v>96.12</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>118.39</v>
+        <v>109.89</v>
       </c>
       <c r="K15" t="n">
-        <v>41.57</v>
+        <v>38.59</v>
       </c>
       <c r="L15" t="n">
-        <v>125.47</v>
+        <v>116.47</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-108.86</v>
+        <v>-99.78</v>
       </c>
       <c r="K16" t="n">
-        <v>95.72</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>144.96</v>
+        <v>132.87</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>48.55</v>
+        <v>48.98</v>
       </c>
       <c r="K17" t="n">
-        <v>74.47</v>
+        <v>75.13</v>
       </c>
       <c r="L17" t="n">
-        <v>88.90000000000001</v>
+        <v>89.69</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>84.56</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-73.70999999999999</v>
+        <v>-72.8</v>
       </c>
       <c r="L18" t="n">
-        <v>112.17</v>
+        <v>110.79</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="K19" t="n">
-        <v>97.92</v>
+        <v>101.79</v>
       </c>
       <c r="L19" t="n">
-        <v>97.93000000000001</v>
+        <v>101.8</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-105.76</v>
+        <v>-102.29</v>
       </c>
       <c r="K20" t="n">
-        <v>187.76</v>
+        <v>181.61</v>
       </c>
       <c r="L20" t="n">
-        <v>215.5</v>
+        <v>208.44</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>135.89</v>
+        <v>137.04</v>
       </c>
       <c r="K21" t="n">
-        <v>-89.7</v>
+        <v>-90.45999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>162.83</v>
+        <v>164.2</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-175.37</v>
+        <v>-171.3</v>
       </c>
       <c r="K22" t="n">
-        <v>108.12</v>
+        <v>105.61</v>
       </c>
       <c r="L22" t="n">
-        <v>206.02</v>
+        <v>201.24</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>398.31</v>
+        <v>379.84</v>
       </c>
       <c r="K23" t="n">
-        <v>84.75</v>
+        <v>80.81999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>407.23</v>
+        <v>388.34</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-46.74</v>
+        <v>-46.78</v>
       </c>
       <c r="K24" t="n">
-        <v>275.78</v>
+        <v>276.01</v>
       </c>
       <c r="L24" t="n">
-        <v>279.71</v>
+        <v>279.95</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>129.22</v>
+        <v>134.96</v>
       </c>
       <c r="K25" t="n">
-        <v>136.05</v>
+        <v>142.09</v>
       </c>
       <c r="L25" t="n">
-        <v>187.64</v>
+        <v>195.97</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>481.13</v>
+        <v>486.77</v>
       </c>
       <c r="K26" t="n">
-        <v>212.48</v>
+        <v>214.97</v>
       </c>
       <c r="L26" t="n">
-        <v>525.96</v>
+        <v>532.12</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-131.74</v>
+        <v>-137.99</v>
       </c>
       <c r="K27" t="n">
-        <v>-314.49</v>
+        <v>-329.4</v>
       </c>
       <c r="L27" t="n">
-        <v>340.96</v>
+        <v>357.13</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>310.23</v>
+        <v>304.33</v>
       </c>
       <c r="K28" t="n">
-        <v>432.25</v>
+        <v>424.03</v>
       </c>
       <c r="L28" t="n">
-        <v>532.0599999999999</v>
+        <v>521.9400000000001</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>-28.11</v>
+        <v>-27.95</v>
       </c>
       <c r="K29" t="n">
-        <v>78.31999999999999</v>
+        <v>77.87</v>
       </c>
       <c r="L29" t="n">
-        <v>83.22</v>
+        <v>82.73999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>26.1</v>
+        <v>25.25</v>
       </c>
       <c r="K30" t="n">
-        <v>92.86</v>
+        <v>89.83</v>
       </c>
       <c r="L30" t="n">
-        <v>96.45</v>
+        <v>93.31</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-35.84</v>
+        <v>-35.73</v>
       </c>
       <c r="K31" t="n">
-        <v>65.19</v>
+        <v>64.98</v>
       </c>
       <c r="L31" t="n">
-        <v>74.39</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>-111.88</v>
+        <v>-111.45</v>
       </c>
       <c r="K32" t="n">
-        <v>-24.28</v>
+        <v>-24.18</v>
       </c>
       <c r="L32" t="n">
-        <v>114.48</v>
+        <v>114.05</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-9.07</v>
+        <v>-8.6</v>
       </c>
       <c r="K33" t="n">
-        <v>-145.92</v>
+        <v>-138.38</v>
       </c>
       <c r="L33" t="n">
-        <v>146.2</v>
+        <v>138.65</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-98.09999999999999</v>
+        <v>-101.02</v>
       </c>
       <c r="K34" t="n">
-        <v>20.63</v>
+        <v>21.24</v>
       </c>
       <c r="L34" t="n">
-        <v>100.25</v>
+        <v>103.23</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-32.61</v>
+        <v>-33.54</v>
       </c>
       <c r="K35" t="n">
-        <v>-172.23</v>
+        <v>-177.13</v>
       </c>
       <c r="L35" t="n">
-        <v>175.29</v>
+        <v>180.27</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-64.02</v>
+        <v>-63.77</v>
       </c>
       <c r="K36" t="n">
-        <v>-163.63</v>
+        <v>-162.99</v>
       </c>
       <c r="L36" t="n">
-        <v>175.71</v>
+        <v>175.03</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-40.9</v>
+        <v>-38.18</v>
       </c>
       <c r="K37" t="n">
-        <v>320.95</v>
+        <v>299.63</v>
       </c>
       <c r="L37" t="n">
-        <v>323.55</v>
+        <v>302.05</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-151.26</v>
+        <v>-145.87</v>
       </c>
       <c r="K38" t="n">
-        <v>398.06</v>
+        <v>383.86</v>
       </c>
       <c r="L38" t="n">
-        <v>425.83</v>
+        <v>410.64</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>190.31</v>
+        <v>199.48</v>
       </c>
       <c r="K39" t="n">
-        <v>-122.76</v>
+        <v>-128.68</v>
       </c>
       <c r="L39" t="n">
-        <v>226.47</v>
+        <v>237.38</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>206.23</v>
+        <v>212.13</v>
       </c>
       <c r="K40" t="n">
-        <v>172.16</v>
+        <v>177.09</v>
       </c>
       <c r="L40" t="n">
-        <v>268.64</v>
+        <v>276.34</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-75.95</v>
+        <v>-82.05</v>
       </c>
       <c r="K41" t="n">
-        <v>-377.39</v>
+        <v>-407.66</v>
       </c>
       <c r="L41" t="n">
-        <v>384.95</v>
+        <v>415.84</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>8.01</v>
+        <v>7.83</v>
       </c>
       <c r="K42" t="n">
-        <v>516.47</v>
+        <v>504.89</v>
       </c>
       <c r="L42" t="n">
-        <v>516.53</v>
+        <v>504.95</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-81.84</v>
+        <v>-83.88</v>
       </c>
       <c r="K43" t="n">
-        <v>-449.58</v>
+        <v>-460.8</v>
       </c>
       <c r="L43" t="n">
-        <v>456.97</v>
+        <v>468.38</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>36.65</v>
+        <v>38.76</v>
       </c>
       <c r="K44" t="n">
-        <v>-47.62</v>
+        <v>-50.36</v>
       </c>
       <c r="L44" t="n">
-        <v>60.09</v>
+        <v>63.55</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>69.19</v>
+        <v>63.07</v>
       </c>
       <c r="K45" t="n">
-        <v>-148.67</v>
+        <v>-135.52</v>
       </c>
       <c r="L45" t="n">
-        <v>163.99</v>
+        <v>149.48</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-118.67</v>
+        <v>-111.32</v>
       </c>
       <c r="K46" t="n">
-        <v>32.03</v>
+        <v>30.05</v>
       </c>
       <c r="L46" t="n">
-        <v>122.92</v>
+        <v>115.31</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-81.16</v>
+        <v>-77.5</v>
       </c>
       <c r="K47" t="n">
-        <v>135.3</v>
+        <v>129.19</v>
       </c>
       <c r="L47" t="n">
-        <v>157.77</v>
+        <v>150.65</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>108.23</v>
+        <v>102.14</v>
       </c>
       <c r="K48" t="n">
-        <v>100.01</v>
+        <v>94.38</v>
       </c>
       <c r="L48" t="n">
-        <v>147.37</v>
+        <v>139.07</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>15.67</v>
+        <v>15.25</v>
       </c>
       <c r="K49" t="n">
-        <v>-126.47</v>
+        <v>-123.04</v>
       </c>
       <c r="L49" t="n">
-        <v>127.43</v>
+        <v>123.98</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>39.17</v>
+        <v>41.03</v>
       </c>
       <c r="K50" t="n">
-        <v>147.37</v>
+        <v>154.4</v>
       </c>
       <c r="L50" t="n">
-        <v>152.49</v>
+        <v>159.76</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-111.32</v>
+        <v>-122.24</v>
       </c>
       <c r="K51" t="n">
-        <v>-26.29</v>
+        <v>-28.87</v>
       </c>
       <c r="L51" t="n">
-        <v>114.38</v>
+        <v>125.6</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>-80.16</v>
+        <v>-77.20999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>233.38</v>
+        <v>224.79</v>
       </c>
       <c r="L52" t="n">
-        <v>246.76</v>
+        <v>237.68</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>54.03</v>
+        <v>57.94</v>
       </c>
       <c r="K53" t="n">
-        <v>-269.05</v>
+        <v>-288.51</v>
       </c>
       <c r="L53" t="n">
-        <v>274.42</v>
+        <v>294.27</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>301.92</v>
+        <v>298.01</v>
       </c>
       <c r="K54" t="n">
-        <v>64.98</v>
+        <v>64.14</v>
       </c>
       <c r="L54" t="n">
-        <v>308.83</v>
+        <v>304.83</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-203.17</v>
+        <v>-208.49</v>
       </c>
       <c r="K55" t="n">
-        <v>-114.68</v>
+        <v>-117.68</v>
       </c>
       <c r="L55" t="n">
-        <v>233.31</v>
+        <v>239.41</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>467.61</v>
+        <v>463.07</v>
       </c>
       <c r="K56" t="n">
-        <v>38.48</v>
+        <v>38.1</v>
       </c>
       <c r="L56" t="n">
-        <v>469.19</v>
+        <v>464.63</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>17</v>
       </c>
       <c r="J57" t="n">
-        <v>-351.65</v>
+        <v>-385.94</v>
       </c>
       <c r="K57" t="n">
-        <v>-101.31</v>
+        <v>-111.19</v>
       </c>
       <c r="L57" t="n">
-        <v>365.95</v>
+        <v>401.64</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>64.79000000000001</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>606.35</v>
+        <v>601.6799999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>609.8</v>
+        <v>605.11</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-55.53</v>
+        <v>-55.46</v>
       </c>
       <c r="K59" t="n">
-        <v>68.83</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>88.44</v>
+        <v>88.33</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-110.88</v>
+        <v>-105.1</v>
       </c>
       <c r="K60" t="n">
-        <v>90.09999999999999</v>
+        <v>85.39</v>
       </c>
       <c r="L60" t="n">
-        <v>142.87</v>
+        <v>135.42</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-87.17</v>
+        <v>-85.39</v>
       </c>
       <c r="K61" t="n">
-        <v>9.550000000000001</v>
+        <v>9.35</v>
       </c>
       <c r="L61" t="n">
-        <v>87.7</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>179.28</v>
+        <v>167.82</v>
       </c>
       <c r="K62" t="n">
-        <v>-37.61</v>
+        <v>-35.21</v>
       </c>
       <c r="L62" t="n">
-        <v>183.19</v>
+        <v>171.47</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-56.68</v>
+        <v>-54.79</v>
       </c>
       <c r="K63" t="n">
-        <v>-123.81</v>
+        <v>-119.67</v>
       </c>
       <c r="L63" t="n">
-        <v>136.17</v>
+        <v>131.61</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-105.03</v>
+        <v>-105.04</v>
       </c>
       <c r="K64" t="n">
         <v>31.76</v>
       </c>
       <c r="L64" t="n">
-        <v>109.73</v>
+        <v>109.74</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-163.77</v>
+        <v>-158.26</v>
       </c>
       <c r="K65" t="n">
-        <v>-161.64</v>
+        <v>-156.2</v>
       </c>
       <c r="L65" t="n">
-        <v>230.1</v>
+        <v>222.37</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>18</v>
       </c>
       <c r="J66" t="n">
-        <v>-172.04</v>
+        <v>-175.12</v>
       </c>
       <c r="K66" t="n">
-        <v>84.92</v>
+        <v>86.44</v>
       </c>
       <c r="L66" t="n">
-        <v>191.86</v>
+        <v>195.29</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-197.56</v>
+        <v>-201.31</v>
       </c>
       <c r="K67" t="n">
-        <v>29.13</v>
+        <v>29.68</v>
       </c>
       <c r="L67" t="n">
-        <v>199.69</v>
+        <v>203.49</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>113.61</v>
+        <v>112.59</v>
       </c>
       <c r="K68" t="n">
-        <v>357.53</v>
+        <v>354.32</v>
       </c>
       <c r="L68" t="n">
-        <v>375.15</v>
+        <v>371.78</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-395.5</v>
+        <v>-386.02</v>
       </c>
       <c r="K69" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="L69" t="n">
-        <v>395.5</v>
+        <v>386.03</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-281.38</v>
+        <v>-285.21</v>
       </c>
       <c r="K70" t="n">
-        <v>241.36</v>
+        <v>244.65</v>
       </c>
       <c r="L70" t="n">
-        <v>370.71</v>
+        <v>375.76</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>345.91</v>
+        <v>350.57</v>
       </c>
       <c r="K71" t="n">
-        <v>425.6</v>
+        <v>431.33</v>
       </c>
       <c r="L71" t="n">
-        <v>548.45</v>
+        <v>555.83</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-387.84</v>
+        <v>-415.63</v>
       </c>
       <c r="K72" t="n">
-        <v>-39.26</v>
+        <v>-42.07</v>
       </c>
       <c r="L72" t="n">
-        <v>389.82</v>
+        <v>417.76</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>-609.1</v>
+        <v>-613.1</v>
       </c>
       <c r="K73" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="L73" t="n">
-        <v>609.1</v>
+        <v>613.11</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>58.78</v>
+        <v>55.01</v>
       </c>
       <c r="K74" t="n">
-        <v>-100.85</v>
+        <v>-94.40000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>116.73</v>
+        <v>109.26</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-94.94</v>
+        <v>-92.47</v>
       </c>
       <c r="K75" t="n">
-        <v>4.94</v>
+        <v>4.81</v>
       </c>
       <c r="L75" t="n">
-        <v>95.06999999999999</v>
+        <v>92.59</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>81.14</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>-44.88</v>
+        <v>-43.52</v>
       </c>
       <c r="L76" t="n">
-        <v>92.72</v>
+        <v>89.92</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-6.43</v>
+        <v>-6.85</v>
       </c>
       <c r="K77" t="n">
-        <v>-88.8</v>
+        <v>-94.5</v>
       </c>
       <c r="L77" t="n">
-        <v>89.03</v>
+        <v>94.73999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>17.67</v>
+        <v>18.24</v>
       </c>
       <c r="K78" t="n">
-        <v>-98.44</v>
+        <v>-101.64</v>
       </c>
       <c r="L78" t="n">
-        <v>100.01</v>
+        <v>103.26</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-113.69</v>
+        <v>-113.24</v>
       </c>
       <c r="K79" t="n">
-        <v>-16.14</v>
+        <v>-16.07</v>
       </c>
       <c r="L79" t="n">
-        <v>114.83</v>
+        <v>114.37</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.27</v>
+        <v>-8.4</v>
       </c>
       <c r="K80" t="n">
-        <v>-197.8</v>
+        <v>-200.8</v>
       </c>
       <c r="L80" t="n">
-        <v>197.98</v>
+        <v>200.97</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.92</v>
+        <v>-6.94</v>
       </c>
       <c r="K81" t="n">
-        <v>210.5</v>
+        <v>211.29</v>
       </c>
       <c r="L81" t="n">
-        <v>210.61</v>
+        <v>211.4</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>222.56</v>
+        <v>220.45</v>
       </c>
       <c r="K82" t="n">
-        <v>22.85</v>
+        <v>22.63</v>
       </c>
       <c r="L82" t="n">
-        <v>223.73</v>
+        <v>221.6</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-152.11</v>
+        <v>-147.08</v>
       </c>
       <c r="K83" t="n">
-        <v>507.88</v>
+        <v>491.09</v>
       </c>
       <c r="L83" t="n">
-        <v>530.17</v>
+        <v>512.64</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-84.25</v>
+        <v>-88.63</v>
       </c>
       <c r="K84" t="n">
-        <v>-262.72</v>
+        <v>-276.37</v>
       </c>
       <c r="L84" t="n">
-        <v>275.9</v>
+        <v>290.23</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>92.13</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>481.52</v>
+        <v>465.91</v>
       </c>
       <c r="L85" t="n">
-        <v>490.25</v>
+        <v>474.36</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>404.9</v>
+        <v>433.26</v>
       </c>
       <c r="K86" t="n">
-        <v>-18.24</v>
+        <v>-19.52</v>
       </c>
       <c r="L86" t="n">
-        <v>405.31</v>
+        <v>433.7</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-399.05</v>
+        <v>-419.99</v>
       </c>
       <c r="K87" t="n">
-        <v>-14.77</v>
+        <v>-15.54</v>
       </c>
       <c r="L87" t="n">
-        <v>399.33</v>
+        <v>420.28</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>-525.04</v>
+        <v>-532.34</v>
       </c>
       <c r="K88" t="n">
-        <v>-142.75</v>
+        <v>-144.74</v>
       </c>
       <c r="L88" t="n">
-        <v>544.11</v>
+        <v>551.66</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-01.xlsx
+++ b/output/2025-07-01.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>5.89</v>
+        <v>5.96</v>
       </c>
       <c r="F14" t="n">
-        <v>16.11</v>
+        <v>15.24</v>
       </c>
       <c r="G14" t="n">
-        <v>328.8</v>
+        <v>341.9</v>
       </c>
       <c r="H14" t="n">
         <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>65.97</v>
+        <v>104.89</v>
       </c>
       <c r="K14" t="n">
-        <v>69.90000000000001</v>
+        <v>-0.17</v>
       </c>
       <c r="L14" t="n">
-        <v>96.12</v>
+        <v>104.89</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:35:04</t>
+          <t>04:36:28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>6.63</v>
+        <v>6.88</v>
       </c>
       <c r="F15" t="n">
-        <v>15.81</v>
+        <v>13.61</v>
       </c>
       <c r="G15" t="n">
-        <v>345.8</v>
+        <v>333.6</v>
       </c>
       <c r="H15" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>109.89</v>
+        <v>-69.62</v>
       </c>
       <c r="K15" t="n">
-        <v>38.59</v>
+        <v>-52.81</v>
       </c>
       <c r="L15" t="n">
-        <v>116.47</v>
+        <v>87.39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:35:50</t>
+          <t>04:37:48</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>6.1</v>
+        <v>5.91</v>
       </c>
       <c r="F16" t="n">
-        <v>16.06</v>
+        <v>10.49</v>
       </c>
       <c r="G16" t="n">
-        <v>323.4</v>
+        <v>326</v>
       </c>
       <c r="H16" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-99.78</v>
+        <v>-64.70999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>87.73999999999999</v>
+        <v>18.84</v>
       </c>
       <c r="L16" t="n">
-        <v>132.87</v>
+        <v>67.39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:40:25</t>
+          <t>04:43:34</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>5.64</v>
+        <v>6.37</v>
       </c>
       <c r="F17" t="n">
-        <v>16.33</v>
+        <v>14.03</v>
       </c>
       <c r="G17" t="n">
-        <v>337.2</v>
+        <v>328.2</v>
       </c>
       <c r="H17" t="n">
         <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>48.98</v>
+        <v>-91.09999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>75.13</v>
+        <v>-31.37</v>
       </c>
       <c r="L17" t="n">
-        <v>89.69</v>
+        <v>96.34999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:43:12</t>
+          <t>04:45:45</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="F18" t="n">
-        <v>16.01</v>
+        <v>14.7</v>
       </c>
       <c r="G18" t="n">
-        <v>326.4</v>
+        <v>344.1</v>
       </c>
       <c r="H18" t="n">
-        <v>97.5</v>
+        <v>96.7</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>83.51000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="K18" t="n">
-        <v>-72.8</v>
+        <v>-86.42</v>
       </c>
       <c r="L18" t="n">
-        <v>110.79</v>
+        <v>110.27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:45:02</t>
+          <t>04:47:35</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>6.82</v>
+        <v>5.67</v>
       </c>
       <c r="F19" t="n">
-        <v>16.42</v>
+        <v>11.58</v>
       </c>
       <c r="G19" t="n">
-        <v>325.8</v>
+        <v>321.2</v>
       </c>
       <c r="H19" t="n">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>1.51</v>
+        <v>44.94</v>
       </c>
       <c r="K19" t="n">
-        <v>101.79</v>
+        <v>163.27</v>
       </c>
       <c r="L19" t="n">
-        <v>101.8</v>
+        <v>169.34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:50:38</t>
+          <t>04:51:53</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>5.39</v>
+        <v>6.16</v>
       </c>
       <c r="F20" t="n">
-        <v>16.18</v>
+        <v>12.73</v>
       </c>
       <c r="G20" t="n">
-        <v>352.3</v>
+        <v>326.4</v>
       </c>
       <c r="H20" t="n">
         <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-102.29</v>
+        <v>68.91</v>
       </c>
       <c r="K20" t="n">
-        <v>181.61</v>
+        <v>164.24</v>
       </c>
       <c r="L20" t="n">
-        <v>208.44</v>
+        <v>178.12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:51:28</t>
+          <t>04:53:13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>5.73</v>
+        <v>6.24</v>
       </c>
       <c r="F21" t="n">
-        <v>16.22</v>
+        <v>14.63</v>
       </c>
       <c r="G21" t="n">
-        <v>334.1</v>
+        <v>327.5</v>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>137.04</v>
+        <v>-7.04</v>
       </c>
       <c r="K21" t="n">
-        <v>-90.45999999999999</v>
+        <v>-0.44</v>
       </c>
       <c r="L21" t="n">
-        <v>164.2</v>
+        <v>7.06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:52:53</t>
+          <t>04:55:16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>5.81</v>
+        <v>6.47</v>
       </c>
       <c r="F22" t="n">
-        <v>16.41</v>
+        <v>12.86</v>
       </c>
       <c r="G22" t="n">
-        <v>326.8</v>
+        <v>330.5</v>
       </c>
       <c r="H22" t="n">
         <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-171.3</v>
+        <v>-38.58</v>
       </c>
       <c r="K22" t="n">
-        <v>105.61</v>
+        <v>168.75</v>
       </c>
       <c r="L22" t="n">
-        <v>201.24</v>
+        <v>173.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:57:18</t>
+          <t>05:00:40</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>6.03</v>
+        <v>5.04</v>
       </c>
       <c r="F23" t="n">
-        <v>15.64</v>
+        <v>12.61</v>
       </c>
       <c r="G23" t="n">
-        <v>314.8</v>
+        <v>323.9</v>
       </c>
       <c r="H23" t="n">
         <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>379.84</v>
+        <v>-155.47</v>
       </c>
       <c r="K23" t="n">
-        <v>80.81999999999999</v>
+        <v>216.6</v>
       </c>
       <c r="L23" t="n">
-        <v>388.34</v>
+        <v>266.62</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:59:43</t>
+          <t>05:03:01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>5.62</v>
+        <v>6.01</v>
       </c>
       <c r="F24" t="n">
-        <v>16.02</v>
+        <v>13.55</v>
       </c>
       <c r="G24" t="n">
-        <v>339.4</v>
+        <v>316.4</v>
       </c>
       <c r="H24" t="n">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-46.78</v>
+        <v>175.33</v>
       </c>
       <c r="K24" t="n">
-        <v>276.01</v>
+        <v>14.17</v>
       </c>
       <c r="L24" t="n">
-        <v>279.95</v>
+        <v>175.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:01:20</t>
+          <t>05:04:03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5.15</v>
+        <v>6.18</v>
       </c>
       <c r="F25" t="n">
-        <v>16.14</v>
+        <v>15.7</v>
       </c>
       <c r="G25" t="n">
-        <v>332.3</v>
+        <v>336.4</v>
       </c>
       <c r="H25" t="n">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>134.96</v>
+        <v>-201.22</v>
       </c>
       <c r="K25" t="n">
-        <v>142.09</v>
+        <v>-224.63</v>
       </c>
       <c r="L25" t="n">
-        <v>195.97</v>
+        <v>301.58</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:06:00</t>
+          <t>05:08:15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>6.46</v>
+        <v>6.3</v>
       </c>
       <c r="F26" t="n">
-        <v>16.22</v>
+        <v>16.51</v>
       </c>
       <c r="G26" t="n">
-        <v>318.3</v>
+        <v>324.3</v>
       </c>
       <c r="H26" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I26" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>486.77</v>
+        <v>-599.24</v>
       </c>
       <c r="K26" t="n">
-        <v>214.97</v>
+        <v>-23.7</v>
       </c>
       <c r="L26" t="n">
-        <v>532.12</v>
+        <v>599.7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:07:53</t>
+          <t>05:09:23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>5.69</v>
+        <v>4.82</v>
       </c>
       <c r="F27" t="n">
-        <v>16.13</v>
+        <v>10.68</v>
       </c>
       <c r="G27" t="n">
-        <v>310.6</v>
+        <v>324</v>
       </c>
       <c r="H27" t="n">
-        <v>98.40000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="I27" t="n">
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-137.99</v>
+        <v>-373.06</v>
       </c>
       <c r="K27" t="n">
-        <v>-329.4</v>
+        <v>185.13</v>
       </c>
       <c r="L27" t="n">
-        <v>357.13</v>
+        <v>416.47</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:08:46</t>
+          <t>05:11:21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>5.68</v>
+        <v>5.62</v>
       </c>
       <c r="F28" t="n">
-        <v>15.68</v>
+        <v>14.74</v>
       </c>
       <c r="G28" t="n">
-        <v>333.4</v>
+        <v>325.1</v>
       </c>
       <c r="H28" t="n">
-        <v>94.3</v>
+        <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>304.33</v>
+        <v>-255.69</v>
       </c>
       <c r="K28" t="n">
-        <v>424.03</v>
+        <v>-256.9</v>
       </c>
       <c r="L28" t="n">
-        <v>521.9400000000001</v>
+        <v>362.45</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:19:43</t>
+          <t>05:21:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>5.81</v>
+        <v>5.77</v>
       </c>
       <c r="F29" t="n">
-        <v>16.18</v>
+        <v>16.41</v>
       </c>
       <c r="G29" t="n">
-        <v>324.3</v>
+        <v>332.2</v>
       </c>
       <c r="H29" t="n">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-27.95</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>77.87</v>
+        <v>-11.74</v>
       </c>
       <c r="L29" t="n">
-        <v>82.73999999999999</v>
+        <v>14.33</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:21:28</t>
+          <t>05:23:48</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>6.28</v>
+        <v>6.86</v>
       </c>
       <c r="F30" t="n">
-        <v>16.59</v>
+        <v>16.47</v>
       </c>
       <c r="G30" t="n">
         <v>328.2</v>
       </c>
       <c r="H30" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I30" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>25.25</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
-        <v>89.83</v>
+        <v>87.23</v>
       </c>
       <c r="L30" t="n">
-        <v>93.31</v>
+        <v>87.31999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:22:47</t>
+          <t>05:25:35</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>6.03</v>
+        <v>6.73</v>
       </c>
       <c r="F31" t="n">
-        <v>16.29</v>
+        <v>14.56</v>
       </c>
       <c r="G31" t="n">
-        <v>339</v>
+        <v>336.5</v>
       </c>
       <c r="H31" t="n">
         <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-35.73</v>
+        <v>88.72</v>
       </c>
       <c r="K31" t="n">
-        <v>64.98</v>
+        <v>-18.19</v>
       </c>
       <c r="L31" t="n">
-        <v>74.16</v>
+        <v>90.56999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:28:10</t>
+          <t>05:31:11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>6.59</v>
+        <v>6.25</v>
       </c>
       <c r="F32" t="n">
-        <v>16.08</v>
+        <v>13.22</v>
       </c>
       <c r="G32" t="n">
-        <v>326.9</v>
+        <v>327.2</v>
       </c>
       <c r="H32" t="n">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>-111.45</v>
+        <v>-66.65000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-24.18</v>
+        <v>76.05</v>
       </c>
       <c r="L32" t="n">
-        <v>114.05</v>
+        <v>101.12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:29:06</t>
+          <t>05:32:41</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>6</v>
+        <v>6.24</v>
       </c>
       <c r="F33" t="n">
-        <v>15.51</v>
+        <v>12.72</v>
       </c>
       <c r="G33" t="n">
-        <v>330.6</v>
+        <v>344</v>
       </c>
       <c r="H33" t="n">
-        <v>100</v>
+        <v>92.2</v>
       </c>
       <c r="I33" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-8.6</v>
+        <v>-40.66</v>
       </c>
       <c r="K33" t="n">
-        <v>-138.38</v>
+        <v>114.83</v>
       </c>
       <c r="L33" t="n">
-        <v>138.65</v>
+        <v>121.82</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:30:43</t>
+          <t>05:33:51</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>7.08</v>
+        <v>6.09</v>
       </c>
       <c r="F34" t="n">
-        <v>15.94</v>
+        <v>13.39</v>
       </c>
       <c r="G34" t="n">
-        <v>339.2</v>
+        <v>337.1</v>
       </c>
       <c r="H34" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="I34" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-101.02</v>
+        <v>28.85</v>
       </c>
       <c r="K34" t="n">
-        <v>21.24</v>
+        <v>-140.19</v>
       </c>
       <c r="L34" t="n">
-        <v>103.23</v>
+        <v>143.13</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:35:02</t>
+          <t>05:39:30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>6.67</v>
+        <v>6.84</v>
       </c>
       <c r="F35" t="n">
-        <v>15.78</v>
+        <v>15.9</v>
       </c>
       <c r="G35" t="n">
-        <v>339.5</v>
+        <v>321</v>
       </c>
       <c r="H35" t="n">
-        <v>90.3</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-33.54</v>
+        <v>80.14</v>
       </c>
       <c r="K35" t="n">
-        <v>-177.13</v>
+        <v>-145.41</v>
       </c>
       <c r="L35" t="n">
-        <v>180.27</v>
+        <v>166.03</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:36:48</t>
+          <t>05:41:08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>5.64</v>
+        <v>6.48</v>
       </c>
       <c r="F36" t="n">
-        <v>16.22</v>
+        <v>14.65</v>
       </c>
       <c r="G36" t="n">
-        <v>322.3</v>
+        <v>329.1</v>
       </c>
       <c r="H36" t="n">
-        <v>100</v>
+        <v>94.8</v>
       </c>
       <c r="I36" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-63.77</v>
+        <v>-106.01</v>
       </c>
       <c r="K36" t="n">
-        <v>-162.99</v>
+        <v>-100.65</v>
       </c>
       <c r="L36" t="n">
-        <v>175.03</v>
+        <v>146.18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:39:19</t>
+          <t>05:43:26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>6.18</v>
+        <v>6.46</v>
       </c>
       <c r="F37" t="n">
-        <v>16.51</v>
+        <v>14.05</v>
       </c>
       <c r="G37" t="n">
-        <v>333.1</v>
+        <v>331.7</v>
       </c>
       <c r="H37" t="n">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-38.18</v>
+        <v>-139.53</v>
       </c>
       <c r="K37" t="n">
-        <v>299.63</v>
+        <v>-85.23999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>302.05</v>
+        <v>163.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:44:41</t>
+          <t>05:47:17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>6.37</v>
+        <v>7.28</v>
       </c>
       <c r="F38" t="n">
-        <v>16.15</v>
+        <v>18.4</v>
       </c>
       <c r="G38" t="n">
-        <v>323.3</v>
+        <v>325.8</v>
       </c>
       <c r="H38" t="n">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-145.87</v>
+        <v>-284.62</v>
       </c>
       <c r="K38" t="n">
-        <v>383.86</v>
+        <v>-232.66</v>
       </c>
       <c r="L38" t="n">
-        <v>410.64</v>
+        <v>367.62</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:46:51</t>
+          <t>05:48:51</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>6.28</v>
+        <v>6.15</v>
       </c>
       <c r="F39" t="n">
-        <v>15.92</v>
+        <v>15.64</v>
       </c>
       <c r="G39" t="n">
-        <v>319.4</v>
+        <v>333.3</v>
       </c>
       <c r="H39" t="n">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J39" t="n">
-        <v>199.48</v>
+        <v>106.13</v>
       </c>
       <c r="K39" t="n">
-        <v>-128.68</v>
+        <v>347.94</v>
       </c>
       <c r="L39" t="n">
-        <v>237.38</v>
+        <v>363.76</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:48:20</t>
+          <t>05:50:11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>6.68</v>
+        <v>5.82</v>
       </c>
       <c r="F40" t="n">
-        <v>16.8</v>
+        <v>14.3</v>
       </c>
       <c r="G40" t="n">
-        <v>336.6</v>
+        <v>330.3</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>212.13</v>
+        <v>-251.67</v>
       </c>
       <c r="K40" t="n">
-        <v>177.09</v>
+        <v>-110.96</v>
       </c>
       <c r="L40" t="n">
-        <v>276.34</v>
+        <v>275.04</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:52:48</t>
+          <t>05:54:11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>6.82</v>
+        <v>5.99</v>
       </c>
       <c r="F41" t="n">
-        <v>15.77</v>
+        <v>14.22</v>
       </c>
       <c r="G41" t="n">
-        <v>321.4</v>
+        <v>324.2</v>
       </c>
       <c r="H41" t="n">
-        <v>94.8</v>
+        <v>96</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-82.05</v>
+        <v>-300.32</v>
       </c>
       <c r="K41" t="n">
-        <v>-407.66</v>
+        <v>153.01</v>
       </c>
       <c r="L41" t="n">
-        <v>415.84</v>
+        <v>337.05</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:53:41</t>
+          <t>05:55:52</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>5.77</v>
+        <v>6.51</v>
       </c>
       <c r="F42" t="n">
-        <v>15.98</v>
+        <v>18.02</v>
       </c>
       <c r="G42" t="n">
-        <v>327.1</v>
+        <v>335.3</v>
       </c>
       <c r="H42" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>7.83</v>
+        <v>339.99</v>
       </c>
       <c r="K42" t="n">
-        <v>504.89</v>
+        <v>131.6</v>
       </c>
       <c r="L42" t="n">
-        <v>504.95</v>
+        <v>364.56</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:55:10</t>
+          <t>05:56:34</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>6.7</v>
+        <v>6.34</v>
       </c>
       <c r="F43" t="n">
-        <v>16.04</v>
+        <v>14.9</v>
       </c>
       <c r="G43" t="n">
-        <v>327.6</v>
+        <v>336.4</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
       </c>
       <c r="I43" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>-83.88</v>
+        <v>-545.89</v>
       </c>
       <c r="K43" t="n">
-        <v>-460.8</v>
+        <v>442.7</v>
       </c>
       <c r="L43" t="n">
-        <v>468.38</v>
+        <v>702.84</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:03:22</t>
+          <t>06:08:15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>6.69</v>
+        <v>6.47</v>
       </c>
       <c r="F44" t="n">
-        <v>15.25</v>
+        <v>17.15</v>
       </c>
       <c r="G44" t="n">
-        <v>330.6</v>
+        <v>330.3</v>
       </c>
       <c r="H44" t="n">
-        <v>100</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>38.76</v>
+        <v>94.79000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>-50.36</v>
+        <v>20.59</v>
       </c>
       <c r="L44" t="n">
-        <v>63.55</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:05:04</t>
+          <t>06:09:44</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>6.95</v>
+        <v>5.92</v>
       </c>
       <c r="F45" t="n">
-        <v>16.1</v>
+        <v>10.52</v>
       </c>
       <c r="G45" t="n">
-        <v>341.3</v>
+        <v>325.7</v>
       </c>
       <c r="H45" t="n">
-        <v>97.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>63.07</v>
+        <v>40.4</v>
       </c>
       <c r="K45" t="n">
-        <v>-135.52</v>
+        <v>105.58</v>
       </c>
       <c r="L45" t="n">
-        <v>149.48</v>
+        <v>113.05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:07:30</t>
+          <t>06:11:23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>6.61</v>
+        <v>5.46</v>
       </c>
       <c r="F46" t="n">
-        <v>16.36</v>
+        <v>16.25</v>
       </c>
       <c r="G46" t="n">
-        <v>327.5</v>
+        <v>324.3</v>
       </c>
       <c r="H46" t="n">
-        <v>98.2</v>
+        <v>97.7</v>
       </c>
       <c r="I46" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>-111.32</v>
+        <v>62.16</v>
       </c>
       <c r="K46" t="n">
-        <v>30.05</v>
+        <v>56.38</v>
       </c>
       <c r="L46" t="n">
-        <v>115.31</v>
+        <v>83.92</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:12:07</t>
+          <t>06:15:53</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>7.5</v>
+        <v>6.21</v>
       </c>
       <c r="F47" t="n">
-        <v>16.26</v>
+        <v>16.78</v>
       </c>
       <c r="G47" t="n">
-        <v>336</v>
+        <v>317.8</v>
       </c>
       <c r="H47" t="n">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>-77.5</v>
+        <v>99.62</v>
       </c>
       <c r="K47" t="n">
-        <v>129.19</v>
+        <v>-77.03</v>
       </c>
       <c r="L47" t="n">
-        <v>150.65</v>
+        <v>125.93</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:13:08</t>
+          <t>06:17:24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>5.99</v>
+        <v>7.18</v>
       </c>
       <c r="F48" t="n">
-        <v>16.6</v>
+        <v>17.52</v>
       </c>
       <c r="G48" t="n">
-        <v>324.8</v>
+        <v>319.9</v>
       </c>
       <c r="H48" t="n">
-        <v>94.2</v>
+        <v>89.8</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>102.14</v>
+        <v>138.79</v>
       </c>
       <c r="K48" t="n">
-        <v>94.38</v>
+        <v>-37.11</v>
       </c>
       <c r="L48" t="n">
-        <v>139.07</v>
+        <v>143.67</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:14:01</t>
+          <t>06:19:30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>6.5</v>
+        <v>6.02</v>
       </c>
       <c r="F49" t="n">
-        <v>15.77</v>
+        <v>12.37</v>
       </c>
       <c r="G49" t="n">
-        <v>343.2</v>
+        <v>350.9</v>
       </c>
       <c r="H49" t="n">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>15.25</v>
+        <v>-119.98</v>
       </c>
       <c r="K49" t="n">
-        <v>-123.04</v>
+        <v>-54.19</v>
       </c>
       <c r="L49" t="n">
-        <v>123.98</v>
+        <v>131.65</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:18:44</t>
+          <t>06:23:28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>6.4</v>
+        <v>7.43</v>
       </c>
       <c r="F50" t="n">
-        <v>16.77</v>
+        <v>18.24</v>
       </c>
       <c r="G50" t="n">
-        <v>322.1</v>
+        <v>330.5</v>
       </c>
       <c r="H50" t="n">
         <v>100</v>
       </c>
       <c r="I50" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>41.03</v>
+        <v>139.05</v>
       </c>
       <c r="K50" t="n">
-        <v>154.4</v>
+        <v>160.19</v>
       </c>
       <c r="L50" t="n">
-        <v>159.76</v>
+        <v>212.12</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:20:50</t>
+          <t>06:25:03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>6.5</v>
+        <v>6.36</v>
       </c>
       <c r="F51" t="n">
-        <v>15.73</v>
+        <v>15.05</v>
       </c>
       <c r="G51" t="n">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H51" t="n">
-        <v>100</v>
+        <v>99.2</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-122.24</v>
+        <v>-157.88</v>
       </c>
       <c r="K51" t="n">
-        <v>-28.87</v>
+        <v>151.09</v>
       </c>
       <c r="L51" t="n">
-        <v>125.6</v>
+        <v>218.53</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:22:00</t>
+          <t>06:26:32</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>6.47</v>
+        <v>5.3</v>
       </c>
       <c r="F52" t="n">
-        <v>15.1</v>
+        <v>11.94</v>
       </c>
       <c r="G52" t="n">
-        <v>336.1</v>
+        <v>339.2</v>
       </c>
       <c r="H52" t="n">
-        <v>95.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I52" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-77.20999999999999</v>
+        <v>-33.89</v>
       </c>
       <c r="K52" t="n">
-        <v>224.79</v>
+        <v>189.45</v>
       </c>
       <c r="L52" t="n">
-        <v>237.68</v>
+        <v>192.46</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:26:41</t>
+          <t>06:31:49</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>7.9</v>
+        <v>7.13</v>
       </c>
       <c r="F53" t="n">
-        <v>16.46</v>
+        <v>18.4</v>
       </c>
       <c r="G53" t="n">
-        <v>337.2</v>
+        <v>323.2</v>
       </c>
       <c r="H53" t="n">
         <v>100</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>57.94</v>
+        <v>-47.08</v>
       </c>
       <c r="K53" t="n">
-        <v>-288.51</v>
+        <v>-58.17</v>
       </c>
       <c r="L53" t="n">
-        <v>294.27</v>
+        <v>74.83</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:28:21</t>
+          <t>06:33:41</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>5.89</v>
+        <v>6.41</v>
       </c>
       <c r="F54" t="n">
-        <v>15.8</v>
+        <v>13.65</v>
       </c>
       <c r="G54" t="n">
-        <v>328.1</v>
+        <v>330.6</v>
       </c>
       <c r="H54" t="n">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="I54" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>298.01</v>
+        <v>-2.83</v>
       </c>
       <c r="K54" t="n">
-        <v>64.14</v>
+        <v>367.94</v>
       </c>
       <c r="L54" t="n">
-        <v>304.83</v>
+        <v>367.95</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:30:08</t>
+          <t>06:34:39</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>5.73</v>
+        <v>6.99</v>
       </c>
       <c r="F55" t="n">
-        <v>15.8</v>
+        <v>16.17</v>
       </c>
       <c r="G55" t="n">
-        <v>325.3</v>
+        <v>324.1</v>
       </c>
       <c r="H55" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-208.49</v>
+        <v>-225.03</v>
       </c>
       <c r="K55" t="n">
-        <v>-117.68</v>
+        <v>221.54</v>
       </c>
       <c r="L55" t="n">
-        <v>239.41</v>
+        <v>315.79</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:34:50</t>
+          <t>06:38:26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>5.75</v>
+        <v>6.3</v>
       </c>
       <c r="F56" t="n">
-        <v>16.09</v>
+        <v>17.63</v>
       </c>
       <c r="G56" t="n">
-        <v>326.1</v>
+        <v>328.9</v>
       </c>
       <c r="H56" t="n">
         <v>100</v>
       </c>
       <c r="I56" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>463.07</v>
+        <v>-324.88</v>
       </c>
       <c r="K56" t="n">
-        <v>38.1</v>
+        <v>-126.53</v>
       </c>
       <c r="L56" t="n">
-        <v>464.63</v>
+        <v>348.65</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:35:41</t>
+          <t>06:40:29</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>6.95</v>
+        <v>5.96</v>
       </c>
       <c r="F57" t="n">
-        <v>16.43</v>
+        <v>16.04</v>
       </c>
       <c r="G57" t="n">
-        <v>330.1</v>
+        <v>326.7</v>
       </c>
       <c r="H57" t="n">
-        <v>95.5</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>-385.94</v>
+        <v>19.97</v>
       </c>
       <c r="K57" t="n">
-        <v>-111.19</v>
+        <v>403.28</v>
       </c>
       <c r="L57" t="n">
-        <v>401.64</v>
+        <v>403.78</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:36:57</t>
+          <t>06:41:26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>6.64</v>
+        <v>7.5</v>
       </c>
       <c r="F58" t="n">
-        <v>15.65</v>
+        <v>16.84</v>
       </c>
       <c r="G58" t="n">
-        <v>344.6</v>
+        <v>341</v>
       </c>
       <c r="H58" t="n">
         <v>100</v>
       </c>
       <c r="I58" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>64.29000000000001</v>
+        <v>283.61</v>
       </c>
       <c r="K58" t="n">
-        <v>601.6799999999999</v>
+        <v>249.38</v>
       </c>
       <c r="L58" t="n">
-        <v>605.11</v>
+        <v>377.66</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:45:11</t>
+          <t>06:54:00</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>5.8</v>
+        <v>7.03</v>
       </c>
       <c r="F59" t="n">
-        <v>16.02</v>
+        <v>17.24</v>
       </c>
       <c r="G59" t="n">
-        <v>334.4</v>
+        <v>335.8</v>
       </c>
       <c r="H59" t="n">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-55.46</v>
+        <v>14.52</v>
       </c>
       <c r="K59" t="n">
-        <v>68.73999999999999</v>
+        <v>-74.91</v>
       </c>
       <c r="L59" t="n">
-        <v>88.33</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:47:16</t>
+          <t>06:56:13</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>7.27</v>
+        <v>6.53</v>
       </c>
       <c r="F60" t="n">
-        <v>16.32</v>
+        <v>15.9</v>
       </c>
       <c r="G60" t="n">
-        <v>328.2</v>
+        <v>337</v>
       </c>
       <c r="H60" t="n">
-        <v>98.40000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="I60" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-105.1</v>
+        <v>24.01</v>
       </c>
       <c r="K60" t="n">
-        <v>85.39</v>
+        <v>-109.67</v>
       </c>
       <c r="L60" t="n">
-        <v>135.42</v>
+        <v>112.27</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:49:52</t>
+          <t>06:58:16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>6.07</v>
+        <v>6.67</v>
       </c>
       <c r="F61" t="n">
-        <v>15.21</v>
+        <v>17.78</v>
       </c>
       <c r="G61" t="n">
-        <v>328.9</v>
+        <v>320.6</v>
       </c>
       <c r="H61" t="n">
         <v>100</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-85.39</v>
+        <v>-31.09</v>
       </c>
       <c r="K61" t="n">
-        <v>9.35</v>
+        <v>-94.31</v>
       </c>
       <c r="L61" t="n">
-        <v>85.90000000000001</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:55:30</t>
+          <t>07:02:36</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>6.39</v>
+        <v>6.1</v>
       </c>
       <c r="F62" t="n">
-        <v>16.39</v>
+        <v>16.4</v>
       </c>
       <c r="G62" t="n">
-        <v>321.7</v>
+        <v>347</v>
       </c>
       <c r="H62" t="n">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="I62" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>167.82</v>
+        <v>-85.42</v>
       </c>
       <c r="K62" t="n">
-        <v>-35.21</v>
+        <v>41.86</v>
       </c>
       <c r="L62" t="n">
-        <v>171.47</v>
+        <v>95.12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>06:56:55</t>
+          <t>07:05:11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>6.33</v>
+        <v>6.47</v>
       </c>
       <c r="F63" t="n">
-        <v>16.28</v>
+        <v>15.97</v>
       </c>
       <c r="G63" t="n">
-        <v>329.8</v>
+        <v>324.8</v>
       </c>
       <c r="H63" t="n">
-        <v>97.7</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-54.79</v>
+        <v>-37.96</v>
       </c>
       <c r="K63" t="n">
-        <v>-119.67</v>
+        <v>86.78</v>
       </c>
       <c r="L63" t="n">
-        <v>131.61</v>
+        <v>94.72</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>06:57:53</t>
+          <t>07:05:58</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>6.54</v>
+        <v>7.23</v>
       </c>
       <c r="F64" t="n">
-        <v>16.04</v>
+        <v>17.92</v>
       </c>
       <c r="G64" t="n">
-        <v>325.9</v>
+        <v>322.5</v>
       </c>
       <c r="H64" t="n">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>-105.04</v>
+        <v>-118.59</v>
       </c>
       <c r="K64" t="n">
-        <v>31.76</v>
+        <v>111.43</v>
       </c>
       <c r="L64" t="n">
-        <v>109.74</v>
+        <v>162.73</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:03:19</t>
+          <t>07:11:36</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.95</v>
+        <v>6.95</v>
       </c>
       <c r="F65" t="n">
-        <v>15.71</v>
+        <v>14.96</v>
       </c>
       <c r="G65" t="n">
-        <v>317.5</v>
+        <v>319.7</v>
       </c>
       <c r="H65" t="n">
         <v>96.40000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-158.26</v>
+        <v>-82.98999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>-156.2</v>
+        <v>176.01</v>
       </c>
       <c r="L65" t="n">
-        <v>222.37</v>
+        <v>194.6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:04:41</t>
+          <t>07:12:12</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>6.53</v>
+        <v>6.32</v>
       </c>
       <c r="F66" t="n">
-        <v>15.87</v>
+        <v>15.1</v>
       </c>
       <c r="G66" t="n">
-        <v>333</v>
+        <v>323.1</v>
       </c>
       <c r="H66" t="n">
-        <v>97.2</v>
+        <v>100</v>
       </c>
       <c r="I66" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-175.12</v>
+        <v>-14.73</v>
       </c>
       <c r="K66" t="n">
-        <v>86.44</v>
+        <v>217.35</v>
       </c>
       <c r="L66" t="n">
-        <v>195.29</v>
+        <v>217.85</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:07:08</t>
+          <t>07:13:33</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>6.72</v>
+        <v>6.98</v>
       </c>
       <c r="F67" t="n">
-        <v>15.79</v>
+        <v>15.06</v>
       </c>
       <c r="G67" t="n">
-        <v>317.6</v>
+        <v>322.8</v>
       </c>
       <c r="H67" t="n">
-        <v>100</v>
+        <v>96.8</v>
       </c>
       <c r="I67" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-201.31</v>
+        <v>-0.3</v>
       </c>
       <c r="K67" t="n">
-        <v>29.68</v>
+        <v>175.89</v>
       </c>
       <c r="L67" t="n">
-        <v>203.49</v>
+        <v>175.89</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:09:54</t>
+          <t>07:18:42</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>6.8</v>
+        <v>7.36</v>
       </c>
       <c r="F68" t="n">
-        <v>15.51</v>
+        <v>16.4</v>
       </c>
       <c r="G68" t="n">
-        <v>333.3</v>
+        <v>334.1</v>
       </c>
       <c r="H68" t="n">
         <v>100</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>112.59</v>
+        <v>-218.12</v>
       </c>
       <c r="K68" t="n">
-        <v>354.32</v>
+        <v>142.82</v>
       </c>
       <c r="L68" t="n">
-        <v>371.78</v>
+        <v>260.72</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:12:03</t>
+          <t>07:19:32</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>6.61</v>
+        <v>7.27</v>
       </c>
       <c r="F69" t="n">
-        <v>15.27</v>
+        <v>15.64</v>
       </c>
       <c r="G69" t="n">
-        <v>316.6</v>
+        <v>315.7</v>
       </c>
       <c r="H69" t="n">
         <v>100</v>
       </c>
       <c r="I69" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-386.02</v>
+        <v>145.04</v>
       </c>
       <c r="K69" t="n">
-        <v>2.08</v>
+        <v>-355.14</v>
       </c>
       <c r="L69" t="n">
-        <v>386.03</v>
+        <v>383.61</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:14:09</t>
+          <t>07:21:09</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>7.15</v>
+        <v>6.18</v>
       </c>
       <c r="F70" t="n">
-        <v>16.72</v>
+        <v>17.93</v>
       </c>
       <c r="G70" t="n">
-        <v>319.4</v>
+        <v>323.5</v>
       </c>
       <c r="H70" t="n">
-        <v>95.7</v>
+        <v>100</v>
       </c>
       <c r="I70" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>-285.21</v>
+        <v>28.4</v>
       </c>
       <c r="K70" t="n">
-        <v>244.65</v>
+        <v>16.5</v>
       </c>
       <c r="L70" t="n">
-        <v>375.76</v>
+        <v>32.85</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:17:32</t>
+          <t>07:26:35</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>6.87</v>
+        <v>5.92</v>
       </c>
       <c r="F71" t="n">
-        <v>16.08</v>
+        <v>12.04</v>
       </c>
       <c r="G71" t="n">
-        <v>314.9</v>
+        <v>337.5</v>
       </c>
       <c r="H71" t="n">
-        <v>100</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>350.57</v>
+        <v>-377.58</v>
       </c>
       <c r="K71" t="n">
-        <v>431.33</v>
+        <v>-140.3</v>
       </c>
       <c r="L71" t="n">
-        <v>555.83</v>
+        <v>402.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:19:40</t>
+          <t>07:29:01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>6.22</v>
+        <v>5.97</v>
       </c>
       <c r="F72" t="n">
-        <v>16.08</v>
+        <v>15.87</v>
       </c>
       <c r="G72" t="n">
-        <v>317</v>
+        <v>327.4</v>
       </c>
       <c r="H72" t="n">
-        <v>98.7</v>
+        <v>98.2</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>-415.63</v>
+        <v>214.01</v>
       </c>
       <c r="K72" t="n">
-        <v>-42.07</v>
+        <v>500.26</v>
       </c>
       <c r="L72" t="n">
-        <v>417.76</v>
+        <v>544.11</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:21:51</t>
+          <t>07:30:20</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>7.71</v>
+        <v>5.63</v>
       </c>
       <c r="F73" t="n">
-        <v>16.1</v>
+        <v>14.36</v>
       </c>
       <c r="G73" t="n">
-        <v>333.8</v>
+        <v>327.7</v>
       </c>
       <c r="H73" t="n">
-        <v>91</v>
+        <v>95.8</v>
       </c>
       <c r="I73" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-613.1</v>
+        <v>-407.13</v>
       </c>
       <c r="K73" t="n">
-        <v>3.12</v>
+        <v>-49.66</v>
       </c>
       <c r="L73" t="n">
-        <v>613.11</v>
+        <v>410.14</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:31:35</t>
+          <t>07:38:41</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>6.09</v>
+        <v>7.11</v>
       </c>
       <c r="F74" t="n">
-        <v>15.72</v>
+        <v>17.09</v>
       </c>
       <c r="G74" t="n">
-        <v>334</v>
+        <v>315.3</v>
       </c>
       <c r="H74" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>55.01</v>
+        <v>46.36</v>
       </c>
       <c r="K74" t="n">
-        <v>-94.40000000000001</v>
+        <v>68.72</v>
       </c>
       <c r="L74" t="n">
-        <v>109.26</v>
+        <v>82.90000000000001</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:32:59</t>
+          <t>07:40:54</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>6.9</v>
+        <v>6.57</v>
       </c>
       <c r="F75" t="n">
-        <v>16.61</v>
+        <v>18.4</v>
       </c>
       <c r="G75" t="n">
-        <v>320.9</v>
+        <v>329.6</v>
       </c>
       <c r="H75" t="n">
-        <v>98</v>
+        <v>95.5</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J75" t="n">
-        <v>-92.47</v>
+        <v>82.58</v>
       </c>
       <c r="K75" t="n">
-        <v>4.81</v>
+        <v>-15.75</v>
       </c>
       <c r="L75" t="n">
-        <v>92.59</v>
+        <v>84.06999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:34:22</t>
+          <t>07:43:06</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>6.41</v>
+        <v>7.44</v>
       </c>
       <c r="F76" t="n">
-        <v>16.18</v>
+        <v>18.04</v>
       </c>
       <c r="G76" t="n">
-        <v>338.8</v>
+        <v>324.2</v>
       </c>
       <c r="H76" t="n">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>78.68000000000001</v>
+        <v>66.92</v>
       </c>
       <c r="K76" t="n">
-        <v>-43.52</v>
+        <v>43.03</v>
       </c>
       <c r="L76" t="n">
-        <v>89.92</v>
+        <v>79.56</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:40:07</t>
+          <t>07:47:44</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>6.66</v>
+        <v>6.51</v>
       </c>
       <c r="F77" t="n">
-        <v>15.99</v>
+        <v>16.28</v>
       </c>
       <c r="G77" t="n">
-        <v>317.1</v>
+        <v>326</v>
       </c>
       <c r="H77" t="n">
-        <v>97.3</v>
+        <v>100</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-6.85</v>
+        <v>-86.27</v>
       </c>
       <c r="K77" t="n">
-        <v>-94.5</v>
+        <v>14.76</v>
       </c>
       <c r="L77" t="n">
-        <v>94.73999999999999</v>
+        <v>87.53</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:42:15</t>
+          <t>07:49:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>6.46</v>
+        <v>7.22</v>
       </c>
       <c r="F78" t="n">
-        <v>16.17</v>
+        <v>18.4</v>
       </c>
       <c r="G78" t="n">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="H78" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>18.24</v>
+        <v>48.92</v>
       </c>
       <c r="K78" t="n">
-        <v>-101.64</v>
+        <v>121.64</v>
       </c>
       <c r="L78" t="n">
-        <v>103.26</v>
+        <v>131.11</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:43:07</t>
+          <t>07:50:33</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>6.75</v>
+        <v>7.55</v>
       </c>
       <c r="F79" t="n">
-        <v>16.51</v>
+        <v>18.4</v>
       </c>
       <c r="G79" t="n">
-        <v>321.3</v>
+        <v>327.8</v>
       </c>
       <c r="H79" t="n">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="I79" t="n">
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-113.24</v>
+        <v>43.29</v>
       </c>
       <c r="K79" t="n">
-        <v>-16.07</v>
+        <v>-127.7</v>
       </c>
       <c r="L79" t="n">
-        <v>114.37</v>
+        <v>134.83</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:47:23</t>
+          <t>07:54:58</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>7.47</v>
+        <v>6.27</v>
       </c>
       <c r="F80" t="n">
-        <v>15.51</v>
+        <v>14.69</v>
       </c>
       <c r="G80" t="n">
-        <v>319.8</v>
+        <v>320.4</v>
       </c>
       <c r="H80" t="n">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="I80" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.4</v>
+        <v>119.94</v>
       </c>
       <c r="K80" t="n">
-        <v>-200.8</v>
+        <v>198.69</v>
       </c>
       <c r="L80" t="n">
-        <v>200.97</v>
+        <v>232.08</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:48:02</t>
+          <t>07:56:56</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>6.64</v>
+        <v>7.69</v>
       </c>
       <c r="F81" t="n">
-        <v>16.67</v>
+        <v>18.4</v>
       </c>
       <c r="G81" t="n">
-        <v>315</v>
+        <v>337.6</v>
       </c>
       <c r="H81" t="n">
         <v>100</v>
       </c>
       <c r="I81" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.94</v>
+        <v>-291.42</v>
       </c>
       <c r="K81" t="n">
-        <v>211.29</v>
+        <v>-34.99</v>
       </c>
       <c r="L81" t="n">
-        <v>211.4</v>
+        <v>293.51</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:49:54</t>
+          <t>07:58:26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>7.22</v>
+        <v>6.71</v>
       </c>
       <c r="F82" t="n">
-        <v>15.47</v>
+        <v>18.35</v>
       </c>
       <c r="G82" t="n">
-        <v>326.5</v>
+        <v>329.3</v>
       </c>
       <c r="H82" t="n">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>220.45</v>
+        <v>-69.81</v>
       </c>
       <c r="K82" t="n">
-        <v>22.63</v>
+        <v>143.54</v>
       </c>
       <c r="L82" t="n">
-        <v>221.6</v>
+        <v>159.61</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>07:54:14</t>
+          <t>08:02:21</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>7.76</v>
+        <v>7.49</v>
       </c>
       <c r="F83" t="n">
-        <v>16</v>
+        <v>18.4</v>
       </c>
       <c r="G83" t="n">
-        <v>333.3</v>
+        <v>325.4</v>
       </c>
       <c r="H83" t="n">
-        <v>92.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>-147.08</v>
+        <v>-378.32</v>
       </c>
       <c r="K83" t="n">
-        <v>491.09</v>
+        <v>39.11</v>
       </c>
       <c r="L83" t="n">
-        <v>512.64</v>
+        <v>380.34</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>07:56:07</t>
+          <t>08:04:16</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>6.91</v>
+        <v>7.76</v>
       </c>
       <c r="F84" t="n">
-        <v>16.02</v>
+        <v>18.4</v>
       </c>
       <c r="G84" t="n">
-        <v>325.8</v>
+        <v>332.7</v>
       </c>
       <c r="H84" t="n">
-        <v>94.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="I84" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>-88.63</v>
+        <v>-329.94</v>
       </c>
       <c r="K84" t="n">
-        <v>-276.37</v>
+        <v>245.54</v>
       </c>
       <c r="L84" t="n">
-        <v>290.23</v>
+        <v>411.28</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>07:57:28</t>
+          <t>08:05:06</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>7.55</v>
+        <v>6.88</v>
       </c>
       <c r="F85" t="n">
-        <v>15.9</v>
+        <v>18.4</v>
       </c>
       <c r="G85" t="n">
-        <v>337.7</v>
+        <v>327.4</v>
       </c>
       <c r="H85" t="n">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>89.15000000000001</v>
+        <v>53.73</v>
       </c>
       <c r="K85" t="n">
-        <v>465.91</v>
+        <v>422.92</v>
       </c>
       <c r="L85" t="n">
-        <v>474.36</v>
+        <v>426.31</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:01:42</t>
+          <t>08:09:36</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>6.92</v>
+        <v>6.95</v>
       </c>
       <c r="F86" t="n">
-        <v>16.32</v>
+        <v>16.83</v>
       </c>
       <c r="G86" t="n">
-        <v>321.1</v>
+        <v>335.9</v>
       </c>
       <c r="H86" t="n">
-        <v>97.90000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>433.26</v>
+        <v>418.32</v>
       </c>
       <c r="K86" t="n">
-        <v>-19.52</v>
+        <v>93.16</v>
       </c>
       <c r="L86" t="n">
-        <v>433.7</v>
+        <v>428.57</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:02:47</t>
+          <t>08:11:46</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>6.02</v>
+        <v>6.06</v>
       </c>
       <c r="F87" t="n">
-        <v>15.08</v>
+        <v>10.41</v>
       </c>
       <c r="G87" t="n">
-        <v>331.3</v>
+        <v>311</v>
       </c>
       <c r="H87" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-419.99</v>
+        <v>-404.97</v>
       </c>
       <c r="K87" t="n">
-        <v>-15.54</v>
+        <v>5.8</v>
       </c>
       <c r="L87" t="n">
-        <v>420.28</v>
+        <v>405.02</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:04:03</t>
+          <t>08:12:45</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>7.61</v>
+        <v>7.65</v>
       </c>
       <c r="F88" t="n">
-        <v>16.71</v>
+        <v>18.4</v>
       </c>
       <c r="G88" t="n">
-        <v>328</v>
+        <v>343.6</v>
       </c>
       <c r="H88" t="n">
-        <v>98.59999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="I88" t="n">
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>-532.34</v>
+        <v>-550.12</v>
       </c>
       <c r="K88" t="n">
-        <v>-144.74</v>
+        <v>-57.73</v>
       </c>
       <c r="L88" t="n">
-        <v>551.66</v>
+        <v>553.14</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-01.xlsx
+++ b/output/2025-07-01.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>104.89</v>
+        <v>98.98</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="L14" t="n">
-        <v>104.89</v>
+        <v>98.98</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-69.62</v>
+        <v>-64.76000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-52.81</v>
+        <v>-49.12</v>
       </c>
       <c r="L15" t="n">
-        <v>87.39</v>
+        <v>81.28</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>-64.70999999999999</v>
+        <v>-62.63</v>
       </c>
       <c r="K16" t="n">
-        <v>18.84</v>
+        <v>18.24</v>
       </c>
       <c r="L16" t="n">
-        <v>67.39</v>
+        <v>65.23999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-91.09999999999999</v>
+        <v>-86.34</v>
       </c>
       <c r="K17" t="n">
-        <v>-31.37</v>
+        <v>-29.73</v>
       </c>
       <c r="L17" t="n">
-        <v>96.34999999999999</v>
+        <v>91.31999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>68.5</v>
+        <v>71.39</v>
       </c>
       <c r="K18" t="n">
-        <v>-86.42</v>
+        <v>-90.06</v>
       </c>
       <c r="L18" t="n">
-        <v>110.27</v>
+        <v>114.92</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>44.94</v>
+        <v>46.95</v>
       </c>
       <c r="K19" t="n">
-        <v>163.27</v>
+        <v>170.57</v>
       </c>
       <c r="L19" t="n">
-        <v>169.34</v>
+        <v>176.92</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>68.91</v>
+        <v>71.23</v>
       </c>
       <c r="K20" t="n">
-        <v>164.24</v>
+        <v>169.76</v>
       </c>
       <c r="L20" t="n">
-        <v>178.12</v>
+        <v>184.09</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.04</v>
+        <v>-7.28</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.44</v>
+        <v>-0.45</v>
       </c>
       <c r="L21" t="n">
-        <v>7.06</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-38.58</v>
+        <v>-39.86</v>
       </c>
       <c r="K22" t="n">
-        <v>168.75</v>
+        <v>174.36</v>
       </c>
       <c r="L22" t="n">
-        <v>173.1</v>
+        <v>178.86</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-155.47</v>
+        <v>-156.9</v>
       </c>
       <c r="K23" t="n">
-        <v>216.6</v>
+        <v>218.59</v>
       </c>
       <c r="L23" t="n">
-        <v>266.62</v>
+        <v>269.07</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>175.33</v>
+        <v>169.94</v>
       </c>
       <c r="K24" t="n">
-        <v>14.17</v>
+        <v>13.74</v>
       </c>
       <c r="L24" t="n">
-        <v>175.9</v>
+        <v>170.5</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-201.22</v>
+        <v>-203.59</v>
       </c>
       <c r="K25" t="n">
-        <v>-224.63</v>
+        <v>-227.27</v>
       </c>
       <c r="L25" t="n">
-        <v>301.58</v>
+        <v>305.13</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-599.24</v>
+        <v>-601.17</v>
       </c>
       <c r="K26" t="n">
-        <v>-23.7</v>
+        <v>-23.77</v>
       </c>
       <c r="L26" t="n">
-        <v>599.7</v>
+        <v>601.64</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-373.06</v>
+        <v>-407.62</v>
       </c>
       <c r="K27" t="n">
-        <v>185.13</v>
+        <v>202.27</v>
       </c>
       <c r="L27" t="n">
-        <v>416.47</v>
+        <v>455.05</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-255.69</v>
+        <v>-271.24</v>
       </c>
       <c r="K28" t="n">
-        <v>-256.9</v>
+        <v>-272.52</v>
       </c>
       <c r="L28" t="n">
-        <v>362.45</v>
+        <v>384.49</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.220000000000001</v>
+        <v>-8.44</v>
       </c>
       <c r="K29" t="n">
-        <v>-11.74</v>
+        <v>-12.06</v>
       </c>
       <c r="L29" t="n">
-        <v>14.33</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>4</v>
+        <v>3.64</v>
       </c>
       <c r="K30" t="n">
-        <v>87.23</v>
+        <v>79.38</v>
       </c>
       <c r="L30" t="n">
-        <v>87.31999999999999</v>
+        <v>79.47</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>88.72</v>
+        <v>87.59</v>
       </c>
       <c r="K31" t="n">
-        <v>-18.19</v>
+        <v>-17.96</v>
       </c>
       <c r="L31" t="n">
-        <v>90.56999999999999</v>
+        <v>89.41</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>-66.65000000000001</v>
+        <v>-68.18000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>76.05</v>
+        <v>77.8</v>
       </c>
       <c r="L32" t="n">
-        <v>101.12</v>
+        <v>103.44</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-40.66</v>
+        <v>-42.29</v>
       </c>
       <c r="K33" t="n">
-        <v>114.83</v>
+        <v>119.42</v>
       </c>
       <c r="L33" t="n">
-        <v>121.82</v>
+        <v>126.69</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>28.85</v>
+        <v>28.51</v>
       </c>
       <c r="K34" t="n">
-        <v>-140.19</v>
+        <v>-138.53</v>
       </c>
       <c r="L34" t="n">
-        <v>143.13</v>
+        <v>141.43</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>80.14</v>
+        <v>81.28</v>
       </c>
       <c r="K35" t="n">
-        <v>-145.41</v>
+        <v>-147.47</v>
       </c>
       <c r="L35" t="n">
-        <v>166.03</v>
+        <v>168.39</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-106.01</v>
+        <v>-111.45</v>
       </c>
       <c r="K36" t="n">
-        <v>-100.65</v>
+        <v>-105.81</v>
       </c>
       <c r="L36" t="n">
-        <v>146.18</v>
+        <v>153.68</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-139.53</v>
+        <v>-141.55</v>
       </c>
       <c r="K37" t="n">
-        <v>-85.23999999999999</v>
+        <v>-86.48</v>
       </c>
       <c r="L37" t="n">
-        <v>163.5</v>
+        <v>165.88</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-284.62</v>
+        <v>-288.42</v>
       </c>
       <c r="K38" t="n">
-        <v>-232.66</v>
+        <v>-235.77</v>
       </c>
       <c r="L38" t="n">
-        <v>367.62</v>
+        <v>372.52</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>26</v>
       </c>
       <c r="J39" t="n">
-        <v>106.13</v>
+        <v>102.9</v>
       </c>
       <c r="K39" t="n">
-        <v>347.94</v>
+        <v>337.34</v>
       </c>
       <c r="L39" t="n">
-        <v>363.76</v>
+        <v>352.69</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-251.67</v>
+        <v>-243.85</v>
       </c>
       <c r="K40" t="n">
-        <v>-110.96</v>
+        <v>-107.52</v>
       </c>
       <c r="L40" t="n">
-        <v>275.04</v>
+        <v>266.5</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>-300.32</v>
+        <v>-300.96</v>
       </c>
       <c r="K41" t="n">
-        <v>153.01</v>
+        <v>153.34</v>
       </c>
       <c r="L41" t="n">
-        <v>337.05</v>
+        <v>337.78</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>339.99</v>
+        <v>341.3</v>
       </c>
       <c r="K42" t="n">
-        <v>131.6</v>
+        <v>132.11</v>
       </c>
       <c r="L42" t="n">
-        <v>364.56</v>
+        <v>365.98</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>-545.89</v>
+        <v>-600.55</v>
       </c>
       <c r="K43" t="n">
-        <v>442.7</v>
+        <v>487.03</v>
       </c>
       <c r="L43" t="n">
-        <v>702.84</v>
+        <v>773.21</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>94.79000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="K44" t="n">
-        <v>20.59</v>
+        <v>19.62</v>
       </c>
       <c r="L44" t="n">
-        <v>97</v>
+        <v>92.41</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>40.4</v>
+        <v>42.88</v>
       </c>
       <c r="K45" t="n">
-        <v>105.58</v>
+        <v>112.06</v>
       </c>
       <c r="L45" t="n">
-        <v>113.05</v>
+        <v>119.98</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>62.16</v>
+        <v>63.9</v>
       </c>
       <c r="K46" t="n">
-        <v>56.38</v>
+        <v>57.96</v>
       </c>
       <c r="L46" t="n">
-        <v>83.92</v>
+        <v>86.27</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>99.62</v>
+        <v>92.45</v>
       </c>
       <c r="K47" t="n">
-        <v>-77.03</v>
+        <v>-71.48</v>
       </c>
       <c r="L47" t="n">
-        <v>125.93</v>
+        <v>116.87</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>138.79</v>
+        <v>133.73</v>
       </c>
       <c r="K48" t="n">
-        <v>-37.11</v>
+        <v>-35.76</v>
       </c>
       <c r="L48" t="n">
-        <v>143.67</v>
+        <v>138.43</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-119.98</v>
+        <v>-122.91</v>
       </c>
       <c r="K49" t="n">
-        <v>-54.19</v>
+        <v>-55.52</v>
       </c>
       <c r="L49" t="n">
-        <v>131.65</v>
+        <v>134.87</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>22</v>
       </c>
       <c r="J50" t="n">
-        <v>139.05</v>
+        <v>143.57</v>
       </c>
       <c r="K50" t="n">
-        <v>160.19</v>
+        <v>165.39</v>
       </c>
       <c r="L50" t="n">
-        <v>212.12</v>
+        <v>219.01</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-157.88</v>
+        <v>-160.18</v>
       </c>
       <c r="K51" t="n">
-        <v>151.09</v>
+        <v>153.3</v>
       </c>
       <c r="L51" t="n">
-        <v>218.53</v>
+        <v>221.72</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-33.89</v>
+        <v>-33.76</v>
       </c>
       <c r="K52" t="n">
-        <v>189.45</v>
+        <v>188.73</v>
       </c>
       <c r="L52" t="n">
-        <v>192.46</v>
+        <v>191.73</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-47.08</v>
+        <v>-50.4</v>
       </c>
       <c r="K53" t="n">
-        <v>-58.17</v>
+        <v>-62.27</v>
       </c>
       <c r="L53" t="n">
-        <v>74.83</v>
+        <v>80.11</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-2.83</v>
+        <v>-3.08</v>
       </c>
       <c r="K54" t="n">
-        <v>367.94</v>
+        <v>399.99</v>
       </c>
       <c r="L54" t="n">
-        <v>367.95</v>
+        <v>400</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>-225.03</v>
+        <v>-240.86</v>
       </c>
       <c r="K55" t="n">
-        <v>221.54</v>
+        <v>237.12</v>
       </c>
       <c r="L55" t="n">
-        <v>315.79</v>
+        <v>337.99</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>-324.88</v>
+        <v>-318.86</v>
       </c>
       <c r="K56" t="n">
-        <v>-126.53</v>
+        <v>-124.18</v>
       </c>
       <c r="L56" t="n">
-        <v>348.65</v>
+        <v>342.19</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>19.97</v>
+        <v>20.83</v>
       </c>
       <c r="K57" t="n">
-        <v>403.28</v>
+        <v>420.61</v>
       </c>
       <c r="L57" t="n">
-        <v>403.78</v>
+        <v>421.13</v>
       </c>
     </row>
     <row r="58">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>14.52</v>
+        <v>14.79</v>
       </c>
       <c r="K59" t="n">
-        <v>-74.91</v>
+        <v>-76.3</v>
       </c>
       <c r="L59" t="n">
-        <v>76.3</v>
+        <v>77.72</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>24.01</v>
+        <v>24.16</v>
       </c>
       <c r="K60" t="n">
-        <v>-109.67</v>
+        <v>-110.34</v>
       </c>
       <c r="L60" t="n">
-        <v>112.27</v>
+        <v>112.95</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-31.09</v>
+        <v>-28.97</v>
       </c>
       <c r="K61" t="n">
-        <v>-94.31</v>
+        <v>-87.87</v>
       </c>
       <c r="L61" t="n">
-        <v>99.3</v>
+        <v>92.52</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>-85.42</v>
+        <v>-84.40000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>41.86</v>
+        <v>41.36</v>
       </c>
       <c r="L62" t="n">
-        <v>95.12</v>
+        <v>93.98999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-37.96</v>
+        <v>-36.71</v>
       </c>
       <c r="K63" t="n">
-        <v>86.78</v>
+        <v>83.92</v>
       </c>
       <c r="L63" t="n">
-        <v>94.72</v>
+        <v>91.59</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>23</v>
       </c>
       <c r="J64" t="n">
-        <v>-118.59</v>
+        <v>-116.48</v>
       </c>
       <c r="K64" t="n">
-        <v>111.43</v>
+        <v>109.45</v>
       </c>
       <c r="L64" t="n">
-        <v>162.73</v>
+        <v>159.83</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-82.98999999999999</v>
+        <v>-82.54000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>176.01</v>
+        <v>175.06</v>
       </c>
       <c r="L65" t="n">
-        <v>194.6</v>
+        <v>193.55</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-14.73</v>
+        <v>-14.94</v>
       </c>
       <c r="K66" t="n">
-        <v>217.35</v>
+        <v>220.53</v>
       </c>
       <c r="L66" t="n">
-        <v>217.85</v>
+        <v>221.04</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="K67" t="n">
-        <v>175.89</v>
+        <v>187.89</v>
       </c>
       <c r="L67" t="n">
-        <v>175.89</v>
+        <v>187.89</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-218.12</v>
+        <v>-221.06</v>
       </c>
       <c r="K68" t="n">
-        <v>142.82</v>
+        <v>144.74</v>
       </c>
       <c r="L68" t="n">
-        <v>260.72</v>
+        <v>264.22</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>145.04</v>
+        <v>149.85</v>
       </c>
       <c r="K69" t="n">
-        <v>-355.14</v>
+        <v>-366.93</v>
       </c>
       <c r="L69" t="n">
-        <v>383.61</v>
+        <v>396.35</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>28.4</v>
+        <v>27.54</v>
       </c>
       <c r="K70" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="L70" t="n">
-        <v>32.85</v>
+        <v>31.85</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-377.58</v>
+        <v>-378.29</v>
       </c>
       <c r="K71" t="n">
-        <v>-140.3</v>
+        <v>-140.56</v>
       </c>
       <c r="L71" t="n">
-        <v>402.8</v>
+        <v>403.56</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>22</v>
       </c>
       <c r="J72" t="n">
-        <v>214.01</v>
+        <v>227.34</v>
       </c>
       <c r="K72" t="n">
-        <v>500.26</v>
+        <v>531.42</v>
       </c>
       <c r="L72" t="n">
-        <v>544.11</v>
+        <v>578.01</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>-407.13</v>
+        <v>-446.72</v>
       </c>
       <c r="K73" t="n">
-        <v>-49.66</v>
+        <v>-54.49</v>
       </c>
       <c r="L73" t="n">
-        <v>410.14</v>
+        <v>450.03</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>20</v>
       </c>
       <c r="J74" t="n">
-        <v>46.36</v>
+        <v>47.2</v>
       </c>
       <c r="K74" t="n">
-        <v>68.72</v>
+        <v>69.97</v>
       </c>
       <c r="L74" t="n">
-        <v>82.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>25</v>
       </c>
       <c r="J75" t="n">
-        <v>82.58</v>
+        <v>77</v>
       </c>
       <c r="K75" t="n">
-        <v>-15.75</v>
+        <v>-14.69</v>
       </c>
       <c r="L75" t="n">
-        <v>84.06999999999999</v>
+        <v>78.39</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>66.92</v>
+        <v>63.28</v>
       </c>
       <c r="K76" t="n">
-        <v>43.03</v>
+        <v>40.69</v>
       </c>
       <c r="L76" t="n">
-        <v>79.56</v>
+        <v>75.23</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-86.27</v>
+        <v>-85.04000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>14.76</v>
+        <v>14.55</v>
       </c>
       <c r="L77" t="n">
-        <v>87.53</v>
+        <v>86.28</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>48.92</v>
+        <v>48.05</v>
       </c>
       <c r="K78" t="n">
-        <v>121.64</v>
+        <v>119.48</v>
       </c>
       <c r="L78" t="n">
-        <v>131.11</v>
+        <v>128.78</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>43.29</v>
+        <v>44</v>
       </c>
       <c r="K79" t="n">
-        <v>-127.7</v>
+        <v>-129.79</v>
       </c>
       <c r="L79" t="n">
-        <v>134.83</v>
+        <v>137.05</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>25</v>
       </c>
       <c r="J80" t="n">
-        <v>119.94</v>
+        <v>116.93</v>
       </c>
       <c r="K80" t="n">
-        <v>198.69</v>
+        <v>193.69</v>
       </c>
       <c r="L80" t="n">
-        <v>232.08</v>
+        <v>226.25</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>20</v>
       </c>
       <c r="J81" t="n">
-        <v>-291.42</v>
+        <v>-311.15</v>
       </c>
       <c r="K81" t="n">
-        <v>-34.99</v>
+        <v>-37.36</v>
       </c>
       <c r="L81" t="n">
-        <v>293.51</v>
+        <v>313.39</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>-69.81</v>
+        <v>-70.81</v>
       </c>
       <c r="K82" t="n">
-        <v>143.54</v>
+        <v>145.59</v>
       </c>
       <c r="L82" t="n">
-        <v>159.61</v>
+        <v>161.89</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>-378.32</v>
+        <v>-375.64</v>
       </c>
       <c r="K83" t="n">
-        <v>39.11</v>
+        <v>38.83</v>
       </c>
       <c r="L83" t="n">
-        <v>380.34</v>
+        <v>377.64</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>-329.94</v>
+        <v>-359.3</v>
       </c>
       <c r="K84" t="n">
-        <v>245.54</v>
+        <v>267.39</v>
       </c>
       <c r="L84" t="n">
-        <v>411.28</v>
+        <v>447.87</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>53.73</v>
+        <v>55.49</v>
       </c>
       <c r="K85" t="n">
-        <v>422.92</v>
+        <v>436.74</v>
       </c>
       <c r="L85" t="n">
-        <v>426.31</v>
+        <v>440.25</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>418.32</v>
+        <v>429.22</v>
       </c>
       <c r="K86" t="n">
-        <v>93.16</v>
+        <v>95.59</v>
       </c>
       <c r="L86" t="n">
-        <v>428.57</v>
+        <v>439.73</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-404.97</v>
+        <v>-445.1</v>
       </c>
       <c r="K87" t="n">
-        <v>5.8</v>
+        <v>6.37</v>
       </c>
       <c r="L87" t="n">
-        <v>405.02</v>
+        <v>445.15</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>-550.12</v>
+        <v>-590.87</v>
       </c>
       <c r="K88" t="n">
-        <v>-57.73</v>
+        <v>-62</v>
       </c>
       <c r="L88" t="n">
-        <v>553.14</v>
+        <v>594.12</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-01.xlsx
+++ b/output/2025-07-01.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>5.96</v>
+        <v>5.99</v>
       </c>
       <c r="F14" t="n">
-        <v>15.24</v>
+        <v>12.49</v>
       </c>
       <c r="G14" t="n">
-        <v>341.9</v>
+        <v>323.1</v>
       </c>
       <c r="H14" t="n">
-        <v>100</v>
+        <v>59.7</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>98.98</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.16</v>
+        <v>163</v>
       </c>
       <c r="L14" t="n">
-        <v>98.98</v>
+        <v>175.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:36:28</t>
+          <t>04:35:46</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>6.88</v>
+        <v>6.07</v>
       </c>
       <c r="F15" t="n">
-        <v>13.61</v>
+        <v>13.88</v>
       </c>
       <c r="G15" t="n">
-        <v>333.6</v>
+        <v>336.1</v>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>59.8</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J15" t="n">
-        <v>-64.76000000000001</v>
+        <v>-118.35</v>
       </c>
       <c r="K15" t="n">
-        <v>-49.12</v>
+        <v>35.96</v>
       </c>
       <c r="L15" t="n">
-        <v>81.28</v>
+        <v>123.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:37:48</t>
+          <t>04:36:33</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>5.91</v>
+        <v>6.44</v>
       </c>
       <c r="F16" t="n">
-        <v>10.49</v>
+        <v>11.12</v>
       </c>
       <c r="G16" t="n">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>59.9</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>-62.63</v>
+        <v>-60.34</v>
       </c>
       <c r="K16" t="n">
-        <v>18.24</v>
+        <v>-39.78</v>
       </c>
       <c r="L16" t="n">
-        <v>65.23999999999999</v>
+        <v>72.27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:43:34</t>
+          <t>04:41:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>6.37</v>
+        <v>5.36</v>
       </c>
       <c r="F17" t="n">
-        <v>14.03</v>
+        <v>6.88</v>
       </c>
       <c r="G17" t="n">
-        <v>328.2</v>
+        <v>329.2</v>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>85.8</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-86.34</v>
+        <v>20.11</v>
       </c>
       <c r="K17" t="n">
-        <v>-29.73</v>
+        <v>132.72</v>
       </c>
       <c r="L17" t="n">
-        <v>91.31999999999999</v>
+        <v>134.24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:45:45</t>
+          <t>04:42:08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>5.9</v>
+        <v>5.78</v>
       </c>
       <c r="F18" t="n">
-        <v>14.7</v>
+        <v>11.85</v>
       </c>
       <c r="G18" t="n">
-        <v>344.1</v>
+        <v>332.7</v>
       </c>
       <c r="H18" t="n">
-        <v>96.7</v>
+        <v>40.1</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>71.39</v>
+        <v>-62.97</v>
       </c>
       <c r="K18" t="n">
-        <v>-90.06</v>
+        <v>132.94</v>
       </c>
       <c r="L18" t="n">
-        <v>114.92</v>
+        <v>147.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:47:35</t>
+          <t>04:44:32</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>5.67</v>
+        <v>5.99</v>
       </c>
       <c r="F19" t="n">
-        <v>11.58</v>
+        <v>13.49</v>
       </c>
       <c r="G19" t="n">
-        <v>321.2</v>
+        <v>323.6</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>71.3</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J19" t="n">
-        <v>46.95</v>
+        <v>-133.04</v>
       </c>
       <c r="K19" t="n">
-        <v>170.57</v>
+        <v>134</v>
       </c>
       <c r="L19" t="n">
-        <v>176.92</v>
+        <v>188.83</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:51:53</t>
+          <t>04:49:21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>6.16</v>
+        <v>5.2</v>
       </c>
       <c r="F20" t="n">
-        <v>12.73</v>
+        <v>10.92</v>
       </c>
       <c r="G20" t="n">
-        <v>326.4</v>
+        <v>345</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>51.4</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>71.23</v>
+        <v>122.66</v>
       </c>
       <c r="K20" t="n">
-        <v>169.76</v>
+        <v>100.3</v>
       </c>
       <c r="L20" t="n">
-        <v>184.09</v>
+        <v>158.45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:53:13</t>
+          <t>04:50:31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>6.24</v>
+        <v>5.66</v>
       </c>
       <c r="F21" t="n">
-        <v>14.63</v>
+        <v>11.52</v>
       </c>
       <c r="G21" t="n">
-        <v>327.5</v>
+        <v>319.7</v>
       </c>
       <c r="H21" t="n">
-        <v>97.09999999999999</v>
+        <v>41.4</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.28</v>
+        <v>-154.66</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.45</v>
+        <v>40.77</v>
       </c>
       <c r="L21" t="n">
-        <v>7.29</v>
+        <v>159.94</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:55:16</t>
+          <t>04:51:10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>6.47</v>
+        <v>6.31</v>
       </c>
       <c r="F22" t="n">
-        <v>12.86</v>
+        <v>11.59</v>
       </c>
       <c r="G22" t="n">
-        <v>330.5</v>
+        <v>329.8</v>
       </c>
       <c r="H22" t="n">
-        <v>100</v>
+        <v>58.1</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-39.86</v>
+        <v>-191.39</v>
       </c>
       <c r="K22" t="n">
-        <v>174.36</v>
+        <v>169.71</v>
       </c>
       <c r="L22" t="n">
-        <v>178.86</v>
+        <v>255.79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:00:40</t>
+          <t>04:57:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>5.04</v>
+        <v>5.32</v>
       </c>
       <c r="F23" t="n">
-        <v>12.61</v>
+        <v>13.86</v>
       </c>
       <c r="G23" t="n">
-        <v>323.9</v>
+        <v>329.3</v>
       </c>
       <c r="H23" t="n">
-        <v>100</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J23" t="n">
-        <v>-156.9</v>
+        <v>253.94</v>
       </c>
       <c r="K23" t="n">
-        <v>218.59</v>
+        <v>-184.25</v>
       </c>
       <c r="L23" t="n">
-        <v>269.07</v>
+        <v>313.74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:03:01</t>
+          <t>04:58:44</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>6.01</v>
+        <v>6.58</v>
       </c>
       <c r="F24" t="n">
-        <v>13.55</v>
+        <v>13.85</v>
       </c>
       <c r="G24" t="n">
-        <v>316.4</v>
+        <v>333</v>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>64.5</v>
       </c>
       <c r="I24" t="n">
         <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>169.94</v>
+        <v>-237.81</v>
       </c>
       <c r="K24" t="n">
-        <v>13.74</v>
+        <v>413.39</v>
       </c>
       <c r="L24" t="n">
-        <v>170.5</v>
+        <v>476.91</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:04:03</t>
+          <t>05:00:42</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>6.18</v>
+        <v>5.5</v>
       </c>
       <c r="F25" t="n">
-        <v>15.7</v>
+        <v>13.32</v>
       </c>
       <c r="G25" t="n">
-        <v>336.4</v>
+        <v>330.1</v>
       </c>
       <c r="H25" t="n">
-        <v>100</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>-203.59</v>
+        <v>-209.25</v>
       </c>
       <c r="K25" t="n">
-        <v>-227.27</v>
+        <v>207.33</v>
       </c>
       <c r="L25" t="n">
-        <v>305.13</v>
+        <v>294.57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:08:15</t>
+          <t>05:06:46</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>6.3</v>
+        <v>6.21</v>
       </c>
       <c r="F26" t="n">
-        <v>16.51</v>
+        <v>13.03</v>
       </c>
       <c r="G26" t="n">
-        <v>324.3</v>
+        <v>336.7</v>
       </c>
       <c r="H26" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J26" t="n">
-        <v>-601.17</v>
+        <v>344.12</v>
       </c>
       <c r="K26" t="n">
-        <v>-23.77</v>
+        <v>-268.55</v>
       </c>
       <c r="L26" t="n">
-        <v>601.64</v>
+        <v>436.51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:09:23</t>
+          <t>05:08:18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.82</v>
+        <v>5.52</v>
       </c>
       <c r="F27" t="n">
-        <v>10.68</v>
+        <v>12.58</v>
       </c>
       <c r="G27" t="n">
-        <v>324</v>
+        <v>356.8</v>
       </c>
       <c r="H27" t="n">
-        <v>96.3</v>
+        <v>67</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J27" t="n">
-        <v>-407.62</v>
+        <v>-13.99</v>
       </c>
       <c r="K27" t="n">
-        <v>202.27</v>
+        <v>234.71</v>
       </c>
       <c r="L27" t="n">
-        <v>455.05</v>
+        <v>235.13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:11:21</t>
+          <t>05:08:58</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>5.62</v>
+        <v>6.53</v>
       </c>
       <c r="F28" t="n">
-        <v>14.74</v>
+        <v>16.58</v>
       </c>
       <c r="G28" t="n">
-        <v>325.1</v>
+        <v>327.5</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="I28" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J28" t="n">
-        <v>-271.24</v>
+        <v>-396.8</v>
       </c>
       <c r="K28" t="n">
-        <v>-272.52</v>
+        <v>134.08</v>
       </c>
       <c r="L28" t="n">
-        <v>384.49</v>
+        <v>418.84</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:21:52</t>
+          <t>05:21:04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>5.77</v>
+        <v>6.31</v>
       </c>
       <c r="F29" t="n">
-        <v>16.41</v>
+        <v>14.84</v>
       </c>
       <c r="G29" t="n">
-        <v>332.2</v>
+        <v>334.9</v>
       </c>
       <c r="H29" t="n">
-        <v>100</v>
+        <v>51.5</v>
       </c>
       <c r="I29" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.44</v>
+        <v>-44.08</v>
       </c>
       <c r="K29" t="n">
-        <v>-12.06</v>
+        <v>-145.82</v>
       </c>
       <c r="L29" t="n">
-        <v>14.72</v>
+        <v>152.34</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:23:48</t>
+          <t>05:22:48</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>6.86</v>
+        <v>6.32</v>
       </c>
       <c r="F30" t="n">
-        <v>16.47</v>
+        <v>12.19</v>
       </c>
       <c r="G30" t="n">
-        <v>328.2</v>
+        <v>329.6</v>
       </c>
       <c r="H30" t="n">
-        <v>100</v>
+        <v>65.8</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>3.64</v>
+        <v>7.57</v>
       </c>
       <c r="K30" t="n">
-        <v>79.38</v>
+        <v>156.09</v>
       </c>
       <c r="L30" t="n">
-        <v>79.47</v>
+        <v>156.27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:25:35</t>
+          <t>05:25:06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>6.73</v>
+        <v>5.15</v>
       </c>
       <c r="F31" t="n">
-        <v>14.56</v>
+        <v>11.61</v>
       </c>
       <c r="G31" t="n">
-        <v>336.5</v>
+        <v>321.7</v>
       </c>
       <c r="H31" t="n">
-        <v>100</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>87.59</v>
+        <v>-44.18</v>
       </c>
       <c r="K31" t="n">
-        <v>-17.96</v>
+        <v>16.94</v>
       </c>
       <c r="L31" t="n">
-        <v>89.41</v>
+        <v>47.32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:31:11</t>
+          <t>05:30:16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>6.25</v>
+        <v>6.31</v>
       </c>
       <c r="F32" t="n">
-        <v>13.22</v>
+        <v>13.4</v>
       </c>
       <c r="G32" t="n">
-        <v>327.2</v>
+        <v>335.4</v>
       </c>
       <c r="H32" t="n">
-        <v>98.90000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>-68.18000000000001</v>
+        <v>-158.02</v>
       </c>
       <c r="K32" t="n">
-        <v>77.8</v>
+        <v>-128.35</v>
       </c>
       <c r="L32" t="n">
-        <v>103.44</v>
+        <v>203.58</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:32:41</t>
+          <t>05:31:39</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>6.24</v>
+        <v>6.48</v>
       </c>
       <c r="F33" t="n">
-        <v>12.72</v>
+        <v>15.96</v>
       </c>
       <c r="G33" t="n">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="H33" t="n">
-        <v>92.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J33" t="n">
-        <v>-42.29</v>
+        <v>-57.3</v>
       </c>
       <c r="K33" t="n">
-        <v>119.42</v>
+        <v>108.62</v>
       </c>
       <c r="L33" t="n">
-        <v>126.69</v>
+        <v>122.81</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:33:51</t>
+          <t>05:33:15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>6.09</v>
+        <v>5.26</v>
       </c>
       <c r="F34" t="n">
-        <v>13.39</v>
+        <v>11.74</v>
       </c>
       <c r="G34" t="n">
-        <v>337.1</v>
+        <v>323.8</v>
       </c>
       <c r="H34" t="n">
-        <v>100</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>28.51</v>
+        <v>26.63</v>
       </c>
       <c r="K34" t="n">
-        <v>-138.53</v>
+        <v>-120.73</v>
       </c>
       <c r="L34" t="n">
-        <v>141.43</v>
+        <v>123.63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:39:30</t>
+          <t>05:36:34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>6.84</v>
+        <v>6.3</v>
       </c>
       <c r="F35" t="n">
-        <v>15.9</v>
+        <v>12.01</v>
       </c>
       <c r="G35" t="n">
-        <v>321</v>
+        <v>332.9</v>
       </c>
       <c r="H35" t="n">
-        <v>96.09999999999999</v>
+        <v>60.7</v>
       </c>
       <c r="I35" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>81.28</v>
+        <v>-68.61</v>
       </c>
       <c r="K35" t="n">
-        <v>-147.47</v>
+        <v>178.46</v>
       </c>
       <c r="L35" t="n">
-        <v>168.39</v>
+        <v>191.19</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:41:08</t>
+          <t>05:37:45</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>6.48</v>
+        <v>6.23</v>
       </c>
       <c r="F36" t="n">
-        <v>14.65</v>
+        <v>13.79</v>
       </c>
       <c r="G36" t="n">
-        <v>329.1</v>
+        <v>329.9</v>
       </c>
       <c r="H36" t="n">
-        <v>94.8</v>
+        <v>43.6</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J36" t="n">
-        <v>-111.45</v>
+        <v>-203.46</v>
       </c>
       <c r="K36" t="n">
-        <v>-105.81</v>
+        <v>-166.82</v>
       </c>
       <c r="L36" t="n">
-        <v>153.68</v>
+        <v>263.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:43:26</t>
+          <t>05:39:47</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>6.46</v>
+        <v>6.96</v>
       </c>
       <c r="F37" t="n">
-        <v>14.05</v>
+        <v>17.54</v>
       </c>
       <c r="G37" t="n">
-        <v>331.7</v>
+        <v>331.5</v>
       </c>
       <c r="H37" t="n">
-        <v>100</v>
+        <v>55.2</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-141.55</v>
+        <v>-157.48</v>
       </c>
       <c r="K37" t="n">
-        <v>-86.48</v>
+        <v>188.43</v>
       </c>
       <c r="L37" t="n">
-        <v>165.88</v>
+        <v>245.57</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:47:17</t>
+          <t>05:44:44</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>7.28</v>
+        <v>6.26</v>
       </c>
       <c r="F38" t="n">
-        <v>18.4</v>
+        <v>13.86</v>
       </c>
       <c r="G38" t="n">
-        <v>325.8</v>
+        <v>334.8</v>
       </c>
       <c r="H38" t="n">
-        <v>100</v>
+        <v>36.9</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-288.42</v>
+        <v>-419.67</v>
       </c>
       <c r="K38" t="n">
-        <v>-235.77</v>
+        <v>200.49</v>
       </c>
       <c r="L38" t="n">
-        <v>372.52</v>
+        <v>465.1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:48:51</t>
+          <t>05:46:46</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>6.15</v>
+        <v>6.38</v>
       </c>
       <c r="F39" t="n">
-        <v>15.64</v>
+        <v>13.9</v>
       </c>
       <c r="G39" t="n">
-        <v>333.3</v>
+        <v>331.2</v>
       </c>
       <c r="H39" t="n">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="I39" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J39" t="n">
-        <v>102.9</v>
+        <v>-289.53</v>
       </c>
       <c r="K39" t="n">
-        <v>337.34</v>
+        <v>-97.95</v>
       </c>
       <c r="L39" t="n">
-        <v>352.69</v>
+        <v>305.65</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:50:11</t>
+          <t>05:48:38</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,13 +1717,13 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>5.82</v>
+        <v>7.31</v>
       </c>
       <c r="F40" t="n">
-        <v>14.3</v>
+        <v>18.4</v>
       </c>
       <c r="G40" t="n">
-        <v>330.3</v>
+        <v>330.7</v>
       </c>
       <c r="H40" t="n">
         <v>100</v>
@@ -1732,19 +1732,19 @@
         <v>26</v>
       </c>
       <c r="J40" t="n">
-        <v>-243.85</v>
+        <v>120.43</v>
       </c>
       <c r="K40" t="n">
-        <v>-107.52</v>
+        <v>332.62</v>
       </c>
       <c r="L40" t="n">
-        <v>266.5</v>
+        <v>353.75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:54:11</t>
+          <t>05:53:54</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>5.99</v>
+        <v>6.11</v>
       </c>
       <c r="F41" t="n">
-        <v>14.22</v>
+        <v>14.14</v>
       </c>
       <c r="G41" t="n">
-        <v>324.2</v>
+        <v>332.6</v>
       </c>
       <c r="H41" t="n">
-        <v>96</v>
+        <v>49.4</v>
       </c>
       <c r="I41" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-300.96</v>
+        <v>-447.41</v>
       </c>
       <c r="K41" t="n">
-        <v>153.34</v>
+        <v>188.33</v>
       </c>
       <c r="L41" t="n">
-        <v>337.78</v>
+        <v>485.43</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:55:52</t>
+          <t>05:55:20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>6.51</v>
+        <v>6</v>
       </c>
       <c r="F42" t="n">
-        <v>18.02</v>
+        <v>15.13</v>
       </c>
       <c r="G42" t="n">
-        <v>335.3</v>
+        <v>334.6</v>
       </c>
       <c r="H42" t="n">
-        <v>100</v>
+        <v>31.7</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J42" t="n">
-        <v>341.3</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>132.11</v>
+        <v>-510.95</v>
       </c>
       <c r="L42" t="n">
-        <v>365.98</v>
+        <v>519.17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:56:34</t>
+          <t>05:57:04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>6.34</v>
+        <v>6.37</v>
       </c>
       <c r="F43" t="n">
-        <v>14.9</v>
+        <v>17.22</v>
       </c>
       <c r="G43" t="n">
-        <v>336.4</v>
+        <v>320.9</v>
       </c>
       <c r="H43" t="n">
         <v>100</v>
       </c>
       <c r="I43" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-600.55</v>
+        <v>-253.73</v>
       </c>
       <c r="K43" t="n">
-        <v>487.03</v>
+        <v>343.89</v>
       </c>
       <c r="L43" t="n">
-        <v>773.21</v>
+        <v>427.37</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:08:15</t>
+          <t>06:06:40</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>6.47</v>
+        <v>6.15</v>
       </c>
       <c r="F44" t="n">
-        <v>17.15</v>
+        <v>13.56</v>
       </c>
       <c r="G44" t="n">
-        <v>330.3</v>
+        <v>330.9</v>
       </c>
       <c r="H44" t="n">
-        <v>91.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="I44" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J44" t="n">
-        <v>90.3</v>
+        <v>38.67</v>
       </c>
       <c r="K44" t="n">
-        <v>19.62</v>
+        <v>140.1</v>
       </c>
       <c r="L44" t="n">
-        <v>92.41</v>
+        <v>145.34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:09:44</t>
+          <t>06:08:30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>5.92</v>
+        <v>6.92</v>
       </c>
       <c r="F45" t="n">
-        <v>10.52</v>
+        <v>17.85</v>
       </c>
       <c r="G45" t="n">
-        <v>325.7</v>
+        <v>332.7</v>
       </c>
       <c r="H45" t="n">
-        <v>94.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J45" t="n">
-        <v>42.88</v>
+        <v>-109.59</v>
       </c>
       <c r="K45" t="n">
-        <v>112.06</v>
+        <v>46.78</v>
       </c>
       <c r="L45" t="n">
-        <v>119.98</v>
+        <v>119.15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:11:23</t>
+          <t>06:09:40</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>5.46</v>
+        <v>6.04</v>
       </c>
       <c r="F46" t="n">
-        <v>16.25</v>
+        <v>13.38</v>
       </c>
       <c r="G46" t="n">
-        <v>324.3</v>
+        <v>324.7</v>
       </c>
       <c r="H46" t="n">
-        <v>97.7</v>
+        <v>36</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J46" t="n">
-        <v>63.9</v>
+        <v>-75.03</v>
       </c>
       <c r="K46" t="n">
-        <v>57.96</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>86.27</v>
+        <v>118.92</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:15:53</t>
+          <t>06:13:04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>6.21</v>
+        <v>7.31</v>
       </c>
       <c r="F47" t="n">
-        <v>16.78</v>
+        <v>15.44</v>
       </c>
       <c r="G47" t="n">
-        <v>317.8</v>
+        <v>324.1</v>
       </c>
       <c r="H47" t="n">
-        <v>92.3</v>
+        <v>45.3</v>
       </c>
       <c r="I47" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J47" t="n">
-        <v>92.45</v>
+        <v>-161.73</v>
       </c>
       <c r="K47" t="n">
-        <v>-71.48</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>116.87</v>
+        <v>175.04</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:17:24</t>
+          <t>06:15:28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>7.18</v>
+        <v>6.15</v>
       </c>
       <c r="F48" t="n">
-        <v>17.52</v>
+        <v>14.61</v>
       </c>
       <c r="G48" t="n">
-        <v>319.9</v>
+        <v>332.9</v>
       </c>
       <c r="H48" t="n">
-        <v>89.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>133.73</v>
+        <v>59.01</v>
       </c>
       <c r="K48" t="n">
-        <v>-35.76</v>
+        <v>123.52</v>
       </c>
       <c r="L48" t="n">
-        <v>138.43</v>
+        <v>136.89</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:19:30</t>
+          <t>06:16:41</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>6.02</v>
+        <v>7.8</v>
       </c>
       <c r="F49" t="n">
-        <v>12.37</v>
+        <v>17.95</v>
       </c>
       <c r="G49" t="n">
-        <v>350.9</v>
+        <v>329</v>
       </c>
       <c r="H49" t="n">
-        <v>96.8</v>
+        <v>23.2</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J49" t="n">
-        <v>-122.91</v>
+        <v>-199.27</v>
       </c>
       <c r="K49" t="n">
-        <v>-55.52</v>
+        <v>15.07</v>
       </c>
       <c r="L49" t="n">
-        <v>134.87</v>
+        <v>199.84</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:23:28</t>
+          <t>06:22:01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>7.43</v>
+        <v>6.23</v>
       </c>
       <c r="F50" t="n">
-        <v>18.24</v>
+        <v>18.2</v>
       </c>
       <c r="G50" t="n">
-        <v>330.5</v>
+        <v>325.2</v>
       </c>
       <c r="H50" t="n">
-        <v>100</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J50" t="n">
-        <v>143.57</v>
+        <v>-171.5</v>
       </c>
       <c r="K50" t="n">
-        <v>165.39</v>
+        <v>105.54</v>
       </c>
       <c r="L50" t="n">
-        <v>219.01</v>
+        <v>201.37</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:25:03</t>
+          <t>06:23:15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>6.36</v>
+        <v>6.08</v>
       </c>
       <c r="F51" t="n">
-        <v>15.05</v>
+        <v>15.01</v>
       </c>
       <c r="G51" t="n">
-        <v>330</v>
+        <v>336.5</v>
       </c>
       <c r="H51" t="n">
-        <v>99.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>-160.18</v>
+        <v>-193.17</v>
       </c>
       <c r="K51" t="n">
-        <v>153.3</v>
+        <v>143.93</v>
       </c>
       <c r="L51" t="n">
-        <v>221.72</v>
+        <v>240.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:26:32</t>
+          <t>06:25:36</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>5.3</v>
+        <v>6.84</v>
       </c>
       <c r="F52" t="n">
-        <v>11.94</v>
+        <v>14.18</v>
       </c>
       <c r="G52" t="n">
-        <v>339.2</v>
+        <v>331.3</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>35.6</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-33.76</v>
+        <v>-200.11</v>
       </c>
       <c r="K52" t="n">
-        <v>188.73</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>191.73</v>
+        <v>213.24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:31:49</t>
+          <t>06:28:49</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>7.13</v>
+        <v>6.65</v>
       </c>
       <c r="F53" t="n">
-        <v>18.4</v>
+        <v>15.41</v>
       </c>
       <c r="G53" t="n">
-        <v>323.2</v>
+        <v>321.4</v>
       </c>
       <c r="H53" t="n">
-        <v>100</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>-50.4</v>
+        <v>-252.21</v>
       </c>
       <c r="K53" t="n">
-        <v>-62.27</v>
+        <v>8.74</v>
       </c>
       <c r="L53" t="n">
-        <v>80.11</v>
+        <v>252.36</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:33:41</t>
+          <t>06:30:43</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>6.41</v>
+        <v>6.48</v>
       </c>
       <c r="F54" t="n">
-        <v>13.65</v>
+        <v>12.52</v>
       </c>
       <c r="G54" t="n">
-        <v>330.6</v>
+        <v>339</v>
       </c>
       <c r="H54" t="n">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>-3.08</v>
+        <v>234.64</v>
       </c>
       <c r="K54" t="n">
-        <v>399.99</v>
+        <v>229.31</v>
       </c>
       <c r="L54" t="n">
-        <v>400</v>
+        <v>328.09</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:34:39</t>
+          <t>06:31:24</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>6.99</v>
+        <v>6.43</v>
       </c>
       <c r="F55" t="n">
-        <v>16.17</v>
+        <v>18.4</v>
       </c>
       <c r="G55" t="n">
-        <v>324.1</v>
+        <v>323.3</v>
       </c>
       <c r="H55" t="n">
-        <v>97</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J55" t="n">
-        <v>-240.86</v>
+        <v>-246.4</v>
       </c>
       <c r="K55" t="n">
-        <v>237.12</v>
+        <v>25.35</v>
       </c>
       <c r="L55" t="n">
-        <v>337.99</v>
+        <v>247.7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:38:26</t>
+          <t>06:37:09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>6.3</v>
+        <v>6.06</v>
       </c>
       <c r="F56" t="n">
-        <v>17.63</v>
+        <v>12.98</v>
       </c>
       <c r="G56" t="n">
-        <v>328.9</v>
+        <v>332.1</v>
       </c>
       <c r="H56" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="I56" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-318.86</v>
+        <v>55.62</v>
       </c>
       <c r="K56" t="n">
-        <v>-124.18</v>
+        <v>-376</v>
       </c>
       <c r="L56" t="n">
-        <v>342.19</v>
+        <v>380.09</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:40:29</t>
+          <t>06:39:11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>5.96</v>
+        <v>6.89</v>
       </c>
       <c r="F57" t="n">
-        <v>16.04</v>
+        <v>16.97</v>
       </c>
       <c r="G57" t="n">
-        <v>326.7</v>
+        <v>332.8</v>
       </c>
       <c r="H57" t="n">
-        <v>98.90000000000001</v>
+        <v>63</v>
       </c>
       <c r="I57" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>20.83</v>
+        <v>-397.97</v>
       </c>
       <c r="K57" t="n">
-        <v>420.61</v>
+        <v>35.5</v>
       </c>
       <c r="L57" t="n">
-        <v>421.13</v>
+        <v>399.55</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:41:26</t>
+          <t>06:41:27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>7.5</v>
+        <v>7.18</v>
       </c>
       <c r="F58" t="n">
-        <v>16.84</v>
+        <v>15.01</v>
       </c>
       <c r="G58" t="n">
-        <v>341</v>
+        <v>329.7</v>
       </c>
       <c r="H58" t="n">
-        <v>100</v>
+        <v>65.8</v>
       </c>
       <c r="I58" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J58" t="n">
-        <v>283.61</v>
+        <v>-368.86</v>
       </c>
       <c r="K58" t="n">
-        <v>249.38</v>
+        <v>-260.15</v>
       </c>
       <c r="L58" t="n">
-        <v>377.66</v>
+        <v>451.37</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:54:00</t>
+          <t>06:52:16</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>7.03</v>
+        <v>6.41</v>
       </c>
       <c r="F59" t="n">
-        <v>17.24</v>
+        <v>17.8</v>
       </c>
       <c r="G59" t="n">
-        <v>335.8</v>
+        <v>322.8</v>
       </c>
       <c r="H59" t="n">
-        <v>97.40000000000001</v>
+        <v>44.1</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>14.79</v>
+        <v>-124.09</v>
       </c>
       <c r="K59" t="n">
-        <v>-76.3</v>
+        <v>92.98</v>
       </c>
       <c r="L59" t="n">
-        <v>77.72</v>
+        <v>155.06</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:56:13</t>
+          <t>06:53:18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>6.53</v>
+        <v>7.45</v>
       </c>
       <c r="F60" t="n">
-        <v>15.9</v>
+        <v>18.4</v>
       </c>
       <c r="G60" t="n">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="H60" t="n">
-        <v>95.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>24.16</v>
+        <v>-86.54000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>-110.34</v>
+        <v>99.97</v>
       </c>
       <c r="L60" t="n">
-        <v>112.95</v>
+        <v>132.23</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:58:16</t>
+          <t>06:54:57</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="F61" t="n">
-        <v>17.78</v>
+        <v>17.15</v>
       </c>
       <c r="G61" t="n">
-        <v>320.6</v>
+        <v>317.1</v>
       </c>
       <c r="H61" t="n">
-        <v>100</v>
+        <v>45.5</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J61" t="n">
-        <v>-28.97</v>
+        <v>-40.95</v>
       </c>
       <c r="K61" t="n">
-        <v>-87.87</v>
+        <v>-119.59</v>
       </c>
       <c r="L61" t="n">
-        <v>92.52</v>
+        <v>126.41</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:02:36</t>
+          <t>06:59:28</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>6.1</v>
+        <v>6.56</v>
       </c>
       <c r="F62" t="n">
-        <v>16.4</v>
+        <v>16.71</v>
       </c>
       <c r="G62" t="n">
-        <v>347</v>
+        <v>306.3</v>
       </c>
       <c r="H62" t="n">
-        <v>100</v>
+        <v>59.4</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J62" t="n">
-        <v>-84.40000000000001</v>
+        <v>149.79</v>
       </c>
       <c r="K62" t="n">
-        <v>41.36</v>
+        <v>58.65</v>
       </c>
       <c r="L62" t="n">
-        <v>93.98999999999999</v>
+        <v>160.86</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:05:11</t>
+          <t>07:00:20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>6.47</v>
+        <v>5.85</v>
       </c>
       <c r="F63" t="n">
-        <v>15.97</v>
+        <v>13.12</v>
       </c>
       <c r="G63" t="n">
-        <v>324.8</v>
+        <v>316.8</v>
       </c>
       <c r="H63" t="n">
-        <v>91.59999999999999</v>
+        <v>54.8</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J63" t="n">
-        <v>-36.71</v>
+        <v>147.07</v>
       </c>
       <c r="K63" t="n">
-        <v>83.92</v>
+        <v>86.83</v>
       </c>
       <c r="L63" t="n">
-        <v>91.59</v>
+        <v>170.79</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:05:58</t>
+          <t>07:01:21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>7.23</v>
+        <v>6.78</v>
       </c>
       <c r="F64" t="n">
-        <v>17.92</v>
+        <v>16.3</v>
       </c>
       <c r="G64" t="n">
-        <v>322.5</v>
+        <v>313.9</v>
       </c>
       <c r="H64" t="n">
-        <v>93.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-116.48</v>
+        <v>-39.9</v>
       </c>
       <c r="K64" t="n">
-        <v>109.45</v>
+        <v>174.91</v>
       </c>
       <c r="L64" t="n">
-        <v>159.83</v>
+        <v>179.4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:11:36</t>
+          <t>07:06:55</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>6.95</v>
+        <v>5.85</v>
       </c>
       <c r="F65" t="n">
-        <v>14.96</v>
+        <v>14.38</v>
       </c>
       <c r="G65" t="n">
-        <v>319.7</v>
+        <v>325.2</v>
       </c>
       <c r="H65" t="n">
-        <v>96.40000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-82.54000000000001</v>
+        <v>-172.22</v>
       </c>
       <c r="K65" t="n">
-        <v>175.06</v>
+        <v>73.39</v>
       </c>
       <c r="L65" t="n">
-        <v>193.55</v>
+        <v>187.21</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:12:12</t>
+          <t>07:08:42</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>6.32</v>
+        <v>6.74</v>
       </c>
       <c r="F66" t="n">
-        <v>15.1</v>
+        <v>15.96</v>
       </c>
       <c r="G66" t="n">
-        <v>323.1</v>
+        <v>337.4</v>
       </c>
       <c r="H66" t="n">
-        <v>100</v>
+        <v>61.7</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-14.94</v>
+        <v>16.73</v>
       </c>
       <c r="K66" t="n">
-        <v>220.53</v>
+        <v>245.37</v>
       </c>
       <c r="L66" t="n">
-        <v>221.04</v>
+        <v>245.94</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:13:33</t>
+          <t>07:10:12</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>6.98</v>
+        <v>6.94</v>
       </c>
       <c r="F67" t="n">
-        <v>15.06</v>
+        <v>18.4</v>
       </c>
       <c r="G67" t="n">
-        <v>322.8</v>
+        <v>329</v>
       </c>
       <c r="H67" t="n">
-        <v>96.8</v>
+        <v>41.7</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J67" t="n">
-        <v>-0.32</v>
+        <v>-166.77</v>
       </c>
       <c r="K67" t="n">
-        <v>187.89</v>
+        <v>202.55</v>
       </c>
       <c r="L67" t="n">
-        <v>187.89</v>
+        <v>262.37</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:18:42</t>
+          <t>07:15:11</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>7.36</v>
+        <v>5.39</v>
       </c>
       <c r="F68" t="n">
-        <v>16.4</v>
+        <v>15.45</v>
       </c>
       <c r="G68" t="n">
-        <v>334.1</v>
+        <v>331</v>
       </c>
       <c r="H68" t="n">
-        <v>100</v>
+        <v>51.4</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J68" t="n">
-        <v>-221.06</v>
+        <v>99.79000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>144.74</v>
+        <v>-277.81</v>
       </c>
       <c r="L68" t="n">
-        <v>264.22</v>
+        <v>295.19</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:19:32</t>
+          <t>07:16:36</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>7.27</v>
+        <v>6.5</v>
       </c>
       <c r="F69" t="n">
-        <v>15.64</v>
+        <v>16.78</v>
       </c>
       <c r="G69" t="n">
-        <v>315.7</v>
+        <v>313.8</v>
       </c>
       <c r="H69" t="n">
-        <v>100</v>
+        <v>10.1</v>
       </c>
       <c r="I69" t="n">
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>149.85</v>
+        <v>31.35</v>
       </c>
       <c r="K69" t="n">
-        <v>-366.93</v>
+        <v>338.47</v>
       </c>
       <c r="L69" t="n">
-        <v>396.35</v>
+        <v>339.92</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:21:09</t>
+          <t>07:18:16</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>6.18</v>
+        <v>6.01</v>
       </c>
       <c r="F70" t="n">
-        <v>17.93</v>
+        <v>15.4</v>
       </c>
       <c r="G70" t="n">
-        <v>323.5</v>
+        <v>325.2</v>
       </c>
       <c r="H70" t="n">
-        <v>100</v>
+        <v>74.3</v>
       </c>
       <c r="I70" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J70" t="n">
-        <v>27.54</v>
+        <v>-55.78</v>
       </c>
       <c r="K70" t="n">
-        <v>16</v>
+        <v>225.44</v>
       </c>
       <c r="L70" t="n">
-        <v>31.85</v>
+        <v>232.24</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:26:35</t>
+          <t>07:24:03</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>5.92</v>
+        <v>6.67</v>
       </c>
       <c r="F71" t="n">
-        <v>12.04</v>
+        <v>17.31</v>
       </c>
       <c r="G71" t="n">
-        <v>337.5</v>
+        <v>312.6</v>
       </c>
       <c r="H71" t="n">
-        <v>97.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J71" t="n">
-        <v>-378.29</v>
+        <v>-315.73</v>
       </c>
       <c r="K71" t="n">
-        <v>-140.56</v>
+        <v>-264.35</v>
       </c>
       <c r="L71" t="n">
-        <v>403.56</v>
+        <v>411.78</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:29:01</t>
+          <t>07:25:29</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>5.97</v>
+        <v>7.34</v>
       </c>
       <c r="F72" t="n">
-        <v>15.87</v>
+        <v>17.85</v>
       </c>
       <c r="G72" t="n">
-        <v>327.4</v>
+        <v>332.3</v>
       </c>
       <c r="H72" t="n">
-        <v>98.2</v>
+        <v>51.9</v>
       </c>
       <c r="I72" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>227.34</v>
+        <v>-247.86</v>
       </c>
       <c r="K72" t="n">
-        <v>531.42</v>
+        <v>310.1</v>
       </c>
       <c r="L72" t="n">
-        <v>578.01</v>
+        <v>396.98</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:30:20</t>
+          <t>07:27:27</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>5.63</v>
+        <v>7.51</v>
       </c>
       <c r="F73" t="n">
-        <v>14.36</v>
+        <v>18.4</v>
       </c>
       <c r="G73" t="n">
-        <v>327.7</v>
+        <v>330.1</v>
       </c>
       <c r="H73" t="n">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-446.72</v>
+        <v>-268.22</v>
       </c>
       <c r="K73" t="n">
-        <v>-54.49</v>
+        <v>182.12</v>
       </c>
       <c r="L73" t="n">
-        <v>450.03</v>
+        <v>324.2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:38:41</t>
+          <t>07:38:56</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>7.11</v>
+        <v>7.37</v>
       </c>
       <c r="F74" t="n">
-        <v>17.09</v>
+        <v>18.4</v>
       </c>
       <c r="G74" t="n">
-        <v>315.3</v>
+        <v>347.4</v>
       </c>
       <c r="H74" t="n">
-        <v>100</v>
+        <v>78.7</v>
       </c>
       <c r="I74" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J74" t="n">
-        <v>47.2</v>
+        <v>83</v>
       </c>
       <c r="K74" t="n">
-        <v>69.97</v>
+        <v>82.67</v>
       </c>
       <c r="L74" t="n">
-        <v>84.40000000000001</v>
+        <v>117.14</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:40:54</t>
+          <t>07:39:49</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>6.57</v>
+        <v>6.67</v>
       </c>
       <c r="F75" t="n">
-        <v>18.4</v>
+        <v>17.28</v>
       </c>
       <c r="G75" t="n">
-        <v>329.6</v>
+        <v>328</v>
       </c>
       <c r="H75" t="n">
-        <v>95.5</v>
+        <v>20.3</v>
       </c>
       <c r="I75" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>77</v>
+        <v>-108.56</v>
       </c>
       <c r="K75" t="n">
-        <v>-14.69</v>
+        <v>-130.74</v>
       </c>
       <c r="L75" t="n">
-        <v>78.39</v>
+        <v>169.94</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:43:06</t>
+          <t>07:40:55</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>7.44</v>
+        <v>7.82</v>
       </c>
       <c r="F76" t="n">
-        <v>18.04</v>
+        <v>16.64</v>
       </c>
       <c r="G76" t="n">
-        <v>324.2</v>
+        <v>320.5</v>
       </c>
       <c r="H76" t="n">
-        <v>100</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J76" t="n">
-        <v>63.28</v>
+        <v>-18.63</v>
       </c>
       <c r="K76" t="n">
-        <v>40.69</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>75.23</v>
+        <v>98.05</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:47:44</t>
+          <t>07:45:39</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>6.51</v>
+        <v>7.21</v>
       </c>
       <c r="F77" t="n">
-        <v>16.28</v>
+        <v>18.4</v>
       </c>
       <c r="G77" t="n">
-        <v>326</v>
+        <v>335.4</v>
       </c>
       <c r="H77" t="n">
-        <v>100</v>
+        <v>39.6</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-85.04000000000001</v>
+        <v>-29.16</v>
       </c>
       <c r="K77" t="n">
-        <v>14.55</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>86.28</v>
+        <v>89.11</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:49:00</t>
+          <t>07:47:03</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>7.22</v>
+        <v>6.56</v>
       </c>
       <c r="F78" t="n">
-        <v>18.4</v>
+        <v>15.55</v>
       </c>
       <c r="G78" t="n">
-        <v>324</v>
+        <v>328.9</v>
       </c>
       <c r="H78" t="n">
-        <v>100</v>
+        <v>59.9</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>48.05</v>
+        <v>120.41</v>
       </c>
       <c r="K78" t="n">
-        <v>119.48</v>
+        <v>190.62</v>
       </c>
       <c r="L78" t="n">
-        <v>128.78</v>
+        <v>225.46</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:50:33</t>
+          <t>07:49:01</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>7.55</v>
+        <v>5.96</v>
       </c>
       <c r="F79" t="n">
-        <v>18.4</v>
+        <v>17.87</v>
       </c>
       <c r="G79" t="n">
-        <v>327.8</v>
+        <v>324.2</v>
       </c>
       <c r="H79" t="n">
-        <v>96.3</v>
+        <v>99.2</v>
       </c>
       <c r="I79" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>44</v>
+        <v>120.54</v>
       </c>
       <c r="K79" t="n">
-        <v>-129.79</v>
+        <v>98.36</v>
       </c>
       <c r="L79" t="n">
-        <v>137.05</v>
+        <v>155.58</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:54:58</t>
+          <t>07:54:48</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>6.27</v>
+        <v>6.63</v>
       </c>
       <c r="F80" t="n">
-        <v>14.69</v>
+        <v>18.4</v>
       </c>
       <c r="G80" t="n">
-        <v>320.4</v>
+        <v>328.2</v>
       </c>
       <c r="H80" t="n">
-        <v>100</v>
+        <v>67</v>
       </c>
       <c r="I80" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J80" t="n">
-        <v>116.93</v>
+        <v>111.25</v>
       </c>
       <c r="K80" t="n">
-        <v>193.69</v>
+        <v>239.89</v>
       </c>
       <c r="L80" t="n">
-        <v>226.25</v>
+        <v>264.43</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:56:56</t>
+          <t>07:56:11</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>7.69</v>
+        <v>6.84</v>
       </c>
       <c r="F81" t="n">
-        <v>18.4</v>
+        <v>16.46</v>
       </c>
       <c r="G81" t="n">
-        <v>337.6</v>
+        <v>329.7</v>
       </c>
       <c r="H81" t="n">
-        <v>100</v>
+        <v>61.4</v>
       </c>
       <c r="I81" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>-311.15</v>
+        <v>-5.67</v>
       </c>
       <c r="K81" t="n">
-        <v>-37.36</v>
+        <v>147.82</v>
       </c>
       <c r="L81" t="n">
-        <v>313.39</v>
+        <v>147.93</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:58:26</t>
+          <t>07:58:22</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>6.71</v>
+        <v>6.9</v>
       </c>
       <c r="F82" t="n">
-        <v>18.35</v>
+        <v>18.14</v>
       </c>
       <c r="G82" t="n">
-        <v>329.3</v>
+        <v>328.2</v>
       </c>
       <c r="H82" t="n">
-        <v>100</v>
+        <v>63.6</v>
       </c>
       <c r="I82" t="n">
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>-70.81</v>
+        <v>-33.13</v>
       </c>
       <c r="K82" t="n">
-        <v>145.59</v>
+        <v>240.92</v>
       </c>
       <c r="L82" t="n">
-        <v>161.89</v>
+        <v>243.19</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:02:21</t>
+          <t>08:04:04</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>7.49</v>
+        <v>6.45</v>
       </c>
       <c r="F83" t="n">
-        <v>18.4</v>
+        <v>16.64</v>
       </c>
       <c r="G83" t="n">
-        <v>325.4</v>
+        <v>324.4</v>
       </c>
       <c r="H83" t="n">
-        <v>97.09999999999999</v>
+        <v>61.2</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>-375.64</v>
+        <v>-206.56</v>
       </c>
       <c r="K83" t="n">
-        <v>38.83</v>
+        <v>236.66</v>
       </c>
       <c r="L83" t="n">
-        <v>377.64</v>
+        <v>314.13</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:04:16</t>
+          <t>08:06:17</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>7.76</v>
+        <v>7.11</v>
       </c>
       <c r="F84" t="n">
-        <v>18.4</v>
+        <v>17.5</v>
       </c>
       <c r="G84" t="n">
-        <v>332.7</v>
+        <v>344</v>
       </c>
       <c r="H84" t="n">
-        <v>100</v>
+        <v>80.7</v>
       </c>
       <c r="I84" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J84" t="n">
-        <v>-359.3</v>
+        <v>-284.17</v>
       </c>
       <c r="K84" t="n">
-        <v>267.39</v>
+        <v>-56.44</v>
       </c>
       <c r="L84" t="n">
-        <v>447.87</v>
+        <v>289.72</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:05:06</t>
+          <t>08:07:30</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>6.88</v>
+        <v>7.26</v>
       </c>
       <c r="F85" t="n">
-        <v>18.4</v>
+        <v>17.7</v>
       </c>
       <c r="G85" t="n">
-        <v>327.4</v>
+        <v>332.9</v>
       </c>
       <c r="H85" t="n">
-        <v>100</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J85" t="n">
-        <v>55.49</v>
+        <v>-36.67</v>
       </c>
       <c r="K85" t="n">
-        <v>436.74</v>
+        <v>-260.02</v>
       </c>
       <c r="L85" t="n">
-        <v>440.25</v>
+        <v>262.59</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:09:36</t>
+          <t>08:14:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>6.95</v>
+        <v>6.93</v>
       </c>
       <c r="F86" t="n">
-        <v>16.83</v>
+        <v>18.4</v>
       </c>
       <c r="G86" t="n">
-        <v>335.9</v>
+        <v>328.4</v>
       </c>
       <c r="H86" t="n">
-        <v>95.90000000000001</v>
+        <v>50.5</v>
       </c>
       <c r="I86" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J86" t="n">
-        <v>429.22</v>
+        <v>-286.14</v>
       </c>
       <c r="K86" t="n">
-        <v>95.59</v>
+        <v>395.34</v>
       </c>
       <c r="L86" t="n">
-        <v>439.73</v>
+        <v>488.03</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:11:46</t>
+          <t>08:15:30</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>6.06</v>
+        <v>5.92</v>
       </c>
       <c r="F87" t="n">
-        <v>10.41</v>
+        <v>14.64</v>
       </c>
       <c r="G87" t="n">
-        <v>311</v>
+        <v>325.8</v>
       </c>
       <c r="H87" t="n">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-445.1</v>
+        <v>105.96</v>
       </c>
       <c r="K87" t="n">
-        <v>6.37</v>
+        <v>199.91</v>
       </c>
       <c r="L87" t="n">
-        <v>445.15</v>
+        <v>226.25</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:12:45</t>
+          <t>08:17:05</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>7.65</v>
+        <v>7.15</v>
       </c>
       <c r="F88" t="n">
-        <v>18.4</v>
+        <v>16.7</v>
       </c>
       <c r="G88" t="n">
-        <v>343.6</v>
+        <v>323.3</v>
       </c>
       <c r="H88" t="n">
-        <v>99.3</v>
+        <v>94.5</v>
       </c>
       <c r="I88" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>-590.87</v>
+        <v>-85.63</v>
       </c>
       <c r="K88" t="n">
-        <v>-62</v>
+        <v>135.4</v>
       </c>
       <c r="L88" t="n">
-        <v>594.12</v>
+        <v>160.21</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-01.xlsx
+++ b/output/2025-07-01.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>5.99</v>
+        <v>5.86</v>
       </c>
       <c r="F14" t="n">
-        <v>12.49</v>
+        <v>14.21</v>
       </c>
       <c r="G14" t="n">
-        <v>323.1</v>
+        <v>335</v>
       </c>
       <c r="H14" t="n">
-        <v>59.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>64.68000000000001</v>
+        <v>-104.32</v>
       </c>
       <c r="K14" t="n">
-        <v>163</v>
+        <v>-41.66</v>
       </c>
       <c r="L14" t="n">
-        <v>175.36</v>
+        <v>112.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04:35:46</t>
+          <t>04:35:05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>6.07</v>
+        <v>4.79</v>
       </c>
       <c r="F15" t="n">
-        <v>13.88</v>
+        <v>9.42</v>
       </c>
       <c r="G15" t="n">
-        <v>336.1</v>
+        <v>329.8</v>
       </c>
       <c r="H15" t="n">
-        <v>59.8</v>
+        <v>65.2</v>
       </c>
       <c r="I15" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-118.35</v>
+        <v>73.04000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>35.96</v>
+        <v>71.23</v>
       </c>
       <c r="L15" t="n">
-        <v>123.7</v>
+        <v>102.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04:36:33</t>
+          <t>04:36:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>6.44</v>
+        <v>5.58</v>
       </c>
       <c r="F16" t="n">
-        <v>11.12</v>
+        <v>12.03</v>
       </c>
       <c r="G16" t="n">
-        <v>333</v>
+        <v>320.7</v>
       </c>
       <c r="H16" t="n">
-        <v>59.9</v>
+        <v>60.3</v>
       </c>
       <c r="I16" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-60.34</v>
+        <v>-108.49</v>
       </c>
       <c r="K16" t="n">
-        <v>-39.78</v>
+        <v>30.42</v>
       </c>
       <c r="L16" t="n">
-        <v>72.27</v>
+        <v>112.67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04:41:00</t>
+          <t>04:42:09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>5.36</v>
+        <v>6.07</v>
       </c>
       <c r="F17" t="n">
-        <v>6.88</v>
+        <v>13.44</v>
       </c>
       <c r="G17" t="n">
-        <v>329.2</v>
+        <v>326.5</v>
       </c>
       <c r="H17" t="n">
-        <v>85.8</v>
+        <v>7.6</v>
       </c>
       <c r="I17" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>20.11</v>
+        <v>35.36</v>
       </c>
       <c r="K17" t="n">
-        <v>132.72</v>
+        <v>197.36</v>
       </c>
       <c r="L17" t="n">
-        <v>134.24</v>
+        <v>200.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>04:42:08</t>
+          <t>04:44:07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>5.78</v>
+        <v>5.17</v>
       </c>
       <c r="F18" t="n">
-        <v>11.85</v>
+        <v>9.84</v>
       </c>
       <c r="G18" t="n">
-        <v>332.7</v>
+        <v>325.7</v>
       </c>
       <c r="H18" t="n">
-        <v>40.1</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>-62.97</v>
+        <v>-62.02</v>
       </c>
       <c r="K18" t="n">
-        <v>132.94</v>
+        <v>-120.74</v>
       </c>
       <c r="L18" t="n">
-        <v>147.1</v>
+        <v>135.74</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>04:44:32</t>
+          <t>04:45:46</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>5.99</v>
+        <v>6.39</v>
       </c>
       <c r="F19" t="n">
-        <v>13.49</v>
+        <v>12.4</v>
       </c>
       <c r="G19" t="n">
-        <v>323.6</v>
+        <v>328.3</v>
       </c>
       <c r="H19" t="n">
-        <v>71.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J19" t="n">
-        <v>-133.04</v>
+        <v>-120.85</v>
       </c>
       <c r="K19" t="n">
-        <v>134</v>
+        <v>-112.53</v>
       </c>
       <c r="L19" t="n">
-        <v>188.83</v>
+        <v>165.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>04:49:21</t>
+          <t>04:51:03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>5.2</v>
+        <v>5.64</v>
       </c>
       <c r="F20" t="n">
-        <v>10.92</v>
+        <v>10.74</v>
       </c>
       <c r="G20" t="n">
-        <v>345</v>
+        <v>318.6</v>
       </c>
       <c r="H20" t="n">
-        <v>51.4</v>
+        <v>59.1</v>
       </c>
       <c r="I20" t="n">
         <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>122.66</v>
+        <v>-60.66</v>
       </c>
       <c r="K20" t="n">
-        <v>100.3</v>
+        <v>167.37</v>
       </c>
       <c r="L20" t="n">
-        <v>158.45</v>
+        <v>178.02</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>04:50:31</t>
+          <t>04:52:15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>5.66</v>
+        <v>5.84</v>
       </c>
       <c r="F21" t="n">
-        <v>11.52</v>
+        <v>14.13</v>
       </c>
       <c r="G21" t="n">
-        <v>319.7</v>
+        <v>328.8</v>
       </c>
       <c r="H21" t="n">
-        <v>41.4</v>
+        <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-154.66</v>
+        <v>-39.13</v>
       </c>
       <c r="K21" t="n">
-        <v>40.77</v>
+        <v>293.08</v>
       </c>
       <c r="L21" t="n">
-        <v>159.94</v>
+        <v>295.68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>04:51:10</t>
+          <t>04:54:11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>6.31</v>
+        <v>6.97</v>
       </c>
       <c r="F22" t="n">
-        <v>11.59</v>
+        <v>15.74</v>
       </c>
       <c r="G22" t="n">
-        <v>329.8</v>
+        <v>324.5</v>
       </c>
       <c r="H22" t="n">
-        <v>58.1</v>
+        <v>59.3</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-191.39</v>
+        <v>-136.76</v>
       </c>
       <c r="K22" t="n">
-        <v>169.71</v>
+        <v>5.96</v>
       </c>
       <c r="L22" t="n">
-        <v>255.79</v>
+        <v>136.89</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>04:57:04</t>
+          <t>04:59:41</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>5.32</v>
+        <v>6.18</v>
       </c>
       <c r="F23" t="n">
-        <v>13.86</v>
+        <v>15.16</v>
       </c>
       <c r="G23" t="n">
-        <v>329.3</v>
+        <v>324.2</v>
       </c>
       <c r="H23" t="n">
-        <v>81.59999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="I23" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>253.94</v>
+        <v>182.51</v>
       </c>
       <c r="K23" t="n">
-        <v>-184.25</v>
+        <v>174.47</v>
       </c>
       <c r="L23" t="n">
-        <v>313.74</v>
+        <v>252.48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>04:58:44</t>
+          <t>05:01:14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>6.58</v>
+        <v>5.38</v>
       </c>
       <c r="F24" t="n">
-        <v>13.85</v>
+        <v>12.6</v>
       </c>
       <c r="G24" t="n">
-        <v>333</v>
+        <v>339.7</v>
       </c>
       <c r="H24" t="n">
-        <v>64.5</v>
+        <v>39.2</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-237.81</v>
+        <v>-232.08</v>
       </c>
       <c r="K24" t="n">
-        <v>413.39</v>
+        <v>-67.83</v>
       </c>
       <c r="L24" t="n">
-        <v>476.91</v>
+        <v>241.79</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:00:42</t>
+          <t>05:02:45</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>5.5</v>
+        <v>5.64</v>
       </c>
       <c r="F25" t="n">
-        <v>13.32</v>
+        <v>12.16</v>
       </c>
       <c r="G25" t="n">
-        <v>330.1</v>
+        <v>335.1</v>
       </c>
       <c r="H25" t="n">
-        <v>73.90000000000001</v>
+        <v>50.6</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-209.25</v>
+        <v>-103.79</v>
       </c>
       <c r="K25" t="n">
-        <v>207.33</v>
+        <v>-299.27</v>
       </c>
       <c r="L25" t="n">
-        <v>294.57</v>
+        <v>316.76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:06:46</t>
+          <t>05:07:04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>6.21</v>
+        <v>5.96</v>
       </c>
       <c r="F26" t="n">
-        <v>13.03</v>
+        <v>13.78</v>
       </c>
       <c r="G26" t="n">
-        <v>336.7</v>
+        <v>330.5</v>
       </c>
       <c r="H26" t="n">
-        <v>56</v>
+        <v>62.7</v>
       </c>
       <c r="I26" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J26" t="n">
-        <v>344.12</v>
+        <v>93.22</v>
       </c>
       <c r="K26" t="n">
-        <v>-268.55</v>
+        <v>297.38</v>
       </c>
       <c r="L26" t="n">
-        <v>436.51</v>
+        <v>311.65</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:08:18</t>
+          <t>05:08:41</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>5.52</v>
+        <v>7.03</v>
       </c>
       <c r="F27" t="n">
-        <v>12.58</v>
+        <v>15.51</v>
       </c>
       <c r="G27" t="n">
-        <v>356.8</v>
+        <v>331.1</v>
       </c>
       <c r="H27" t="n">
-        <v>67</v>
+        <v>53.4</v>
       </c>
       <c r="I27" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>-13.99</v>
+        <v>46.08</v>
       </c>
       <c r="K27" t="n">
-        <v>234.71</v>
+        <v>369.46</v>
       </c>
       <c r="L27" t="n">
-        <v>235.13</v>
+        <v>372.32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:08:58</t>
+          <t>05:09:36</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>6.53</v>
+        <v>6.42</v>
       </c>
       <c r="F28" t="n">
-        <v>16.58</v>
+        <v>16.81</v>
       </c>
       <c r="G28" t="n">
-        <v>327.5</v>
+        <v>335</v>
       </c>
       <c r="H28" t="n">
-        <v>52.4</v>
+        <v>56.6</v>
       </c>
       <c r="I28" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>-396.8</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>134.08</v>
+        <v>418.88</v>
       </c>
       <c r="L28" t="n">
-        <v>418.84</v>
+        <v>427.96</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:21:04</t>
+          <t>05:19:25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>6.31</v>
+        <v>6.17</v>
       </c>
       <c r="F29" t="n">
-        <v>14.84</v>
+        <v>14.32</v>
       </c>
       <c r="G29" t="n">
-        <v>334.9</v>
+        <v>324.3</v>
       </c>
       <c r="H29" t="n">
-        <v>51.5</v>
+        <v>83.3</v>
       </c>
       <c r="I29" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-44.08</v>
+        <v>-127.34</v>
       </c>
       <c r="K29" t="n">
-        <v>-145.82</v>
+        <v>-19.48</v>
       </c>
       <c r="L29" t="n">
-        <v>152.34</v>
+        <v>128.82</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:22:48</t>
+          <t>05:20:48</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>6.32</v>
+        <v>5.71</v>
       </c>
       <c r="F30" t="n">
-        <v>12.19</v>
+        <v>11.15</v>
       </c>
       <c r="G30" t="n">
-        <v>329.6</v>
+        <v>339.9</v>
       </c>
       <c r="H30" t="n">
-        <v>65.8</v>
+        <v>36.5</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>7.57</v>
+        <v>167.63</v>
       </c>
       <c r="K30" t="n">
-        <v>156.09</v>
+        <v>-14.96</v>
       </c>
       <c r="L30" t="n">
-        <v>156.27</v>
+        <v>168.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:25:06</t>
+          <t>05:22:16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>5.15</v>
+        <v>7.01</v>
       </c>
       <c r="F31" t="n">
-        <v>11.61</v>
+        <v>15.84</v>
       </c>
       <c r="G31" t="n">
-        <v>321.7</v>
+        <v>324.5</v>
       </c>
       <c r="H31" t="n">
-        <v>69.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I31" t="n">
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-44.18</v>
+        <v>53.56</v>
       </c>
       <c r="K31" t="n">
-        <v>16.94</v>
+        <v>105.14</v>
       </c>
       <c r="L31" t="n">
-        <v>47.32</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:30:16</t>
+          <t>05:26:03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>6.31</v>
+        <v>6.28</v>
       </c>
       <c r="F32" t="n">
-        <v>13.4</v>
+        <v>15.54</v>
       </c>
       <c r="G32" t="n">
-        <v>335.4</v>
+        <v>327</v>
       </c>
       <c r="H32" t="n">
-        <v>77.09999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="I32" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-158.02</v>
+        <v>-1.07</v>
       </c>
       <c r="K32" t="n">
-        <v>-128.35</v>
+        <v>153.98</v>
       </c>
       <c r="L32" t="n">
-        <v>203.58</v>
+        <v>153.98</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:31:39</t>
+          <t>05:26:38</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>6.48</v>
+        <v>6.77</v>
       </c>
       <c r="F33" t="n">
-        <v>15.96</v>
+        <v>15.26</v>
       </c>
       <c r="G33" t="n">
-        <v>327</v>
+        <v>322.5</v>
       </c>
       <c r="H33" t="n">
-        <v>66.59999999999999</v>
+        <v>53</v>
       </c>
       <c r="I33" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>-57.3</v>
+        <v>-159.35</v>
       </c>
       <c r="K33" t="n">
-        <v>108.62</v>
+        <v>-11.62</v>
       </c>
       <c r="L33" t="n">
-        <v>122.81</v>
+        <v>159.77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:33:15</t>
+          <t>05:27:53</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>5.26</v>
+        <v>6.18</v>
       </c>
       <c r="F34" t="n">
-        <v>11.74</v>
+        <v>13.15</v>
       </c>
       <c r="G34" t="n">
-        <v>323.8</v>
+        <v>320</v>
       </c>
       <c r="H34" t="n">
-        <v>87.90000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="I34" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>26.63</v>
+        <v>-100.51</v>
       </c>
       <c r="K34" t="n">
-        <v>-120.73</v>
+        <v>137.65</v>
       </c>
       <c r="L34" t="n">
-        <v>123.63</v>
+        <v>170.44</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:36:34</t>
+          <t>05:33:54</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>6.3</v>
+        <v>6.01</v>
       </c>
       <c r="F35" t="n">
-        <v>12.01</v>
+        <v>13.02</v>
       </c>
       <c r="G35" t="n">
-        <v>332.9</v>
+        <v>336.2</v>
       </c>
       <c r="H35" t="n">
-        <v>60.7</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>-68.61</v>
+        <v>-161.82</v>
       </c>
       <c r="K35" t="n">
-        <v>178.46</v>
+        <v>146.78</v>
       </c>
       <c r="L35" t="n">
-        <v>191.19</v>
+        <v>218.47</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:37:45</t>
+          <t>05:35:42</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>6.23</v>
+        <v>6.13</v>
       </c>
       <c r="F36" t="n">
-        <v>13.79</v>
+        <v>13.15</v>
       </c>
       <c r="G36" t="n">
-        <v>329.9</v>
+        <v>312.3</v>
       </c>
       <c r="H36" t="n">
-        <v>43.6</v>
+        <v>36.7</v>
       </c>
       <c r="I36" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>-203.46</v>
+        <v>-147.35</v>
       </c>
       <c r="K36" t="n">
-        <v>-166.82</v>
+        <v>17.36</v>
       </c>
       <c r="L36" t="n">
-        <v>263.1</v>
+        <v>148.37</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05:39:47</t>
+          <t>05:36:37</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>6.96</v>
+        <v>6.07</v>
       </c>
       <c r="F37" t="n">
-        <v>17.54</v>
+        <v>13.58</v>
       </c>
       <c r="G37" t="n">
-        <v>331.5</v>
+        <v>338</v>
       </c>
       <c r="H37" t="n">
-        <v>55.2</v>
+        <v>77.8</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J37" t="n">
-        <v>-157.48</v>
+        <v>133.27</v>
       </c>
       <c r="K37" t="n">
-        <v>188.43</v>
+        <v>122.12</v>
       </c>
       <c r="L37" t="n">
-        <v>245.57</v>
+        <v>180.76</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>05:44:44</t>
+          <t>05:41:16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>6.26</v>
+        <v>5.43</v>
       </c>
       <c r="F38" t="n">
-        <v>13.86</v>
+        <v>12.01</v>
       </c>
       <c r="G38" t="n">
-        <v>334.8</v>
+        <v>340.4</v>
       </c>
       <c r="H38" t="n">
-        <v>36.9</v>
+        <v>49.9</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-419.67</v>
+        <v>-146.43</v>
       </c>
       <c r="K38" t="n">
-        <v>200.49</v>
+        <v>233.56</v>
       </c>
       <c r="L38" t="n">
-        <v>465.1</v>
+        <v>275.67</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>05:46:46</t>
+          <t>05:42:48</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>6.38</v>
+        <v>5.41</v>
       </c>
       <c r="F39" t="n">
-        <v>13.9</v>
+        <v>14.33</v>
       </c>
       <c r="G39" t="n">
-        <v>331.2</v>
+        <v>317.5</v>
       </c>
       <c r="H39" t="n">
-        <v>86.2</v>
+        <v>60</v>
       </c>
       <c r="I39" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J39" t="n">
-        <v>-289.53</v>
+        <v>268.12</v>
       </c>
       <c r="K39" t="n">
-        <v>-97.95</v>
+        <v>155.74</v>
       </c>
       <c r="L39" t="n">
-        <v>305.65</v>
+        <v>310.07</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>05:48:38</t>
+          <t>05:44:59</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>7.31</v>
+        <v>6.64</v>
       </c>
       <c r="F40" t="n">
-        <v>18.4</v>
+        <v>14.86</v>
       </c>
       <c r="G40" t="n">
-        <v>330.7</v>
+        <v>337.9</v>
       </c>
       <c r="H40" t="n">
-        <v>100</v>
+        <v>40.5</v>
       </c>
       <c r="I40" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>120.43</v>
+        <v>260.38</v>
       </c>
       <c r="K40" t="n">
-        <v>332.62</v>
+        <v>-86.65000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>353.75</v>
+        <v>274.42</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05:53:54</t>
+          <t>05:49:19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>6.11</v>
+        <v>6.06</v>
       </c>
       <c r="F41" t="n">
-        <v>14.14</v>
+        <v>11.42</v>
       </c>
       <c r="G41" t="n">
-        <v>332.6</v>
+        <v>333.3</v>
       </c>
       <c r="H41" t="n">
-        <v>49.4</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-447.41</v>
+        <v>-169.13</v>
       </c>
       <c r="K41" t="n">
-        <v>188.33</v>
+        <v>333.34</v>
       </c>
       <c r="L41" t="n">
-        <v>485.43</v>
+        <v>373.79</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>05:55:20</t>
+          <t>05:50:41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>6</v>
+        <v>5.91</v>
       </c>
       <c r="F42" t="n">
-        <v>15.13</v>
+        <v>12.78</v>
       </c>
       <c r="G42" t="n">
-        <v>334.6</v>
+        <v>336.8</v>
       </c>
       <c r="H42" t="n">
-        <v>31.7</v>
+        <v>23.1</v>
       </c>
       <c r="I42" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>92.01000000000001</v>
+        <v>324.9</v>
       </c>
       <c r="K42" t="n">
-        <v>-510.95</v>
+        <v>-209.5</v>
       </c>
       <c r="L42" t="n">
-        <v>519.17</v>
+        <v>386.58</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>05:57:04</t>
+          <t>05:51:43</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>6.37</v>
+        <v>6.34</v>
       </c>
       <c r="F43" t="n">
-        <v>17.22</v>
+        <v>14.77</v>
       </c>
       <c r="G43" t="n">
-        <v>320.9</v>
+        <v>332.8</v>
       </c>
       <c r="H43" t="n">
-        <v>100</v>
+        <v>40.7</v>
       </c>
       <c r="I43" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>-253.73</v>
+        <v>-287.23</v>
       </c>
       <c r="K43" t="n">
-        <v>343.89</v>
+        <v>446.37</v>
       </c>
       <c r="L43" t="n">
-        <v>427.37</v>
+        <v>530.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:06:40</t>
+          <t>06:01:12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>6.15</v>
+        <v>5.13</v>
       </c>
       <c r="F44" t="n">
-        <v>13.56</v>
+        <v>12.83</v>
       </c>
       <c r="G44" t="n">
-        <v>330.9</v>
+        <v>327.1</v>
       </c>
       <c r="H44" t="n">
-        <v>76.7</v>
+        <v>20.7</v>
       </c>
       <c r="I44" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
-        <v>38.67</v>
+        <v>-84.51000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>140.1</v>
+        <v>-23.29</v>
       </c>
       <c r="L44" t="n">
-        <v>145.34</v>
+        <v>87.65000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:08:30</t>
+          <t>06:03:17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1930,31 +1930,31 @@
         <v>6.92</v>
       </c>
       <c r="F45" t="n">
-        <v>17.85</v>
+        <v>18.4</v>
       </c>
       <c r="G45" t="n">
-        <v>332.7</v>
+        <v>329.3</v>
       </c>
       <c r="H45" t="n">
-        <v>88.59999999999999</v>
+        <v>44.4</v>
       </c>
       <c r="I45" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J45" t="n">
-        <v>-109.59</v>
+        <v>69.58</v>
       </c>
       <c r="K45" t="n">
-        <v>46.78</v>
+        <v>109.55</v>
       </c>
       <c r="L45" t="n">
-        <v>119.15</v>
+        <v>129.77</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:09:40</t>
+          <t>06:05:01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>6.04</v>
+        <v>6.55</v>
       </c>
       <c r="F46" t="n">
-        <v>13.38</v>
+        <v>13.76</v>
       </c>
       <c r="G46" t="n">
-        <v>324.7</v>
+        <v>331</v>
       </c>
       <c r="H46" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I46" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>-75.03</v>
+        <v>-119.98</v>
       </c>
       <c r="K46" t="n">
-        <v>92.26000000000001</v>
+        <v>-68.2</v>
       </c>
       <c r="L46" t="n">
-        <v>118.92</v>
+        <v>138.02</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:13:04</t>
+          <t>06:08:15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>7.31</v>
+        <v>6.58</v>
       </c>
       <c r="F47" t="n">
-        <v>15.44</v>
+        <v>14.1</v>
       </c>
       <c r="G47" t="n">
-        <v>324.1</v>
+        <v>337.8</v>
       </c>
       <c r="H47" t="n">
-        <v>45.3</v>
+        <v>65</v>
       </c>
       <c r="I47" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-161.73</v>
+        <v>-138.49</v>
       </c>
       <c r="K47" t="n">
-        <v>66.93000000000001</v>
+        <v>-31.27</v>
       </c>
       <c r="L47" t="n">
-        <v>175.04</v>
+        <v>141.98</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:15:28</t>
+          <t>06:10:20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>6.15</v>
+        <v>7.37</v>
       </c>
       <c r="F48" t="n">
-        <v>14.61</v>
+        <v>18.4</v>
       </c>
       <c r="G48" t="n">
-        <v>332.9</v>
+        <v>314.5</v>
       </c>
       <c r="H48" t="n">
-        <v>92.59999999999999</v>
+        <v>38.5</v>
       </c>
       <c r="I48" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>59.01</v>
+        <v>-143.76</v>
       </c>
       <c r="K48" t="n">
-        <v>123.52</v>
+        <v>-84.55</v>
       </c>
       <c r="L48" t="n">
-        <v>136.89</v>
+        <v>166.79</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:16:41</t>
+          <t>06:11:55</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>7.8</v>
+        <v>5.84</v>
       </c>
       <c r="F49" t="n">
-        <v>17.95</v>
+        <v>14.31</v>
       </c>
       <c r="G49" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H49" t="n">
-        <v>23.2</v>
+        <v>27.8</v>
       </c>
       <c r="I49" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-199.27</v>
+        <v>-13.25</v>
       </c>
       <c r="K49" t="n">
-        <v>15.07</v>
+        <v>162.72</v>
       </c>
       <c r="L49" t="n">
-        <v>199.84</v>
+        <v>163.26</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:22:01</t>
+          <t>06:16:04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>6.23</v>
+        <v>5.43</v>
       </c>
       <c r="F50" t="n">
-        <v>18.2</v>
+        <v>13.07</v>
       </c>
       <c r="G50" t="n">
-        <v>325.2</v>
+        <v>327.5</v>
       </c>
       <c r="H50" t="n">
-        <v>64.40000000000001</v>
+        <v>40.6</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-171.5</v>
+        <v>-196.12</v>
       </c>
       <c r="K50" t="n">
-        <v>105.54</v>
+        <v>24.68</v>
       </c>
       <c r="L50" t="n">
-        <v>201.37</v>
+        <v>197.67</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:23:15</t>
+          <t>06:18:05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>6.08</v>
+        <v>7.01</v>
       </c>
       <c r="F51" t="n">
-        <v>15.01</v>
+        <v>18.18</v>
       </c>
       <c r="G51" t="n">
-        <v>336.5</v>
+        <v>317.9</v>
       </c>
       <c r="H51" t="n">
-        <v>82.09999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="I51" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-193.17</v>
+        <v>-66</v>
       </c>
       <c r="K51" t="n">
-        <v>143.93</v>
+        <v>-190.38</v>
       </c>
       <c r="L51" t="n">
-        <v>240.9</v>
+        <v>201.5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:25:36</t>
+          <t>06:19:57</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>6.84</v>
+        <v>7.22</v>
       </c>
       <c r="F52" t="n">
-        <v>14.18</v>
+        <v>17.46</v>
       </c>
       <c r="G52" t="n">
-        <v>331.3</v>
+        <v>335.1</v>
       </c>
       <c r="H52" t="n">
-        <v>35.6</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>-200.11</v>
+        <v>83.95</v>
       </c>
       <c r="K52" t="n">
-        <v>73.68000000000001</v>
+        <v>-94.51000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>213.24</v>
+        <v>126.41</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:28:49</t>
+          <t>06:24:51</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>6.65</v>
+        <v>6.41</v>
       </c>
       <c r="F53" t="n">
-        <v>15.41</v>
+        <v>16.84</v>
       </c>
       <c r="G53" t="n">
-        <v>321.4</v>
+        <v>328.8</v>
       </c>
       <c r="H53" t="n">
-        <v>81.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="I53" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>-252.21</v>
+        <v>-159.4</v>
       </c>
       <c r="K53" t="n">
-        <v>8.74</v>
+        <v>316.39</v>
       </c>
       <c r="L53" t="n">
-        <v>252.36</v>
+        <v>354.28</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:30:43</t>
+          <t>06:25:55</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>6.48</v>
+        <v>6.28</v>
       </c>
       <c r="F54" t="n">
-        <v>12.52</v>
+        <v>13.74</v>
       </c>
       <c r="G54" t="n">
-        <v>339</v>
+        <v>330.4</v>
       </c>
       <c r="H54" t="n">
-        <v>83</v>
+        <v>75.3</v>
       </c>
       <c r="I54" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>234.64</v>
+        <v>158.16</v>
       </c>
       <c r="K54" t="n">
-        <v>229.31</v>
+        <v>-236.71</v>
       </c>
       <c r="L54" t="n">
-        <v>328.09</v>
+        <v>284.68</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:31:24</t>
+          <t>06:27:56</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>6.43</v>
+        <v>5.91</v>
       </c>
       <c r="F55" t="n">
         <v>18.4</v>
       </c>
       <c r="G55" t="n">
-        <v>323.3</v>
+        <v>308.7</v>
       </c>
       <c r="H55" t="n">
-        <v>64.09999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-246.4</v>
+        <v>-283.06</v>
       </c>
       <c r="K55" t="n">
-        <v>25.35</v>
+        <v>-114.64</v>
       </c>
       <c r="L55" t="n">
-        <v>247.7</v>
+        <v>305.4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:37:09</t>
+          <t>06:33:20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>6.06</v>
+        <v>7.59</v>
       </c>
       <c r="F56" t="n">
-        <v>12.98</v>
+        <v>17.6</v>
       </c>
       <c r="G56" t="n">
-        <v>332.1</v>
+        <v>327.6</v>
       </c>
       <c r="H56" t="n">
-        <v>62</v>
+        <v>57.8</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>55.62</v>
+        <v>-167.41</v>
       </c>
       <c r="K56" t="n">
-        <v>-376</v>
+        <v>346.12</v>
       </c>
       <c r="L56" t="n">
-        <v>380.09</v>
+        <v>384.49</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>06:39:11</t>
+          <t>06:35:18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>6.89</v>
+        <v>6.17</v>
       </c>
       <c r="F57" t="n">
-        <v>16.97</v>
+        <v>13.51</v>
       </c>
       <c r="G57" t="n">
-        <v>332.8</v>
+        <v>333.2</v>
       </c>
       <c r="H57" t="n">
-        <v>63</v>
+        <v>76.3</v>
       </c>
       <c r="I57" t="n">
         <v>25</v>
       </c>
       <c r="J57" t="n">
-        <v>-397.97</v>
+        <v>-12.05</v>
       </c>
       <c r="K57" t="n">
-        <v>35.5</v>
+        <v>397.39</v>
       </c>
       <c r="L57" t="n">
-        <v>399.55</v>
+        <v>397.57</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>06:41:27</t>
+          <t>06:37:34</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>7.18</v>
+        <v>6.67</v>
       </c>
       <c r="F58" t="n">
-        <v>15.01</v>
+        <v>16.39</v>
       </c>
       <c r="G58" t="n">
-        <v>329.7</v>
+        <v>314.2</v>
       </c>
       <c r="H58" t="n">
-        <v>65.8</v>
+        <v>63</v>
       </c>
       <c r="I58" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-368.86</v>
+        <v>-484.52</v>
       </c>
       <c r="K58" t="n">
-        <v>-260.15</v>
+        <v>9.57</v>
       </c>
       <c r="L58" t="n">
-        <v>451.37</v>
+        <v>484.61</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>06:52:16</t>
+          <t>06:49:53</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>6.41</v>
+        <v>7.29</v>
       </c>
       <c r="F59" t="n">
-        <v>17.8</v>
+        <v>16.72</v>
       </c>
       <c r="G59" t="n">
-        <v>322.8</v>
+        <v>333.5</v>
       </c>
       <c r="H59" t="n">
-        <v>44.1</v>
+        <v>43.3</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-124.09</v>
+        <v>-73.39</v>
       </c>
       <c r="K59" t="n">
-        <v>92.98</v>
+        <v>108.35</v>
       </c>
       <c r="L59" t="n">
-        <v>155.06</v>
+        <v>130.87</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>06:53:18</t>
+          <t>06:51:49</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>7.45</v>
+        <v>7.13</v>
       </c>
       <c r="F60" t="n">
         <v>18.4</v>
       </c>
       <c r="G60" t="n">
-        <v>327</v>
+        <v>335.2</v>
       </c>
       <c r="H60" t="n">
-        <v>73.09999999999999</v>
+        <v>44.6</v>
       </c>
       <c r="I60" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-86.54000000000001</v>
+        <v>-119.38</v>
       </c>
       <c r="K60" t="n">
-        <v>99.97</v>
+        <v>118.47</v>
       </c>
       <c r="L60" t="n">
-        <v>132.23</v>
+        <v>168.18</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>06:54:57</t>
+          <t>06:53:15</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>7</v>
+        <v>6.06</v>
       </c>
       <c r="F61" t="n">
-        <v>17.15</v>
+        <v>15.23</v>
       </c>
       <c r="G61" t="n">
-        <v>317.1</v>
+        <v>331</v>
       </c>
       <c r="H61" t="n">
-        <v>45.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>-40.95</v>
+        <v>-79.91</v>
       </c>
       <c r="K61" t="n">
-        <v>-119.59</v>
+        <v>138.74</v>
       </c>
       <c r="L61" t="n">
-        <v>126.41</v>
+        <v>160.11</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>06:59:28</t>
+          <t>06:57:10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>6.56</v>
+        <v>5.6</v>
       </c>
       <c r="F62" t="n">
-        <v>16.71</v>
+        <v>15.55</v>
       </c>
       <c r="G62" t="n">
-        <v>306.3</v>
+        <v>324.1</v>
       </c>
       <c r="H62" t="n">
-        <v>59.4</v>
+        <v>48.4</v>
       </c>
       <c r="I62" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>149.79</v>
+        <v>-89.92</v>
       </c>
       <c r="K62" t="n">
-        <v>58.65</v>
+        <v>-118.7</v>
       </c>
       <c r="L62" t="n">
-        <v>160.86</v>
+        <v>148.92</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:00:20</t>
+          <t>06:58:25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>5.85</v>
+        <v>6.3</v>
       </c>
       <c r="F63" t="n">
-        <v>13.12</v>
+        <v>15.99</v>
       </c>
       <c r="G63" t="n">
-        <v>316.8</v>
+        <v>328.7</v>
       </c>
       <c r="H63" t="n">
-        <v>54.8</v>
+        <v>47.3</v>
       </c>
       <c r="I63" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>147.07</v>
+        <v>-214.49</v>
       </c>
       <c r="K63" t="n">
-        <v>86.83</v>
+        <v>36.89</v>
       </c>
       <c r="L63" t="n">
-        <v>170.79</v>
+        <v>217.64</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:01:21</t>
+          <t>06:59:27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>6.78</v>
+        <v>6.65</v>
       </c>
       <c r="F64" t="n">
-        <v>16.3</v>
+        <v>17.04</v>
       </c>
       <c r="G64" t="n">
-        <v>313.9</v>
+        <v>321.8</v>
       </c>
       <c r="H64" t="n">
-        <v>77.40000000000001</v>
+        <v>51.6</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-39.9</v>
+        <v>-146.6</v>
       </c>
       <c r="K64" t="n">
-        <v>174.91</v>
+        <v>147.3</v>
       </c>
       <c r="L64" t="n">
-        <v>179.4</v>
+        <v>207.82</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:06:55</t>
+          <t>07:04:34</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>5.85</v>
+        <v>6.54</v>
       </c>
       <c r="F65" t="n">
-        <v>14.38</v>
+        <v>17.97</v>
       </c>
       <c r="G65" t="n">
-        <v>325.2</v>
+        <v>326.5</v>
       </c>
       <c r="H65" t="n">
-        <v>82.2</v>
+        <v>86.7</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-172.22</v>
+        <v>181.21</v>
       </c>
       <c r="K65" t="n">
-        <v>73.39</v>
+        <v>97.8</v>
       </c>
       <c r="L65" t="n">
-        <v>187.21</v>
+        <v>205.91</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:08:42</t>
+          <t>07:06:37</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>6.74</v>
+        <v>6.63</v>
       </c>
       <c r="F66" t="n">
-        <v>15.96</v>
+        <v>17.59</v>
       </c>
       <c r="G66" t="n">
-        <v>337.4</v>
+        <v>319.2</v>
       </c>
       <c r="H66" t="n">
-        <v>61.7</v>
+        <v>50.8</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>16.73</v>
+        <v>-241.93</v>
       </c>
       <c r="K66" t="n">
-        <v>245.37</v>
+        <v>76.62</v>
       </c>
       <c r="L66" t="n">
-        <v>245.94</v>
+        <v>253.78</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:10:12</t>
+          <t>07:07:30</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>6.94</v>
+        <v>6.12</v>
       </c>
       <c r="F67" t="n">
-        <v>18.4</v>
+        <v>14.83</v>
       </c>
       <c r="G67" t="n">
-        <v>329</v>
+        <v>324.8</v>
       </c>
       <c r="H67" t="n">
-        <v>41.7</v>
+        <v>67</v>
       </c>
       <c r="I67" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-166.77</v>
+        <v>215.72</v>
       </c>
       <c r="K67" t="n">
-        <v>202.55</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>262.37</v>
+        <v>231.26</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:15:11</t>
+          <t>07:11:43</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>5.39</v>
+        <v>5.7</v>
       </c>
       <c r="F68" t="n">
-        <v>15.45</v>
+        <v>17.24</v>
       </c>
       <c r="G68" t="n">
-        <v>331</v>
+        <v>322.8</v>
       </c>
       <c r="H68" t="n">
-        <v>51.4</v>
+        <v>65.8</v>
       </c>
       <c r="I68" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>99.79000000000001</v>
+        <v>289.03</v>
       </c>
       <c r="K68" t="n">
-        <v>-277.81</v>
+        <v>60.4</v>
       </c>
       <c r="L68" t="n">
-        <v>295.19</v>
+        <v>295.27</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:16:36</t>
+          <t>07:13:16</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>6.5</v>
+        <v>7.15</v>
       </c>
       <c r="F69" t="n">
-        <v>16.78</v>
+        <v>18.29</v>
       </c>
       <c r="G69" t="n">
-        <v>313.8</v>
+        <v>327.7</v>
       </c>
       <c r="H69" t="n">
-        <v>10.1</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>31.35</v>
+        <v>131.89</v>
       </c>
       <c r="K69" t="n">
-        <v>338.47</v>
+        <v>-333.56</v>
       </c>
       <c r="L69" t="n">
-        <v>339.92</v>
+        <v>358.69</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:18:16</t>
+          <t>07:15:03</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>6.01</v>
+        <v>6.85</v>
       </c>
       <c r="F70" t="n">
-        <v>15.4</v>
+        <v>16.65</v>
       </c>
       <c r="G70" t="n">
-        <v>325.2</v>
+        <v>317.1</v>
       </c>
       <c r="H70" t="n">
-        <v>74.3</v>
+        <v>51.3</v>
       </c>
       <c r="I70" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J70" t="n">
-        <v>-55.78</v>
+        <v>-163.83</v>
       </c>
       <c r="K70" t="n">
-        <v>225.44</v>
+        <v>341.8</v>
       </c>
       <c r="L70" t="n">
-        <v>232.24</v>
+        <v>379.04</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:24:03</t>
+          <t>07:21:33</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>6.67</v>
+        <v>5.99</v>
       </c>
       <c r="F71" t="n">
-        <v>17.31</v>
+        <v>13.99</v>
       </c>
       <c r="G71" t="n">
-        <v>312.6</v>
+        <v>341.1</v>
       </c>
       <c r="H71" t="n">
-        <v>94.59999999999999</v>
+        <v>50.2</v>
       </c>
       <c r="I71" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-315.73</v>
+        <v>145.32</v>
       </c>
       <c r="K71" t="n">
-        <v>-264.35</v>
+        <v>342.35</v>
       </c>
       <c r="L71" t="n">
-        <v>411.78</v>
+        <v>371.92</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:25:29</t>
+          <t>07:23:29</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>7.34</v>
+        <v>7.3</v>
       </c>
       <c r="F72" t="n">
-        <v>17.85</v>
+        <v>18.4</v>
       </c>
       <c r="G72" t="n">
-        <v>332.3</v>
+        <v>332.2</v>
       </c>
       <c r="H72" t="n">
-        <v>51.9</v>
+        <v>54.9</v>
       </c>
       <c r="I72" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J72" t="n">
-        <v>-247.86</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>310.1</v>
+        <v>445.32</v>
       </c>
       <c r="L72" t="n">
-        <v>396.98</v>
+        <v>454.98</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:27:27</t>
+          <t>07:24:25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>7.51</v>
+        <v>6.38</v>
       </c>
       <c r="F73" t="n">
-        <v>18.4</v>
+        <v>16.56</v>
       </c>
       <c r="G73" t="n">
-        <v>330.1</v>
+        <v>336.8</v>
       </c>
       <c r="H73" t="n">
-        <v>100</v>
+        <v>59.7</v>
       </c>
       <c r="I73" t="n">
         <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-268.22</v>
+        <v>-290.13</v>
       </c>
       <c r="K73" t="n">
-        <v>182.12</v>
+        <v>358.57</v>
       </c>
       <c r="L73" t="n">
-        <v>324.2</v>
+        <v>461.25</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:38:56</t>
+          <t>07:33:51</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>7.37</v>
+        <v>7.25</v>
       </c>
       <c r="F74" t="n">
         <v>18.4</v>
       </c>
       <c r="G74" t="n">
-        <v>347.4</v>
+        <v>324.6</v>
       </c>
       <c r="H74" t="n">
-        <v>78.7</v>
+        <v>49.9</v>
       </c>
       <c r="I74" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J74" t="n">
-        <v>83</v>
+        <v>98.48</v>
       </c>
       <c r="K74" t="n">
-        <v>82.67</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>117.14</v>
+        <v>129.18</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:39:49</t>
+          <t>07:36:14</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>6.67</v>
+        <v>7.09</v>
       </c>
       <c r="F75" t="n">
-        <v>17.28</v>
+        <v>16.69</v>
       </c>
       <c r="G75" t="n">
-        <v>328</v>
+        <v>343.9</v>
       </c>
       <c r="H75" t="n">
-        <v>20.3</v>
+        <v>45.8</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-108.56</v>
+        <v>79.48</v>
       </c>
       <c r="K75" t="n">
-        <v>-130.74</v>
+        <v>81.31</v>
       </c>
       <c r="L75" t="n">
-        <v>169.94</v>
+        <v>113.7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>07:40:55</t>
+          <t>07:37:14</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>7.82</v>
+        <v>7.3</v>
       </c>
       <c r="F76" t="n">
-        <v>16.64</v>
+        <v>18.4</v>
       </c>
       <c r="G76" t="n">
-        <v>320.5</v>
+        <v>326.1</v>
       </c>
       <c r="H76" t="n">
-        <v>75.59999999999999</v>
+        <v>50.2</v>
       </c>
       <c r="I76" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-18.63</v>
+        <v>-9.58</v>
       </c>
       <c r="K76" t="n">
-        <v>96.26000000000001</v>
+        <v>143.2</v>
       </c>
       <c r="L76" t="n">
-        <v>98.05</v>
+        <v>143.52</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>07:45:39</t>
+          <t>07:42:01</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>7.21</v>
+        <v>5.9</v>
       </c>
       <c r="F77" t="n">
-        <v>18.4</v>
+        <v>12.31</v>
       </c>
       <c r="G77" t="n">
-        <v>335.4</v>
+        <v>339.3</v>
       </c>
       <c r="H77" t="n">
-        <v>39.6</v>
+        <v>31.7</v>
       </c>
       <c r="I77" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>-29.16</v>
+        <v>-93.18000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>84.20999999999999</v>
+        <v>139.44</v>
       </c>
       <c r="L77" t="n">
-        <v>89.11</v>
+        <v>167.7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>07:47:03</t>
+          <t>07:43:23</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>6.56</v>
+        <v>7.09</v>
       </c>
       <c r="F78" t="n">
-        <v>15.55</v>
+        <v>17.27</v>
       </c>
       <c r="G78" t="n">
-        <v>328.9</v>
+        <v>337.5</v>
       </c>
       <c r="H78" t="n">
-        <v>59.9</v>
+        <v>28.3</v>
       </c>
       <c r="I78" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>120.41</v>
+        <v>186.38</v>
       </c>
       <c r="K78" t="n">
-        <v>190.62</v>
+        <v>176.85</v>
       </c>
       <c r="L78" t="n">
-        <v>225.46</v>
+        <v>256.93</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>07:49:01</t>
+          <t>07:44:55</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>5.96</v>
+        <v>7.17</v>
       </c>
       <c r="F79" t="n">
-        <v>17.87</v>
+        <v>18.4</v>
       </c>
       <c r="G79" t="n">
-        <v>324.2</v>
+        <v>337.3</v>
       </c>
       <c r="H79" t="n">
-        <v>99.2</v>
+        <v>60.7</v>
       </c>
       <c r="I79" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>120.54</v>
+        <v>96.05</v>
       </c>
       <c r="K79" t="n">
-        <v>98.36</v>
+        <v>109.07</v>
       </c>
       <c r="L79" t="n">
-        <v>155.58</v>
+        <v>145.33</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>07:54:48</t>
+          <t>07:50:37</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>6.63</v>
+        <v>7.32</v>
       </c>
       <c r="F80" t="n">
-        <v>18.4</v>
+        <v>17.52</v>
       </c>
       <c r="G80" t="n">
-        <v>328.2</v>
+        <v>323.9</v>
       </c>
       <c r="H80" t="n">
-        <v>67</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>111.25</v>
+        <v>-240.31</v>
       </c>
       <c r="K80" t="n">
-        <v>239.89</v>
+        <v>-121.34</v>
       </c>
       <c r="L80" t="n">
-        <v>264.43</v>
+        <v>269.21</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>07:56:11</t>
+          <t>07:52:32</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>6.84</v>
+        <v>7.82</v>
       </c>
       <c r="F81" t="n">
-        <v>16.46</v>
+        <v>18.4</v>
       </c>
       <c r="G81" t="n">
-        <v>329.7</v>
+        <v>321.7</v>
       </c>
       <c r="H81" t="n">
-        <v>61.4</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J81" t="n">
-        <v>-5.67</v>
+        <v>-185.81</v>
       </c>
       <c r="K81" t="n">
-        <v>147.82</v>
+        <v>-120.99</v>
       </c>
       <c r="L81" t="n">
-        <v>147.93</v>
+        <v>221.73</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>07:58:22</t>
+          <t>07:54:21</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>6.9</v>
+        <v>6.44</v>
       </c>
       <c r="F82" t="n">
-        <v>18.14</v>
+        <v>14.09</v>
       </c>
       <c r="G82" t="n">
-        <v>328.2</v>
+        <v>330.5</v>
       </c>
       <c r="H82" t="n">
-        <v>63.6</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-33.13</v>
+        <v>283.44</v>
       </c>
       <c r="K82" t="n">
-        <v>240.92</v>
+        <v>54.36</v>
       </c>
       <c r="L82" t="n">
-        <v>243.19</v>
+        <v>288.6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:04:04</t>
+          <t>07:59:07</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>6.45</v>
+        <v>6.74</v>
       </c>
       <c r="F83" t="n">
-        <v>16.64</v>
+        <v>17.17</v>
       </c>
       <c r="G83" t="n">
-        <v>324.4</v>
+        <v>329.3</v>
       </c>
       <c r="H83" t="n">
-        <v>61.2</v>
+        <v>47.9</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>-206.56</v>
+        <v>35.39</v>
       </c>
       <c r="K83" t="n">
-        <v>236.66</v>
+        <v>461.64</v>
       </c>
       <c r="L83" t="n">
-        <v>314.13</v>
+        <v>462.99</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:06:17</t>
+          <t>08:00:46</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>7.11</v>
+        <v>6.66</v>
       </c>
       <c r="F84" t="n">
-        <v>17.5</v>
+        <v>14.55</v>
       </c>
       <c r="G84" t="n">
-        <v>344</v>
+        <v>332.2</v>
       </c>
       <c r="H84" t="n">
-        <v>80.7</v>
+        <v>86.2</v>
       </c>
       <c r="I84" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-284.17</v>
+        <v>-89.83</v>
       </c>
       <c r="K84" t="n">
-        <v>-56.44</v>
+        <v>-317.05</v>
       </c>
       <c r="L84" t="n">
-        <v>289.72</v>
+        <v>329.53</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:07:30</t>
+          <t>08:02:18</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>7.26</v>
+        <v>6.64</v>
       </c>
       <c r="F85" t="n">
-        <v>17.7</v>
+        <v>16.02</v>
       </c>
       <c r="G85" t="n">
-        <v>332.9</v>
+        <v>316.5</v>
       </c>
       <c r="H85" t="n">
-        <v>72.59999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="I85" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>-36.67</v>
+        <v>335.04</v>
       </c>
       <c r="K85" t="n">
-        <v>-260.02</v>
+        <v>-71.81999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>262.59</v>
+        <v>342.66</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:14:00</t>
+          <t>08:08:21</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>6.93</v>
+        <v>7.19</v>
       </c>
       <c r="F86" t="n">
-        <v>18.4</v>
+        <v>17.85</v>
       </c>
       <c r="G86" t="n">
-        <v>328.4</v>
+        <v>337.2</v>
       </c>
       <c r="H86" t="n">
-        <v>50.5</v>
+        <v>49.6</v>
       </c>
       <c r="I86" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>-286.14</v>
+        <v>419.36</v>
       </c>
       <c r="K86" t="n">
-        <v>395.34</v>
+        <v>-167.01</v>
       </c>
       <c r="L86" t="n">
-        <v>488.03</v>
+        <v>451.39</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:15:30</t>
+          <t>08:09:17</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>5.92</v>
+        <v>7.58</v>
       </c>
       <c r="F87" t="n">
-        <v>14.64</v>
+        <v>18.4</v>
       </c>
       <c r="G87" t="n">
-        <v>325.8</v>
+        <v>326.5</v>
       </c>
       <c r="H87" t="n">
-        <v>84.09999999999999</v>
+        <v>46</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>105.96</v>
+        <v>-429.31</v>
       </c>
       <c r="K87" t="n">
-        <v>199.91</v>
+        <v>313.21</v>
       </c>
       <c r="L87" t="n">
-        <v>226.25</v>
+        <v>531.42</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:17:05</t>
+          <t>08:10:36</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>7.15</v>
+        <v>6.48</v>
       </c>
       <c r="F88" t="n">
-        <v>16.7</v>
+        <v>17.57</v>
       </c>
       <c r="G88" t="n">
-        <v>323.3</v>
+        <v>326.4</v>
       </c>
       <c r="H88" t="n">
-        <v>94.5</v>
+        <v>81.8</v>
       </c>
       <c r="I88" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-85.63</v>
+        <v>68.03</v>
       </c>
       <c r="K88" t="n">
-        <v>135.4</v>
+        <v>324.8</v>
       </c>
       <c r="L88" t="n">
-        <v>160.21</v>
+        <v>331.85</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-01.xlsx
+++ b/output/2025-07-01.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>65.97</v>
+        <v>76.87</v>
       </c>
       <c r="K14" t="n">
-        <v>69.90000000000001</v>
+        <v>81.45</v>
       </c>
       <c r="L14" t="n">
-        <v>96.12</v>
+        <v>111.99</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>109.89</v>
+        <v>127.44</v>
       </c>
       <c r="K15" t="n">
-        <v>38.59</v>
+        <v>44.75</v>
       </c>
       <c r="L15" t="n">
-        <v>116.47</v>
+        <v>135.07</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-99.78</v>
+        <v>-113.02</v>
       </c>
       <c r="K16" t="n">
-        <v>87.73999999999999</v>
+        <v>99.38</v>
       </c>
       <c r="L16" t="n">
-        <v>132.87</v>
+        <v>150.5</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>48.98</v>
+        <v>62.3</v>
       </c>
       <c r="K17" t="n">
-        <v>75.13</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>89.69</v>
+        <v>114.08</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>83.51000000000001</v>
+        <v>104.46</v>
       </c>
       <c r="K18" t="n">
-        <v>-72.8</v>
+        <v>-91.06</v>
       </c>
       <c r="L18" t="n">
-        <v>110.79</v>
+        <v>138.58</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>1.51</v>
+        <v>2.03</v>
       </c>
       <c r="K19" t="n">
-        <v>101.79</v>
+        <v>137.33</v>
       </c>
       <c r="L19" t="n">
-        <v>101.8</v>
+        <v>137.35</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-102.29</v>
+        <v>-124.86</v>
       </c>
       <c r="K20" t="n">
-        <v>181.61</v>
+        <v>221.68</v>
       </c>
       <c r="L20" t="n">
-        <v>208.44</v>
+        <v>254.43</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>137.04</v>
+        <v>176.52</v>
       </c>
       <c r="K21" t="n">
-        <v>-90.45999999999999</v>
+        <v>-116.53</v>
       </c>
       <c r="L21" t="n">
-        <v>164.2</v>
+        <v>211.52</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>-171.3</v>
+        <v>-212.57</v>
       </c>
       <c r="K22" t="n">
-        <v>105.61</v>
+        <v>131.05</v>
       </c>
       <c r="L22" t="n">
-        <v>201.24</v>
+        <v>249.71</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>379.84</v>
+        <v>487.54</v>
       </c>
       <c r="K23" t="n">
-        <v>80.81999999999999</v>
+        <v>103.74</v>
       </c>
       <c r="L23" t="n">
-        <v>388.34</v>
+        <v>498.46</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-46.78</v>
+        <v>-63.83</v>
       </c>
       <c r="K24" t="n">
-        <v>276.01</v>
+        <v>376.63</v>
       </c>
       <c r="L24" t="n">
-        <v>279.95</v>
+        <v>382</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>18</v>
       </c>
       <c r="J25" t="n">
-        <v>134.96</v>
+        <v>191.73</v>
       </c>
       <c r="K25" t="n">
-        <v>142.09</v>
+        <v>201.85</v>
       </c>
       <c r="L25" t="n">
-        <v>195.97</v>
+        <v>278.39</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>17</v>
       </c>
       <c r="J26" t="n">
-        <v>486.77</v>
+        <v>697.15</v>
       </c>
       <c r="K26" t="n">
-        <v>214.97</v>
+        <v>307.87</v>
       </c>
       <c r="L26" t="n">
-        <v>532.12</v>
+        <v>762.11</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>-137.99</v>
+        <v>-202.77</v>
       </c>
       <c r="K27" t="n">
-        <v>-329.4</v>
+        <v>-484.04</v>
       </c>
       <c r="L27" t="n">
-        <v>357.13</v>
+        <v>524.79</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>304.33</v>
+        <v>411.46</v>
       </c>
       <c r="K28" t="n">
-        <v>424.03</v>
+        <v>573.3</v>
       </c>
       <c r="L28" t="n">
-        <v>521.9400000000001</v>
+        <v>705.67</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>-27.95</v>
+        <v>-34.01</v>
       </c>
       <c r="K29" t="n">
-        <v>77.87</v>
+        <v>94.75</v>
       </c>
       <c r="L29" t="n">
-        <v>82.73999999999999</v>
+        <v>100.67</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>25.25</v>
+        <v>30.97</v>
       </c>
       <c r="K30" t="n">
-        <v>89.83</v>
+        <v>110.19</v>
       </c>
       <c r="L30" t="n">
-        <v>93.31</v>
+        <v>114.46</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-35.73</v>
+        <v>-45.01</v>
       </c>
       <c r="K31" t="n">
-        <v>64.98</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>74.16</v>
+        <v>93.41</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>-111.45</v>
+        <v>-143.06</v>
       </c>
       <c r="K32" t="n">
-        <v>-24.18</v>
+        <v>-31.04</v>
       </c>
       <c r="L32" t="n">
-        <v>114.05</v>
+        <v>146.39</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-8.6</v>
+        <v>-10.26</v>
       </c>
       <c r="K33" t="n">
-        <v>-138.38</v>
+        <v>-165.11</v>
       </c>
       <c r="L33" t="n">
-        <v>138.65</v>
+        <v>165.42</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-101.02</v>
+        <v>-135.25</v>
       </c>
       <c r="K34" t="n">
-        <v>21.24</v>
+        <v>28.44</v>
       </c>
       <c r="L34" t="n">
-        <v>103.23</v>
+        <v>138.2</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>16</v>
       </c>
       <c r="J35" t="n">
-        <v>-33.54</v>
+        <v>-44.69</v>
       </c>
       <c r="K35" t="n">
-        <v>-177.13</v>
+        <v>-236.07</v>
       </c>
       <c r="L35" t="n">
-        <v>180.27</v>
+        <v>240.26</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>19</v>
       </c>
       <c r="J36" t="n">
-        <v>-63.77</v>
+        <v>-81.06999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-162.99</v>
+        <v>-207.2</v>
       </c>
       <c r="L36" t="n">
-        <v>175.03</v>
+        <v>222.5</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-38.18</v>
+        <v>-44.85</v>
       </c>
       <c r="K37" t="n">
-        <v>299.63</v>
+        <v>351.95</v>
       </c>
       <c r="L37" t="n">
-        <v>302.05</v>
+        <v>354.79</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>16</v>
       </c>
       <c r="J38" t="n">
-        <v>-145.87</v>
+        <v>-192.51</v>
       </c>
       <c r="K38" t="n">
-        <v>383.86</v>
+        <v>506.62</v>
       </c>
       <c r="L38" t="n">
-        <v>410.64</v>
+        <v>541.97</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>20</v>
       </c>
       <c r="J39" t="n">
-        <v>199.48</v>
+        <v>289.66</v>
       </c>
       <c r="K39" t="n">
-        <v>-128.68</v>
+        <v>-186.85</v>
       </c>
       <c r="L39" t="n">
-        <v>237.38</v>
+        <v>344.7</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>212.13</v>
+        <v>303.94</v>
       </c>
       <c r="K40" t="n">
-        <v>177.09</v>
+        <v>253.73</v>
       </c>
       <c r="L40" t="n">
-        <v>276.34</v>
+        <v>395.93</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>-82.05</v>
+        <v>-124.17</v>
       </c>
       <c r="K41" t="n">
-        <v>-407.66</v>
+        <v>-616.97</v>
       </c>
       <c r="L41" t="n">
-        <v>415.84</v>
+        <v>629.34</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>7.83</v>
+        <v>10.49</v>
       </c>
       <c r="K42" t="n">
-        <v>504.89</v>
+        <v>676.36</v>
       </c>
       <c r="L42" t="n">
-        <v>504.95</v>
+        <v>676.4400000000001</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>22</v>
       </c>
       <c r="J43" t="n">
-        <v>-83.88</v>
+        <v>-121.51</v>
       </c>
       <c r="K43" t="n">
-        <v>-460.8</v>
+        <v>-667.55</v>
       </c>
       <c r="L43" t="n">
-        <v>468.38</v>
+        <v>678.51</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>38.76</v>
+        <v>52.79</v>
       </c>
       <c r="K44" t="n">
-        <v>-50.36</v>
+        <v>-68.59</v>
       </c>
       <c r="L44" t="n">
-        <v>63.55</v>
+        <v>86.55</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>63.07</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>-135.52</v>
+        <v>-155.32</v>
       </c>
       <c r="L45" t="n">
-        <v>149.48</v>
+        <v>171.32</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-111.32</v>
+        <v>-131.82</v>
       </c>
       <c r="K46" t="n">
-        <v>30.05</v>
+        <v>35.58</v>
       </c>
       <c r="L46" t="n">
-        <v>115.31</v>
+        <v>136.53</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-77.5</v>
+        <v>-95.09</v>
       </c>
       <c r="K47" t="n">
-        <v>129.19</v>
+        <v>158.52</v>
       </c>
       <c r="L47" t="n">
-        <v>150.65</v>
+        <v>184.85</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>102.14</v>
+        <v>120.14</v>
       </c>
       <c r="K48" t="n">
-        <v>94.38</v>
+        <v>111.01</v>
       </c>
       <c r="L48" t="n">
-        <v>139.07</v>
+        <v>163.57</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>15.25</v>
+        <v>18.9</v>
       </c>
       <c r="K49" t="n">
-        <v>-123.04</v>
+        <v>-152.56</v>
       </c>
       <c r="L49" t="n">
-        <v>123.98</v>
+        <v>153.72</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>41.03</v>
+        <v>56.15</v>
       </c>
       <c r="K50" t="n">
-        <v>154.4</v>
+        <v>211.27</v>
       </c>
       <c r="L50" t="n">
-        <v>159.76</v>
+        <v>218.6</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-122.24</v>
+        <v>-175.23</v>
       </c>
       <c r="K51" t="n">
-        <v>-28.87</v>
+        <v>-41.38</v>
       </c>
       <c r="L51" t="n">
-        <v>125.6</v>
+        <v>180.05</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>19</v>
       </c>
       <c r="J52" t="n">
-        <v>-77.20999999999999</v>
+        <v>-94.66</v>
       </c>
       <c r="K52" t="n">
-        <v>224.79</v>
+        <v>275.58</v>
       </c>
       <c r="L52" t="n">
-        <v>237.68</v>
+        <v>291.38</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>57.94</v>
+        <v>82.37</v>
       </c>
       <c r="K53" t="n">
-        <v>-288.51</v>
+        <v>-410.18</v>
       </c>
       <c r="L53" t="n">
-        <v>294.27</v>
+        <v>418.37</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>18</v>
       </c>
       <c r="J54" t="n">
-        <v>298.01</v>
+        <v>401.17</v>
       </c>
       <c r="K54" t="n">
-        <v>64.14</v>
+        <v>86.34</v>
       </c>
       <c r="L54" t="n">
-        <v>304.83</v>
+        <v>410.36</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-208.49</v>
+        <v>-294.24</v>
       </c>
       <c r="K55" t="n">
-        <v>-117.68</v>
+        <v>-166.09</v>
       </c>
       <c r="L55" t="n">
-        <v>239.41</v>
+        <v>337.88</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>21</v>
       </c>
       <c r="J56" t="n">
-        <v>463.07</v>
+        <v>635.3099999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>38.1</v>
+        <v>52.28</v>
       </c>
       <c r="L56" t="n">
-        <v>464.63</v>
+        <v>637.46</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>17</v>
       </c>
       <c r="J57" t="n">
-        <v>-385.94</v>
+        <v>-581.98</v>
       </c>
       <c r="K57" t="n">
-        <v>-111.19</v>
+        <v>-167.67</v>
       </c>
       <c r="L57" t="n">
-        <v>401.64</v>
+        <v>605.65</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>17</v>
       </c>
       <c r="J58" t="n">
-        <v>64.29000000000001</v>
+        <v>90.31</v>
       </c>
       <c r="K58" t="n">
-        <v>601.6799999999999</v>
+        <v>845.24</v>
       </c>
       <c r="L58" t="n">
-        <v>605.11</v>
+        <v>850.05</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-55.46</v>
+        <v>-67.89</v>
       </c>
       <c r="K59" t="n">
-        <v>68.73999999999999</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>88.33</v>
+        <v>108.12</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-105.1</v>
+        <v>-127.23</v>
       </c>
       <c r="K60" t="n">
-        <v>85.39</v>
+        <v>103.38</v>
       </c>
       <c r="L60" t="n">
-        <v>135.42</v>
+        <v>163.94</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-85.39</v>
+        <v>-105.23</v>
       </c>
       <c r="K61" t="n">
-        <v>9.35</v>
+        <v>11.52</v>
       </c>
       <c r="L61" t="n">
-        <v>85.90000000000001</v>
+        <v>105.86</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>167.82</v>
+        <v>197.28</v>
       </c>
       <c r="K62" t="n">
-        <v>-35.21</v>
+        <v>-41.39</v>
       </c>
       <c r="L62" t="n">
-        <v>171.47</v>
+        <v>201.58</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-54.79</v>
+        <v>-66.95999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-119.67</v>
+        <v>-146.25</v>
       </c>
       <c r="L63" t="n">
-        <v>131.61</v>
+        <v>160.85</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-105.04</v>
+        <v>-134.22</v>
       </c>
       <c r="K64" t="n">
-        <v>31.76</v>
+        <v>40.58</v>
       </c>
       <c r="L64" t="n">
-        <v>109.74</v>
+        <v>140.22</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>-158.26</v>
+        <v>-192.62</v>
       </c>
       <c r="K65" t="n">
-        <v>-156.2</v>
+        <v>-190.12</v>
       </c>
       <c r="L65" t="n">
-        <v>222.37</v>
+        <v>270.65</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>18</v>
       </c>
       <c r="J66" t="n">
-        <v>-175.12</v>
+        <v>-231.13</v>
       </c>
       <c r="K66" t="n">
-        <v>86.44</v>
+        <v>114.08</v>
       </c>
       <c r="L66" t="n">
-        <v>195.29</v>
+        <v>257.75</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>-201.31</v>
+        <v>-267.79</v>
       </c>
       <c r="K67" t="n">
-        <v>29.68</v>
+        <v>39.48</v>
       </c>
       <c r="L67" t="n">
-        <v>203.49</v>
+        <v>270.69</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>112.59</v>
+        <v>154.29</v>
       </c>
       <c r="K68" t="n">
-        <v>354.32</v>
+        <v>485.54</v>
       </c>
       <c r="L68" t="n">
-        <v>371.78</v>
+        <v>509.47</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>-386.02</v>
+        <v>-515.91</v>
       </c>
       <c r="K69" t="n">
-        <v>2.08</v>
+        <v>2.77</v>
       </c>
       <c r="L69" t="n">
-        <v>386.03</v>
+        <v>515.92</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-285.21</v>
+        <v>-405.2</v>
       </c>
       <c r="K70" t="n">
-        <v>244.65</v>
+        <v>347.58</v>
       </c>
       <c r="L70" t="n">
-        <v>375.76</v>
+        <v>533.85</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>350.57</v>
+        <v>486.6</v>
       </c>
       <c r="K71" t="n">
-        <v>431.33</v>
+        <v>598.7</v>
       </c>
       <c r="L71" t="n">
-        <v>555.83</v>
+        <v>771.5</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-415.63</v>
+        <v>-636.96</v>
       </c>
       <c r="K72" t="n">
-        <v>-42.07</v>
+        <v>-64.48</v>
       </c>
       <c r="L72" t="n">
-        <v>417.76</v>
+        <v>640.22</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>-613.1</v>
+        <v>-819.27</v>
       </c>
       <c r="K73" t="n">
-        <v>3.12</v>
+        <v>4.17</v>
       </c>
       <c r="L73" t="n">
-        <v>613.11</v>
+        <v>819.28</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>55.01</v>
+        <v>63.83</v>
       </c>
       <c r="K74" t="n">
-        <v>-94.40000000000001</v>
+        <v>-109.53</v>
       </c>
       <c r="L74" t="n">
-        <v>109.26</v>
+        <v>126.77</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-92.47</v>
+        <v>-114.52</v>
       </c>
       <c r="K75" t="n">
-        <v>4.81</v>
+        <v>5.95</v>
       </c>
       <c r="L75" t="n">
-        <v>92.59</v>
+        <v>114.68</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>78.68000000000001</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>-43.52</v>
+        <v>-53.18</v>
       </c>
       <c r="L76" t="n">
-        <v>89.92</v>
+        <v>109.87</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-6.85</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-94.5</v>
+        <v>-130.57</v>
       </c>
       <c r="L77" t="n">
-        <v>94.73999999999999</v>
+        <v>130.91</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>18.24</v>
+        <v>24.38</v>
       </c>
       <c r="K78" t="n">
-        <v>-101.64</v>
+        <v>-135.84</v>
       </c>
       <c r="L78" t="n">
-        <v>103.26</v>
+        <v>138.01</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-113.24</v>
+        <v>-144.72</v>
       </c>
       <c r="K79" t="n">
-        <v>-16.07</v>
+        <v>-20.54</v>
       </c>
       <c r="L79" t="n">
-        <v>114.37</v>
+        <v>146.18</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-8.4</v>
+        <v>-11.06</v>
       </c>
       <c r="K80" t="n">
-        <v>-200.8</v>
+        <v>-264.46</v>
       </c>
       <c r="L80" t="n">
-        <v>200.97</v>
+        <v>264.69</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>17</v>
       </c>
       <c r="J81" t="n">
-        <v>-6.94</v>
+        <v>-9.06</v>
       </c>
       <c r="K81" t="n">
-        <v>211.29</v>
+        <v>275.74</v>
       </c>
       <c r="L81" t="n">
-        <v>211.4</v>
+        <v>275.89</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>220.45</v>
+        <v>281.68</v>
       </c>
       <c r="K82" t="n">
-        <v>22.63</v>
+        <v>28.91</v>
       </c>
       <c r="L82" t="n">
-        <v>221.6</v>
+        <v>283.16</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-147.08</v>
+        <v>-186.4</v>
       </c>
       <c r="K83" t="n">
-        <v>491.09</v>
+        <v>622.38</v>
       </c>
       <c r="L83" t="n">
-        <v>512.64</v>
+        <v>649.6900000000001</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>18</v>
       </c>
       <c r="J84" t="n">
-        <v>-88.63</v>
+        <v>-130.81</v>
       </c>
       <c r="K84" t="n">
-        <v>-276.37</v>
+        <v>-407.88</v>
       </c>
       <c r="L84" t="n">
-        <v>290.23</v>
+        <v>428.34</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>89.15000000000001</v>
+        <v>116.27</v>
       </c>
       <c r="K85" t="n">
-        <v>465.91</v>
+        <v>607.7</v>
       </c>
       <c r="L85" t="n">
-        <v>474.36</v>
+        <v>618.72</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>433.26</v>
+        <v>635.98</v>
       </c>
       <c r="K86" t="n">
-        <v>-19.52</v>
+        <v>-28.65</v>
       </c>
       <c r="L86" t="n">
-        <v>433.7</v>
+        <v>636.63</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>-419.99</v>
+        <v>-629.1</v>
       </c>
       <c r="K87" t="n">
-        <v>-15.54</v>
+        <v>-23.28</v>
       </c>
       <c r="L87" t="n">
-        <v>420.28</v>
+        <v>629.53</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>20</v>
       </c>
       <c r="J88" t="n">
-        <v>-532.34</v>
+        <v>-719.26</v>
       </c>
       <c r="K88" t="n">
-        <v>-144.74</v>
+        <v>-195.56</v>
       </c>
       <c r="L88" t="n">
-        <v>551.66</v>
+        <v>745.38</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-07-01.xlsx
+++ b/output/2025-07-01.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>76.87</v>
+        <v>133.39</v>
       </c>
       <c r="K14" t="n">
-        <v>81.45</v>
+        <v>141.35</v>
       </c>
       <c r="L14" t="n">
-        <v>111.99</v>
+        <v>194.35</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>127.44</v>
+        <v>250.65</v>
       </c>
       <c r="K15" t="n">
-        <v>44.75</v>
+        <v>88.01000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>135.07</v>
+        <v>265.65</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>-113.02</v>
+        <v>-203.44</v>
       </c>
       <c r="K16" t="n">
-        <v>99.38</v>
+        <v>178.88</v>
       </c>
       <c r="L16" t="n">
-        <v>150.5</v>
+        <v>270.9</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>62.3</v>
+        <v>91.66</v>
       </c>
       <c r="K17" t="n">
-        <v>95.56999999999999</v>
+        <v>140.6</v>
       </c>
       <c r="L17" t="n">
-        <v>114.08</v>
+        <v>167.84</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>104.46</v>
+        <v>157.29</v>
       </c>
       <c r="K18" t="n">
-        <v>-91.06</v>
+        <v>-137.11</v>
       </c>
       <c r="L18" t="n">
-        <v>138.58</v>
+        <v>208.66</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>2.03</v>
+        <v>3.52</v>
       </c>
       <c r="K19" t="n">
-        <v>137.33</v>
+        <v>238.16</v>
       </c>
       <c r="L19" t="n">
-        <v>137.35</v>
+        <v>238.18</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>17</v>
       </c>
       <c r="J29" t="n">
-        <v>-34.01</v>
+        <v>-58.19</v>
       </c>
       <c r="K29" t="n">
-        <v>94.75</v>
+        <v>162.13</v>
       </c>
       <c r="L29" t="n">
-        <v>100.67</v>
+        <v>172.25</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>17</v>
       </c>
       <c r="J30" t="n">
-        <v>30.97</v>
+        <v>57.49</v>
       </c>
       <c r="K30" t="n">
-        <v>110.19</v>
+        <v>204.53</v>
       </c>
       <c r="L30" t="n">
-        <v>114.46</v>
+        <v>212.45</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>20</v>
       </c>
       <c r="J31" t="n">
-        <v>-45.01</v>
+        <v>-80.04000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>81.84999999999999</v>
+        <v>145.56</v>
       </c>
       <c r="L31" t="n">
-        <v>93.41</v>
+        <v>166.12</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>-143.06</v>
+        <v>-240.55</v>
       </c>
       <c r="K32" t="n">
-        <v>-31.04</v>
+        <v>-52.19</v>
       </c>
       <c r="L32" t="n">
-        <v>146.39</v>
+        <v>246.15</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>17</v>
       </c>
       <c r="J33" t="n">
-        <v>-10.26</v>
+        <v>-15.9</v>
       </c>
       <c r="K33" t="n">
-        <v>-165.11</v>
+        <v>-255.81</v>
       </c>
       <c r="L33" t="n">
-        <v>165.42</v>
+        <v>256.3</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>-135.25</v>
+        <v>-242.7</v>
       </c>
       <c r="K34" t="n">
-        <v>28.44</v>
+        <v>51.03</v>
       </c>
       <c r="L34" t="n">
-        <v>138.2</v>
+        <v>248.01</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>52.79</v>
+        <v>104.84</v>
       </c>
       <c r="K44" t="n">
-        <v>-68.59</v>
+        <v>-136.22</v>
       </c>
       <c r="L44" t="n">
-        <v>86.55</v>
+        <v>171.9</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>72.29000000000001</v>
+        <v>149.63</v>
       </c>
       <c r="K45" t="n">
-        <v>-155.32</v>
+        <v>-321.51</v>
       </c>
       <c r="L45" t="n">
-        <v>171.32</v>
+        <v>354.63</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-131.82</v>
+        <v>-258.42</v>
       </c>
       <c r="K46" t="n">
-        <v>35.58</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>136.53</v>
+        <v>267.67</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>-95.09</v>
+        <v>-180.07</v>
       </c>
       <c r="K47" t="n">
-        <v>158.52</v>
+        <v>300.18</v>
       </c>
       <c r="L47" t="n">
-        <v>184.85</v>
+        <v>350.04</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>120.14</v>
+        <v>185.87</v>
       </c>
       <c r="K48" t="n">
-        <v>111.01</v>
+        <v>171.76</v>
       </c>
       <c r="L48" t="n">
-        <v>163.57</v>
+        <v>253.08</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>18.9</v>
+        <v>31.4</v>
       </c>
       <c r="K49" t="n">
-        <v>-152.56</v>
+        <v>-253.4</v>
       </c>
       <c r="L49" t="n">
-        <v>153.72</v>
+        <v>255.34</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>17</v>
       </c>
       <c r="J59" t="n">
-        <v>-67.89</v>
+        <v>-115.96</v>
       </c>
       <c r="K59" t="n">
-        <v>84.15000000000001</v>
+        <v>143.73</v>
       </c>
       <c r="L59" t="n">
-        <v>108.12</v>
+        <v>184.67</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>19</v>
       </c>
       <c r="J60" t="n">
-        <v>-127.23</v>
+        <v>-276.7</v>
       </c>
       <c r="K60" t="n">
-        <v>103.38</v>
+        <v>224.83</v>
       </c>
       <c r="L60" t="n">
-        <v>163.94</v>
+        <v>356.53</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>-105.23</v>
+        <v>-188.44</v>
       </c>
       <c r="K61" t="n">
-        <v>11.52</v>
+        <v>20.63</v>
       </c>
       <c r="L61" t="n">
-        <v>105.86</v>
+        <v>189.56</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>17</v>
       </c>
       <c r="J62" t="n">
-        <v>197.28</v>
+        <v>322.79</v>
       </c>
       <c r="K62" t="n">
-        <v>-41.39</v>
+        <v>-67.72</v>
       </c>
       <c r="L62" t="n">
-        <v>201.58</v>
+        <v>329.81</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-66.95999999999999</v>
+        <v>-108.65</v>
       </c>
       <c r="K63" t="n">
-        <v>-146.25</v>
+        <v>-237.32</v>
       </c>
       <c r="L63" t="n">
-        <v>160.85</v>
+        <v>261.01</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-134.22</v>
+        <v>-224.16</v>
       </c>
       <c r="K64" t="n">
-        <v>40.58</v>
+        <v>67.77</v>
       </c>
       <c r="L64" t="n">
-        <v>140.22</v>
+        <v>234.19</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>63.83</v>
+        <v>114.7</v>
       </c>
       <c r="K74" t="n">
-        <v>-109.53</v>
+        <v>-196.82</v>
       </c>
       <c r="L74" t="n">
-        <v>126.77</v>
+        <v>227.8</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-114.52</v>
+        <v>-235.2</v>
       </c>
       <c r="K75" t="n">
-        <v>5.95</v>
+        <v>12.23</v>
       </c>
       <c r="L75" t="n">
-        <v>114.68</v>
+        <v>235.52</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>96.15000000000001</v>
+        <v>182.38</v>
       </c>
       <c r="K76" t="n">
-        <v>-53.18</v>
+        <v>-100.88</v>
       </c>
       <c r="L76" t="n">
-        <v>109.87</v>
+        <v>208.42</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>-9.460000000000001</v>
+        <v>-16.06</v>
       </c>
       <c r="K77" t="n">
-        <v>-130.57</v>
+        <v>-221.63</v>
       </c>
       <c r="L77" t="n">
-        <v>130.91</v>
+        <v>222.21</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>24.38</v>
+        <v>40.27</v>
       </c>
       <c r="K78" t="n">
-        <v>-135.84</v>
+        <v>-224.41</v>
       </c>
       <c r="L78" t="n">
-        <v>138.01</v>
+        <v>227.99</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-144.72</v>
+        <v>-248.65</v>
       </c>
       <c r="K79" t="n">
-        <v>-20.54</v>
+        <v>-35.29</v>
       </c>
       <c r="L79" t="n">
-        <v>146.18</v>
+        <v>251.14</v>
       </c>
     </row>
     <row r="80">
